--- a/Raw data/lci-Abhi image SSP2-Base 2020 new.xlsx
+++ b/Raw data/lci-Abhi image SSP2-Base 2020 new.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20400"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20401"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Prospective LCA\Raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D8ABEF9-7526-4D27-982E-B8031C5E7F0B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00B4C532-7DCD-47D2-800A-7D86D965B00E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17280" windowHeight="8088" activeTab="1" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17280" windowHeight="8088" activeTab="2" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
   </bookViews>
   <sheets>
     <sheet name="Utilities" sheetId="6" r:id="rId1"/>
     <sheet name="Ammonia" sheetId="5" r:id="rId2"/>
+    <sheet name="Methanol" sheetId="7" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="222">
   <si>
     <t>Activity</t>
   </si>
@@ -548,14 +549,159 @@
   </si>
   <si>
     <t>ammonia; hydrogen, PEM electrolysis, electricity mix</t>
+  </si>
+  <si>
+    <t>methanol, BAU</t>
+  </si>
+  <si>
+    <t>methanol, Abhi</t>
+  </si>
+  <si>
+    <t>This is the activity for 1 kg of BAU methanol</t>
+  </si>
+  <si>
+    <t>methanol, blue</t>
+  </si>
+  <si>
+    <t>market for zinc</t>
+  </si>
+  <si>
+    <t>zinc</t>
+  </si>
+  <si>
+    <t>market for molybdenum</t>
+  </si>
+  <si>
+    <t>molybdenum</t>
+  </si>
+  <si>
+    <t>market for nickel, class 1</t>
+  </si>
+  <si>
+    <t>market for aluminium oxide, non-metallurgical</t>
+  </si>
+  <si>
+    <t>market for methanol factory</t>
+  </si>
+  <si>
+    <t>methanol factory</t>
+  </si>
+  <si>
+    <t>aluminium oxide, non-metallurgical</t>
+  </si>
+  <si>
+    <t>market group for natural gas, high pressure</t>
+  </si>
+  <si>
+    <t>natural gas heating, with CCS</t>
+  </si>
+  <si>
+    <t>heating, Abhi</t>
+  </si>
+  <si>
+    <t>air::non-urban air or from high stacks</t>
+  </si>
+  <si>
+    <t>Chloride</t>
+  </si>
+  <si>
+    <t>BOD5, Biological Oxygen Demand</t>
+  </si>
+  <si>
+    <t>Methanol</t>
+  </si>
+  <si>
+    <t>TOC, Total Organic Carbon</t>
+  </si>
+  <si>
+    <t>AOX, Adsorbable Organic Halogen as Cl</t>
+  </si>
+  <si>
+    <t>Suspended solids, unspecified</t>
+  </si>
+  <si>
+    <t>DOC, Dissolved Organic Carbon</t>
+  </si>
+  <si>
+    <t>Sulfur dioxide</t>
+  </si>
+  <si>
+    <t>Formaldehyde</t>
+  </si>
+  <si>
+    <t>Phosphorus</t>
+  </si>
+  <si>
+    <t>COD, Chemical Oxygen Demand</t>
+  </si>
+  <si>
+    <t>Phenol</t>
+  </si>
+  <si>
+    <t>This is the market activity for heating using natural gas with CCS</t>
+  </si>
+  <si>
+    <t>source</t>
+  </si>
+  <si>
+    <t>market group for electricity, low voltage</t>
+  </si>
+  <si>
+    <t>electricity, low voltage</t>
+  </si>
+  <si>
+    <t>industrial furnace production, natural gas</t>
+  </si>
+  <si>
+    <t>industrial furnace, natural gas</t>
+  </si>
+  <si>
+    <t>carbon dioxide storage/natural gas, post, 200km pipeline, storage 1000m</t>
+  </si>
+  <si>
+    <t>Dinitrogen monoxide</t>
+  </si>
+  <si>
+    <t>Acetaldehyde</t>
+  </si>
+  <si>
+    <t>Acetic acid</t>
+  </si>
+  <si>
+    <t>Benzene</t>
+  </si>
+  <si>
+    <t>Butane</t>
+  </si>
+  <si>
+    <t>Dioxins, measured as 2,3,7,8-tetrachlorodibenzo-p-dioxin</t>
+  </si>
+  <si>
+    <t>PAH, polycyclic aromatic hydrocarbons</t>
+  </si>
+  <si>
+    <t>Pentane</t>
+  </si>
+  <si>
+    <t>Propane</t>
+  </si>
+  <si>
+    <t>Propionic acid</t>
+  </si>
+  <si>
+    <t>Toluene</t>
+  </si>
+  <si>
+    <t>This is the activity for 1 kg of blue methanol</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -627,7 +773,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -666,6 +812,30 @@
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="11" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="11" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="11" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -982,7 +1152,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55E8D1F9-2651-4D58-AB8D-D63402B2F76A}">
-  <dimension ref="A1:K255"/>
+  <dimension ref="A1:K290"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="70.44140625" bestFit="1" customWidth="1"/>
@@ -5715,6 +5885,682 @@
         <v>31</v>
       </c>
       <c r="H255" s="8"/>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A256" s="2"/>
+      <c r="B256" s="2"/>
+      <c r="C256" s="3"/>
+      <c r="D256" s="2"/>
+      <c r="E256" s="2"/>
+      <c r="F256" s="2"/>
+      <c r="G256" s="2"/>
+      <c r="H256" s="2"/>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A257" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B257" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="C257" s="23"/>
+      <c r="D257" s="5"/>
+      <c r="E257" s="5"/>
+      <c r="F257" s="5"/>
+      <c r="G257" s="5"/>
+      <c r="H257" s="5"/>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A258" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="B258" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="C258" s="23"/>
+      <c r="D258" s="5"/>
+      <c r="E258" s="5"/>
+      <c r="F258" s="5"/>
+      <c r="G258" s="5"/>
+      <c r="H258" s="5"/>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A259" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B259" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C259" s="23"/>
+      <c r="D259" s="5"/>
+      <c r="E259" s="5"/>
+      <c r="F259" s="5"/>
+      <c r="G259" s="5"/>
+      <c r="H259" s="5"/>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A260" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B260" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="C260" s="23"/>
+      <c r="D260" s="5"/>
+      <c r="E260" s="5"/>
+      <c r="F260" s="5"/>
+      <c r="G260" s="5"/>
+      <c r="H260" s="5"/>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A261" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="B261" s="7">
+        <v>1</v>
+      </c>
+      <c r="C261" s="23"/>
+      <c r="D261" s="24"/>
+      <c r="E261" s="5"/>
+      <c r="F261" s="5"/>
+      <c r="G261" s="5"/>
+      <c r="H261" s="5"/>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A262" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B262" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C262" s="23"/>
+      <c r="D262" s="24"/>
+      <c r="E262" s="5"/>
+      <c r="F262" s="5"/>
+      <c r="G262" s="5"/>
+      <c r="H262" s="5"/>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A263" s="22" t="s">
+        <v>204</v>
+      </c>
+      <c r="B263" s="5"/>
+      <c r="C263" s="23"/>
+      <c r="D263" s="24"/>
+      <c r="E263" s="5"/>
+      <c r="F263" s="5"/>
+      <c r="G263" s="5"/>
+      <c r="H263" s="5"/>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A264" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="B264" s="5"/>
+      <c r="C264" s="23"/>
+      <c r="D264" s="5"/>
+      <c r="E264" s="5"/>
+      <c r="F264" s="5"/>
+      <c r="G264" s="5"/>
+      <c r="H264" s="5"/>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A265" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B265" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C265" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D265" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E265" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F265" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G265" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H265" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A266" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="B266" s="25">
+        <v>1</v>
+      </c>
+      <c r="C266" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D266" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="E266" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F266" s="20"/>
+      <c r="G266" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H266" s="20" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A267" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B267" s="26">
+        <v>2.8998115122517001E-2</v>
+      </c>
+      <c r="C267" t="s">
+        <v>18</v>
+      </c>
+      <c r="D267" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="E267" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F267" s="20"/>
+      <c r="G267" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H267" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A268" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="B268" s="6">
+        <v>1.1684210526315801E-3</v>
+      </c>
+      <c r="C268" t="s">
+        <v>18</v>
+      </c>
+      <c r="D268" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="E268" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F268" s="20"/>
+      <c r="G268" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H268" s="21" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A269" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="B269" s="6">
+        <v>2.9473684210526402E-9</v>
+      </c>
+      <c r="C269" t="s">
+        <v>18</v>
+      </c>
+      <c r="D269" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E269" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F269" s="20"/>
+      <c r="G269" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H269" s="21" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A270" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="B270" s="27">
+        <v>5.3052631578947428E-2</v>
+      </c>
+      <c r="C270" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D270" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="E270" t="s">
+        <v>9</v>
+      </c>
+      <c r="F270" s="19"/>
+      <c r="G270" t="s">
+        <v>20</v>
+      </c>
+      <c r="H270" s="20" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A271" t="s">
+        <v>29</v>
+      </c>
+      <c r="B271" s="27">
+        <v>5.8947368421052686E-3</v>
+      </c>
+      <c r="C271" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D271" s="5"/>
+      <c r="E271" t="s">
+        <v>9</v>
+      </c>
+      <c r="F271" s="28" t="s">
+        <v>190</v>
+      </c>
+      <c r="G271" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A272" t="s">
+        <v>101</v>
+      </c>
+      <c r="B272" s="16">
+        <v>2.2105263157894801E-6</v>
+      </c>
+      <c r="C272" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D272" s="20"/>
+      <c r="E272" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F272" s="28" t="s">
+        <v>190</v>
+      </c>
+      <c r="G272" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A273" t="s">
+        <v>100</v>
+      </c>
+      <c r="B273" s="16">
+        <v>2.10526315789474E-6</v>
+      </c>
+      <c r="C273" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D273" s="20"/>
+      <c r="E273" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F273" s="28" t="s">
+        <v>190</v>
+      </c>
+      <c r="G273" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A274" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="B274" s="16">
+        <v>1.05263157894737E-7</v>
+      </c>
+      <c r="C274" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D274" s="20"/>
+      <c r="E274" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F274" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="G274" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A275" t="s">
+        <v>37</v>
+      </c>
+      <c r="B275" s="16">
+        <v>1.8842105263157901E-5</v>
+      </c>
+      <c r="C275" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D275" s="20"/>
+      <c r="E275" t="s">
+        <v>9</v>
+      </c>
+      <c r="F275" s="28" t="s">
+        <v>190</v>
+      </c>
+      <c r="G275" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A276" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="B276" s="16">
+        <v>5.7894736842105305E-7</v>
+      </c>
+      <c r="C276" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D276" s="20"/>
+      <c r="E276" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F276" s="28" t="s">
+        <v>190</v>
+      </c>
+      <c r="G276" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A277" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B277" s="16">
+        <v>2.1052631578947401E-7</v>
+      </c>
+      <c r="C277" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D277" s="20"/>
+      <c r="E277" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F277" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="G277" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A278" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="B278" s="16">
+        <v>1.05263157894737E-9</v>
+      </c>
+      <c r="C278" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D278" s="20"/>
+      <c r="E278" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F278" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="G278" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A279" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="B279" s="16">
+        <v>1.5789473684210501E-7</v>
+      </c>
+      <c r="C279" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D279" s="20"/>
+      <c r="E279" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F279" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="G279" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A280" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="B280" s="16">
+        <v>4.2105263157894802E-7</v>
+      </c>
+      <c r="C280" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D280" s="20"/>
+      <c r="E280" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F280" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="G280" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A281" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="B281" s="16">
+        <v>1.0526315789473699E-11</v>
+      </c>
+      <c r="C281" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D281" s="20"/>
+      <c r="E281" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F281" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="G281" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A282" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="B282" s="16">
+        <v>7.3684210526315899E-7</v>
+      </c>
+      <c r="C282" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D282" s="20"/>
+      <c r="E282" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F282" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="G282" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A283" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="B283" s="6">
+        <v>0</v>
+      </c>
+      <c r="C283" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E283" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F283" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="G283" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A284" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="B284" s="16">
+        <v>1.05263157894737E-7</v>
+      </c>
+      <c r="C284" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E284" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F284" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="G284" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A285" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="B285" s="16">
+        <v>3.1578947368421103E-11</v>
+      </c>
+      <c r="C285" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E285" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F285" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="G285" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A286" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="B286" s="16">
+        <v>1.0526315789473701E-8</v>
+      </c>
+      <c r="C286" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E286" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F286" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="G286" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A287" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="B287" s="16">
+        <v>1.2631578947368401E-6</v>
+      </c>
+      <c r="C287" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E287" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F287" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="G287" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A288" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="B288" s="16">
+        <v>2.1052631578947401E-7</v>
+      </c>
+      <c r="C288" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E288" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F288" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="G288" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A289" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="B289" s="16">
+        <v>2.1052631578947401E-8</v>
+      </c>
+      <c r="C289" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E289" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F289" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="G289" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A290" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="B290" s="16">
+        <v>2.1052631578947401E-7</v>
+      </c>
+      <c r="C290" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E290" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F290" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="G290" s="5" t="s">
+        <v>31</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7498,4 +8344,1547 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20D067F8-C305-44D3-8E28-CF1FDCAD7A72}">
+  <dimension ref="A1:H75"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="86.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="8">
+        <v>1</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>174</v>
+      </c>
+      <c r="B9" s="9">
+        <v>1</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="9">
+        <v>0.65178999999999998</v>
+      </c>
+      <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="8"/>
+      <c r="G10" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B11" s="9">
+        <v>6.93</v>
+      </c>
+      <c r="C11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="8"/>
+      <c r="G11" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="4">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="C12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>178</v>
+      </c>
+      <c r="B13" s="14">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="C13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="8"/>
+      <c r="G13" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>180</v>
+      </c>
+      <c r="B14" s="14">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="C14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="8"/>
+      <c r="G14" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="14">
+        <v>9.0000000000000006E-5</v>
+      </c>
+      <c r="C15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="8"/>
+      <c r="G15" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>182</v>
+      </c>
+      <c r="B16" s="14">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="C16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="8"/>
+      <c r="G16" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="17">
+        <f>0.2+0.00071996+0.64928</f>
+        <v>0.84999996</v>
+      </c>
+      <c r="C17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>183</v>
+      </c>
+      <c r="B18" s="14">
+        <f>0.00020525+0.000034749</f>
+        <v>2.3999900000000002E-4</v>
+      </c>
+      <c r="C18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="8"/>
+      <c r="G18" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>184</v>
+      </c>
+      <c r="B19" s="14">
+        <v>3.7199999999999998E-11</v>
+      </c>
+      <c r="C19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>100</v>
+      </c>
+      <c r="B20" s="14">
+        <v>9.7999999999999997E-4</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="10"/>
+      <c r="E20" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="14">
+        <v>8.1600000000000006E-3</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="10"/>
+      <c r="E21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>191</v>
+      </c>
+      <c r="B22" s="14">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="10"/>
+      <c r="E22" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="14">
+        <v>1.4999999999999999E-4</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" s="10"/>
+      <c r="E23" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="14">
+        <v>5.67375E-3</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" s="10"/>
+      <c r="E24" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>192</v>
+      </c>
+      <c r="B25" s="14">
+        <v>1.8000000000000001E-4</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" s="10"/>
+      <c r="E25" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>193</v>
+      </c>
+      <c r="B26" s="16">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" s="10"/>
+      <c r="E26" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>194</v>
+      </c>
+      <c r="B27" s="16">
+        <v>2.4000000000000001E-4</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" s="10"/>
+      <c r="E27" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>195</v>
+      </c>
+      <c r="B28" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" s="10"/>
+      <c r="E28" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>193</v>
+      </c>
+      <c r="B29" s="16">
+        <v>5.2999999999999998E-4</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="4">
+        <v>3.3362499999999998E-3</v>
+      </c>
+      <c r="C30" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>196</v>
+      </c>
+      <c r="B31" s="16">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="C31" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>197</v>
+      </c>
+      <c r="B32" s="16">
+        <v>2.4000000000000001E-4</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>198</v>
+      </c>
+      <c r="B33" s="16">
+        <v>1.38E-5</v>
+      </c>
+      <c r="C33" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>199</v>
+      </c>
+      <c r="B34" s="16">
+        <v>1E-4</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>200</v>
+      </c>
+      <c r="B35" s="16">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="C35" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E35" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="B36" s="16">
+        <v>4.8999999999999998E-4</v>
+      </c>
+      <c r="C36" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H36" s="8"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="B37" s="14">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="C37" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D37" s="8"/>
+      <c r="E37" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H37" s="8"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B40" t="s">
+        <v>221</v>
+      </c>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B42" s="8">
+        <v>1</v>
+      </c>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B43" t="s">
+        <v>175</v>
+      </c>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>177</v>
+      </c>
+      <c r="B47" s="9">
+        <v>1</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" t="s">
+        <v>9</v>
+      </c>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H47" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>47</v>
+      </c>
+      <c r="B48" s="9">
+        <v>0.65178999999999998</v>
+      </c>
+      <c r="C48" t="s">
+        <v>18</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E48" t="s">
+        <v>21</v>
+      </c>
+      <c r="F48" s="8"/>
+      <c r="G48" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="B49" s="25">
+        <v>6.93</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D49" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F49" s="20"/>
+      <c r="G49" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H49" s="20" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>55</v>
+      </c>
+      <c r="B50" s="4">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="C50" t="s">
+        <v>18</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E50" t="s">
+        <v>24</v>
+      </c>
+      <c r="G50" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H50" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>178</v>
+      </c>
+      <c r="B51" s="14">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="C51" t="s">
+        <v>18</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F51" s="8"/>
+      <c r="G51" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H51" s="10" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>180</v>
+      </c>
+      <c r="B52" s="14">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="C52" t="s">
+        <v>18</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F52" s="8"/>
+      <c r="G52" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H52" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>73</v>
+      </c>
+      <c r="B53" s="14">
+        <v>9.0000000000000006E-5</v>
+      </c>
+      <c r="C53" t="s">
+        <v>18</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F53" s="8"/>
+      <c r="G53" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H53" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>182</v>
+      </c>
+      <c r="B54" s="14">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="C54" t="s">
+        <v>18</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F54" s="8"/>
+      <c r="G54" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H54" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>49</v>
+      </c>
+      <c r="B55" s="17">
+        <f>0.2+0.00071996+0.64928</f>
+        <v>0.84999996</v>
+      </c>
+      <c r="C55" t="s">
+        <v>18</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E55" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H55" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>183</v>
+      </c>
+      <c r="B56" s="14">
+        <f>0.00020525+0.000034749</f>
+        <v>2.3999900000000002E-4</v>
+      </c>
+      <c r="C56" t="s">
+        <v>18</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F56" s="8"/>
+      <c r="G56" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H56" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>184</v>
+      </c>
+      <c r="B57" s="14">
+        <v>3.7199999999999998E-11</v>
+      </c>
+      <c r="C57" t="s">
+        <v>18</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G57" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H57" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>100</v>
+      </c>
+      <c r="B58" s="14">
+        <v>9.7999999999999997E-4</v>
+      </c>
+      <c r="C58" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D58" s="10"/>
+      <c r="E58" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="G58" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>32</v>
+      </c>
+      <c r="B59" s="14">
+        <v>8.1600000000000006E-3</v>
+      </c>
+      <c r="C59" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D59" s="10"/>
+      <c r="E59" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G59" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>191</v>
+      </c>
+      <c r="B60" s="14">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="C60" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D60" s="10"/>
+      <c r="E60" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G60" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>37</v>
+      </c>
+      <c r="B61" s="14">
+        <v>1.4999999999999999E-4</v>
+      </c>
+      <c r="C61" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D61" s="10"/>
+      <c r="E61" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="G61" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>38</v>
+      </c>
+      <c r="B62" s="14">
+        <v>5.67375E-3</v>
+      </c>
+      <c r="C62" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D62" s="10"/>
+      <c r="E62" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G62" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>192</v>
+      </c>
+      <c r="B63" s="14">
+        <v>1.8000000000000001E-4</v>
+      </c>
+      <c r="C63" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D63" s="10"/>
+      <c r="E63" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G63" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>193</v>
+      </c>
+      <c r="B64" s="16">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="C64" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D64" s="10"/>
+      <c r="E64" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G64" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>194</v>
+      </c>
+      <c r="B65" s="16">
+        <v>2.4000000000000001E-4</v>
+      </c>
+      <c r="C65" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D65" s="10"/>
+      <c r="E65" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F65" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G65" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>195</v>
+      </c>
+      <c r="B66" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="C66" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D66" s="10"/>
+      <c r="E66" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F66" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G66" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>193</v>
+      </c>
+      <c r="B67" s="16">
+        <v>5.2999999999999998E-4</v>
+      </c>
+      <c r="C67" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E67" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="G67" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>38</v>
+      </c>
+      <c r="B68" s="4">
+        <v>3.3362499999999998E-3</v>
+      </c>
+      <c r="C68" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E68" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="F68" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="G68" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>196</v>
+      </c>
+      <c r="B69" s="16">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="C69" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E69" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F69" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G69" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>197</v>
+      </c>
+      <c r="B70" s="16">
+        <v>2.4000000000000001E-4</v>
+      </c>
+      <c r="C70" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E70" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F70" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G70" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>198</v>
+      </c>
+      <c r="B71" s="16">
+        <v>1.38E-5</v>
+      </c>
+      <c r="C71" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E71" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="G71" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>199</v>
+      </c>
+      <c r="B72" s="16">
+        <v>1E-4</v>
+      </c>
+      <c r="C72" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E72" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F72" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G72" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>200</v>
+      </c>
+      <c r="B73" s="16">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="C73" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E73" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F73" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G73" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A74" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="B74" s="16">
+        <v>4.8999999999999998E-4</v>
+      </c>
+      <c r="C74" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E74" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F74" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G74" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H74" s="8"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A75" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="B75" s="14">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="C75" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D75" s="8"/>
+      <c r="E75" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F75" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G75" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H75" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Raw data/lci-Abhi image SSP2-Base 2020 new.xlsx
+++ b/Raw data/lci-Abhi image SSP2-Base 2020 new.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20401"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Prospective LCA\Raw data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abhinabera/Desktop/Prospective-LCA/Raw data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00B4C532-7DCD-47D2-800A-7D86D965B00E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46778BD5-ABD3-DA47-BE74-D207C1BB04D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17280" windowHeight="8088" activeTab="2" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
   </bookViews>
   <sheets>
     <sheet name="Utilities" sheetId="6" r:id="rId1"/>
@@ -22,12 +22,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1924" uniqueCount="235">
   <si>
     <t>Activity</t>
   </si>
@@ -590,9 +601,6 @@
     <t>aluminium oxide, non-metallurgical</t>
   </si>
   <si>
-    <t>market group for natural gas, high pressure</t>
-  </si>
-  <si>
     <t>natural gas heating, with CCS</t>
   </si>
   <si>
@@ -693,6 +701,48 @@
   </si>
   <si>
     <t>This is the activity for 1 kg of blue methanol</t>
+  </si>
+  <si>
+    <t>heat pump production, heat and power co-generation unit, 160kW electrical</t>
+  </si>
+  <si>
+    <t>heat pump, heat and power co-generation unit, 160kW electrical</t>
+  </si>
+  <si>
+    <t>market for absorption chiller, 100kW</t>
+  </si>
+  <si>
+    <t>absorption chiller, 100kW</t>
+  </si>
+  <si>
+    <t>market for charcoal</t>
+  </si>
+  <si>
+    <t>charcoal</t>
+  </si>
+  <si>
+    <t>market for gas turbine, 10MW electrical</t>
+  </si>
+  <si>
+    <t>gas turbine, 10MW electrical</t>
+  </si>
+  <si>
+    <t>market for liquid storage tank, chemicals, organics</t>
+  </si>
+  <si>
+    <t>liquid storage tank, chemicals, organics</t>
+  </si>
+  <si>
+    <t>market for pump, 40W</t>
+  </si>
+  <si>
+    <t>pump, 40W</t>
+  </si>
+  <si>
+    <t>CH</t>
+  </si>
+  <si>
+    <t>This is the activity for the carbon dioxide storage</t>
   </si>
 </sst>
 </file>
@@ -773,7 +823,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -794,7 +844,6 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -805,12 +854,6 @@
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1152,34 +1195,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55E8D1F9-2651-4D58-AB8D-D63402B2F76A}">
-  <dimension ref="A1:K290"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K310"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="70.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="70.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-    </row>
-    <row r="2" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="11"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+    </row>
+    <row r="2" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="3"/>
@@ -1189,7 +1232,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1203,7 +1246,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
@@ -1217,11 +1260,11 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="8"/>
@@ -1231,7 +1274,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>5</v>
       </c>
@@ -1245,7 +1288,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
         <v>6</v>
       </c>
@@ -1259,7 +1302,7 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>8</v>
       </c>
@@ -1273,7 +1316,7 @@
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -1285,7 +1328,7 @@
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
         <v>11</v>
       </c>
@@ -1311,7 +1354,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -1321,7 +1364,7 @@
       <c r="C11" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" t="s">
         <v>4</v>
       </c>
       <c r="E11" t="s">
@@ -1335,7 +1378,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>53</v>
       </c>
@@ -1345,21 +1388,21 @@
       <c r="C12" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" t="s">
         <v>4</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
       </c>
       <c r="F12" s="8"/>
-      <c r="G12" s="10" t="s">
+      <c r="G12" t="s">
         <v>20</v>
       </c>
       <c r="H12" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>55</v>
       </c>
@@ -1369,7 +1412,7 @@
       <c r="C13" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" t="s">
         <v>44</v>
       </c>
       <c r="E13" t="s">
@@ -1382,7 +1425,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="3"/>
@@ -1392,7 +1435,7 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
@@ -1406,7 +1449,7 @@
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
         <v>2</v>
       </c>
@@ -1420,11 +1463,11 @@
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" t="s">
         <v>4</v>
       </c>
       <c r="C17" s="8"/>
@@ -1434,7 +1477,7 @@
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
         <v>5</v>
       </c>
@@ -1448,7 +1491,7 @@
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
         <v>6</v>
       </c>
@@ -1462,7 +1505,7 @@
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
         <v>8</v>
       </c>
@@ -1476,7 +1519,7 @@
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
@@ -1488,7 +1531,7 @@
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
         <v>11</v>
       </c>
@@ -1514,7 +1557,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>56</v>
       </c>
@@ -1524,7 +1567,7 @@
       <c r="C23" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" t="s">
         <v>4</v>
       </c>
       <c r="E23" t="s">
@@ -1538,7 +1581,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>58</v>
       </c>
@@ -1548,21 +1591,21 @@
       <c r="C24" t="s">
         <v>18</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" t="s">
         <v>4</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
       </c>
       <c r="F24" s="8"/>
-      <c r="G24" s="10" t="s">
+      <c r="G24" t="s">
         <v>20</v>
       </c>
       <c r="H24" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>60</v>
       </c>
@@ -1572,20 +1615,20 @@
       <c r="C25" t="s">
         <v>18</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" t="s">
         <v>4</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
       </c>
-      <c r="G25" s="10" t="s">
+      <c r="G25" t="s">
         <v>20</v>
       </c>
       <c r="H25" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -1595,20 +1638,20 @@
       <c r="C26" t="s">
         <v>18</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" t="s">
         <v>19</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
       </c>
-      <c r="G26" s="10" t="s">
+      <c r="G26" t="s">
         <v>20</v>
       </c>
       <c r="H26" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -1618,7 +1661,7 @@
       <c r="C27" t="s">
         <v>18</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" t="s">
         <v>44</v>
       </c>
       <c r="E27" t="s">
@@ -1631,7 +1674,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="3"/>
@@ -1641,7 +1684,7 @@
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>0</v>
       </c>
@@ -1655,7 +1698,7 @@
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
         <v>2</v>
       </c>
@@ -1669,11 +1712,11 @@
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" t="s">
         <v>4</v>
       </c>
       <c r="C31" s="8"/>
@@ -1683,7 +1726,7 @@
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
         <v>5</v>
       </c>
@@ -1697,7 +1740,7 @@
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
         <v>6</v>
       </c>
@@ -1711,7 +1754,7 @@
       <c r="G33" s="8"/>
       <c r="H33" s="8"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
         <v>8</v>
       </c>
@@ -1725,7 +1768,7 @@
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>10</v>
       </c>
@@ -1737,7 +1780,7 @@
       <c r="G35" s="8"/>
       <c r="H35" s="8"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
         <v>11</v>
       </c>
@@ -1763,7 +1806,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>63</v>
       </c>
@@ -1773,7 +1816,7 @@
       <c r="C37" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D37" s="10" t="s">
+      <c r="D37" t="s">
         <v>4</v>
       </c>
       <c r="E37" t="s">
@@ -1787,7 +1830,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>65</v>
       </c>
@@ -1797,21 +1840,21 @@
       <c r="C38" t="s">
         <v>18</v>
       </c>
-      <c r="D38" s="10" t="s">
+      <c r="D38" t="s">
         <v>4</v>
       </c>
       <c r="E38" t="s">
         <v>9</v>
       </c>
       <c r="F38" s="8"/>
-      <c r="G38" s="10" t="s">
+      <c r="G38" t="s">
         <v>20</v>
       </c>
       <c r="H38" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>67</v>
       </c>
@@ -1821,20 +1864,20 @@
       <c r="C39" t="s">
         <v>18</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="D39" t="s">
         <v>4</v>
       </c>
       <c r="E39" t="s">
         <v>9</v>
       </c>
-      <c r="G39" s="10" t="s">
+      <c r="G39" t="s">
         <v>20</v>
       </c>
       <c r="H39" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>69</v>
       </c>
@@ -1844,20 +1887,20 @@
       <c r="C40" t="s">
         <v>18</v>
       </c>
-      <c r="D40" s="10" t="s">
+      <c r="D40" t="s">
         <v>4</v>
       </c>
       <c r="E40" t="s">
         <v>9</v>
       </c>
-      <c r="G40" s="10" t="s">
+      <c r="G40" t="s">
         <v>20</v>
       </c>
       <c r="H40" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>55</v>
       </c>
@@ -1867,7 +1910,7 @@
       <c r="C41" t="s">
         <v>18</v>
       </c>
-      <c r="D41" s="10" t="s">
+      <c r="D41" t="s">
         <v>44</v>
       </c>
       <c r="E41" t="s">
@@ -1880,7 +1923,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="3"/>
@@ -1890,7 +1933,7 @@
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>0</v>
       </c>
@@ -1904,7 +1947,7 @@
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
         <v>2</v>
       </c>
@@ -1918,11 +1961,11 @@
       <c r="G44" s="8"/>
       <c r="H44" s="8"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B45" t="s">
         <v>4</v>
       </c>
       <c r="C45" s="8"/>
@@ -1932,7 +1975,7 @@
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="8" t="s">
         <v>5</v>
       </c>
@@ -1946,7 +1989,7 @@
       <c r="G46" s="8"/>
       <c r="H46" s="8"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
         <v>6</v>
       </c>
@@ -1960,7 +2003,7 @@
       <c r="G47" s="8"/>
       <c r="H47" s="8"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="8" t="s">
         <v>8</v>
       </c>
@@ -1974,7 +2017,7 @@
       <c r="G48" s="8"/>
       <c r="H48" s="8"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>10</v>
       </c>
@@ -1986,7 +2029,7 @@
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
         <v>11</v>
       </c>
@@ -2012,7 +2055,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>71</v>
       </c>
@@ -2022,7 +2065,7 @@
       <c r="C51" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D51" s="10" t="s">
+      <c r="D51" t="s">
         <v>4</v>
       </c>
       <c r="E51" t="s">
@@ -2036,7 +2079,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>53</v>
       </c>
@@ -2046,21 +2089,21 @@
       <c r="C52" t="s">
         <v>18</v>
       </c>
-      <c r="D52" s="10" t="s">
+      <c r="D52" t="s">
         <v>4</v>
       </c>
       <c r="E52" t="s">
         <v>9</v>
       </c>
       <c r="F52" s="8"/>
-      <c r="G52" s="10" t="s">
+      <c r="G52" t="s">
         <v>20</v>
       </c>
       <c r="H52" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>73</v>
       </c>
@@ -2070,20 +2113,20 @@
       <c r="C53" t="s">
         <v>18</v>
       </c>
-      <c r="D53" s="10" t="s">
+      <c r="D53" t="s">
         <v>4</v>
       </c>
       <c r="E53" t="s">
         <v>9</v>
       </c>
-      <c r="G53" s="10" t="s">
+      <c r="G53" t="s">
         <v>20</v>
       </c>
       <c r="H53" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>62</v>
       </c>
@@ -2093,20 +2136,20 @@
       <c r="C54" t="s">
         <v>18</v>
       </c>
-      <c r="D54" s="10" t="s">
+      <c r="D54" t="s">
         <v>19</v>
       </c>
       <c r="E54" t="s">
         <v>9</v>
       </c>
-      <c r="G54" s="10" t="s">
+      <c r="G54" t="s">
         <v>20</v>
       </c>
       <c r="H54" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>55</v>
       </c>
@@ -2116,7 +2159,7 @@
       <c r="C55" t="s">
         <v>18</v>
       </c>
-      <c r="D55" s="10" t="s">
+      <c r="D55" t="s">
         <v>44</v>
       </c>
       <c r="E55" t="s">
@@ -2129,7 +2172,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="3"/>
@@ -2139,7 +2182,7 @@
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>0</v>
       </c>
@@ -2153,7 +2196,7 @@
       <c r="G57" s="8"/>
       <c r="H57" s="8"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="8" t="s">
         <v>2</v>
       </c>
@@ -2167,11 +2210,11 @@
       <c r="G58" s="8"/>
       <c r="H58" s="8"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B59" s="10" t="s">
+      <c r="B59" t="s">
         <v>4</v>
       </c>
       <c r="C59" s="8"/>
@@ -2181,7 +2224,7 @@
       <c r="G59" s="8"/>
       <c r="H59" s="8"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="8" t="s">
         <v>5</v>
       </c>
@@ -2195,7 +2238,7 @@
       <c r="G60" s="8"/>
       <c r="H60" s="8"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="8" t="s">
         <v>6</v>
       </c>
@@ -2209,7 +2252,7 @@
       <c r="G61" s="8"/>
       <c r="H61" s="8"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="8" t="s">
         <v>8</v>
       </c>
@@ -2223,7 +2266,7 @@
       <c r="G62" s="8"/>
       <c r="H62" s="8"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>10</v>
       </c>
@@ -2235,7 +2278,7 @@
       <c r="G63" s="8"/>
       <c r="H63" s="8"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="8" t="s">
         <v>11</v>
       </c>
@@ -2261,7 +2304,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>75</v>
       </c>
@@ -2271,7 +2314,7 @@
       <c r="C65" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D65" s="10" t="s">
+      <c r="D65" t="s">
         <v>4</v>
       </c>
       <c r="E65" t="s">
@@ -2285,7 +2328,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>77</v>
       </c>
@@ -2295,21 +2338,21 @@
       <c r="C66" t="s">
         <v>18</v>
       </c>
-      <c r="D66" s="10" t="s">
+      <c r="D66" t="s">
         <v>4</v>
       </c>
       <c r="E66" t="s">
         <v>9</v>
       </c>
       <c r="F66" s="8"/>
-      <c r="G66" s="10" t="s">
+      <c r="G66" t="s">
         <v>20</v>
       </c>
       <c r="H66" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>62</v>
       </c>
@@ -2319,20 +2362,20 @@
       <c r="C67" t="s">
         <v>18</v>
       </c>
-      <c r="D67" s="10" t="s">
+      <c r="D67" t="s">
         <v>19</v>
       </c>
       <c r="E67" t="s">
         <v>9</v>
       </c>
-      <c r="G67" s="10" t="s">
+      <c r="G67" t="s">
         <v>20</v>
       </c>
       <c r="H67" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>55</v>
       </c>
@@ -2342,7 +2385,7 @@
       <c r="C68" t="s">
         <v>18</v>
       </c>
-      <c r="D68" s="10" t="s">
+      <c r="D68" t="s">
         <v>44</v>
       </c>
       <c r="E68" t="s">
@@ -2355,7 +2398,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="3"/>
@@ -2365,7 +2408,7 @@
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>0</v>
       </c>
@@ -2379,7 +2422,7 @@
       <c r="G70" s="8"/>
       <c r="H70" s="8"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="8" t="s">
         <v>2</v>
       </c>
@@ -2393,11 +2436,11 @@
       <c r="G71" s="8"/>
       <c r="H71" s="8"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B72" s="10" t="s">
+      <c r="B72" t="s">
         <v>4</v>
       </c>
       <c r="C72" s="8"/>
@@ -2407,7 +2450,7 @@
       <c r="G72" s="8"/>
       <c r="H72" s="8"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="8" t="s">
         <v>5</v>
       </c>
@@ -2421,7 +2464,7 @@
       <c r="G73" s="8"/>
       <c r="H73" s="8"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="8" t="s">
         <v>6</v>
       </c>
@@ -2435,7 +2478,7 @@
       <c r="G74" s="8"/>
       <c r="H74" s="8"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="8" t="s">
         <v>8</v>
       </c>
@@ -2449,7 +2492,7 @@
       <c r="G75" s="8"/>
       <c r="H75" s="8"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>10</v>
       </c>
@@ -2461,7 +2504,7 @@
       <c r="G76" s="8"/>
       <c r="H76" s="8"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="8" t="s">
         <v>11</v>
       </c>
@@ -2487,7 +2530,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>78</v>
       </c>
@@ -2497,7 +2540,7 @@
       <c r="C78" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D78" s="10" t="s">
+      <c r="D78" t="s">
         <v>4</v>
       </c>
       <c r="E78" t="s">
@@ -2511,7 +2554,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>65</v>
       </c>
@@ -2521,21 +2564,21 @@
       <c r="C79" t="s">
         <v>18</v>
       </c>
-      <c r="D79" s="10" t="s">
+      <c r="D79" t="s">
         <v>4</v>
       </c>
       <c r="E79" t="s">
         <v>9</v>
       </c>
       <c r="F79" s="8"/>
-      <c r="G79" s="10" t="s">
+      <c r="G79" t="s">
         <v>20</v>
       </c>
       <c r="H79" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>80</v>
       </c>
@@ -2545,21 +2588,21 @@
       <c r="C80" t="s">
         <v>18</v>
       </c>
-      <c r="D80" s="10" t="s">
+      <c r="D80" t="s">
         <v>19</v>
       </c>
       <c r="E80" t="s">
         <v>9</v>
       </c>
       <c r="F80" s="8"/>
-      <c r="G80" s="10" t="s">
+      <c r="G80" t="s">
         <v>20</v>
       </c>
       <c r="H80" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>62</v>
       </c>
@@ -2569,20 +2612,20 @@
       <c r="C81" t="s">
         <v>18</v>
       </c>
-      <c r="D81" s="10" t="s">
+      <c r="D81" t="s">
         <v>19</v>
       </c>
       <c r="E81" t="s">
         <v>9</v>
       </c>
-      <c r="G81" s="10" t="s">
+      <c r="G81" t="s">
         <v>20</v>
       </c>
       <c r="H81" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>55</v>
       </c>
@@ -2592,7 +2635,7 @@
       <c r="C82" t="s">
         <v>18</v>
       </c>
-      <c r="D82" s="10" t="s">
+      <c r="D82" t="s">
         <v>44</v>
       </c>
       <c r="E82" t="s">
@@ -2605,7 +2648,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="3"/>
@@ -2615,7 +2658,7 @@
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>0</v>
       </c>
@@ -2629,7 +2672,7 @@
       <c r="G84" s="8"/>
       <c r="H84" s="8"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="8" t="s">
         <v>2</v>
       </c>
@@ -2643,11 +2686,11 @@
       <c r="G85" s="8"/>
       <c r="H85" s="8"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B86" s="10" t="s">
+      <c r="B86" t="s">
         <v>4</v>
       </c>
       <c r="C86" s="8"/>
@@ -2657,7 +2700,7 @@
       <c r="G86" s="8"/>
       <c r="H86" s="8"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="8" t="s">
         <v>5</v>
       </c>
@@ -2671,7 +2714,7 @@
       <c r="G87" s="8"/>
       <c r="H87" s="8"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="8" t="s">
         <v>6</v>
       </c>
@@ -2685,7 +2728,7 @@
       <c r="G88" s="8"/>
       <c r="H88" s="8"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="8" t="s">
         <v>8</v>
       </c>
@@ -2699,7 +2742,7 @@
       <c r="G89" s="8"/>
       <c r="H89" s="8"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>10</v>
       </c>
@@ -2711,7 +2754,7 @@
       <c r="G90" s="8"/>
       <c r="H90" s="8"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="8" t="s">
         <v>11</v>
       </c>
@@ -2737,7 +2780,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>82</v>
       </c>
@@ -2747,7 +2790,7 @@
       <c r="C92" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D92" s="10" t="s">
+      <c r="D92" t="s">
         <v>4</v>
       </c>
       <c r="E92" t="s">
@@ -2761,7 +2804,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>77</v>
       </c>
@@ -2771,21 +2814,21 @@
       <c r="C93" t="s">
         <v>18</v>
       </c>
-      <c r="D93" s="10" t="s">
+      <c r="D93" t="s">
         <v>4</v>
       </c>
       <c r="E93" t="s">
         <v>9</v>
       </c>
       <c r="F93" s="8"/>
-      <c r="G93" s="10" t="s">
+      <c r="G93" t="s">
         <v>20</v>
       </c>
       <c r="H93" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>62</v>
       </c>
@@ -2795,20 +2838,20 @@
       <c r="C94" t="s">
         <v>18</v>
       </c>
-      <c r="D94" s="10" t="s">
+      <c r="D94" t="s">
         <v>19</v>
       </c>
       <c r="E94" t="s">
         <v>9</v>
       </c>
-      <c r="G94" s="10" t="s">
+      <c r="G94" t="s">
         <v>20</v>
       </c>
       <c r="H94" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>55</v>
       </c>
@@ -2818,7 +2861,7 @@
       <c r="C95" t="s">
         <v>18</v>
       </c>
-      <c r="D95" s="10" t="s">
+      <c r="D95" t="s">
         <v>44</v>
       </c>
       <c r="E95" t="s">
@@ -2831,7 +2874,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="3"/>
@@ -2841,7 +2884,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>0</v>
       </c>
@@ -2855,7 +2898,7 @@
       <c r="G97" s="8"/>
       <c r="H97" s="8"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="8" t="s">
         <v>2</v>
       </c>
@@ -2869,11 +2912,11 @@
       <c r="G98" s="8"/>
       <c r="H98" s="8"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B99" s="10" t="s">
+      <c r="B99" t="s">
         <v>4</v>
       </c>
       <c r="C99" s="8"/>
@@ -2883,7 +2926,7 @@
       <c r="G99" s="8"/>
       <c r="H99" s="8"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="8" t="s">
         <v>5</v>
       </c>
@@ -2897,7 +2940,7 @@
       <c r="G100" s="8"/>
       <c r="H100" s="8"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="8" t="s">
         <v>6</v>
       </c>
@@ -2911,7 +2954,7 @@
       <c r="G101" s="8"/>
       <c r="H101" s="8"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="8" t="s">
         <v>8</v>
       </c>
@@ -2925,7 +2968,7 @@
       <c r="G102" s="8"/>
       <c r="H102" s="8"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
         <v>10</v>
       </c>
@@ -2937,7 +2980,7 @@
       <c r="G103" s="8"/>
       <c r="H103" s="8"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="8" t="s">
         <v>11</v>
       </c>
@@ -2963,7 +3006,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>172</v>
       </c>
@@ -2973,7 +3016,7 @@
       <c r="C105" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D105" s="10" t="s">
+      <c r="D105" t="s">
         <v>4</v>
       </c>
       <c r="E105" t="s">
@@ -2987,7 +3030,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>51</v>
       </c>
@@ -2997,21 +3040,21 @@
       <c r="C106" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D106" s="10" t="s">
+      <c r="D106" t="s">
         <v>4</v>
       </c>
       <c r="E106" t="s">
         <v>9</v>
       </c>
       <c r="F106" s="8"/>
-      <c r="G106" s="10" t="s">
+      <c r="G106" t="s">
         <v>20</v>
       </c>
       <c r="H106" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>56</v>
       </c>
@@ -3021,21 +3064,21 @@
       <c r="C107" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D107" s="10" t="s">
+      <c r="D107" t="s">
         <v>4</v>
       </c>
       <c r="E107" t="s">
         <v>9</v>
       </c>
       <c r="F107" s="8"/>
-      <c r="G107" s="10" t="s">
+      <c r="G107" t="s">
         <v>20</v>
       </c>
       <c r="H107" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>63</v>
       </c>
@@ -3045,21 +3088,21 @@
       <c r="C108" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D108" s="10" t="s">
+      <c r="D108" t="s">
         <v>4</v>
       </c>
       <c r="E108" t="s">
         <v>9</v>
       </c>
       <c r="F108" s="8"/>
-      <c r="G108" s="10" t="s">
+      <c r="G108" t="s">
         <v>20</v>
       </c>
       <c r="H108" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>71</v>
       </c>
@@ -3069,21 +3112,21 @@
       <c r="C109" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D109" s="10" t="s">
+      <c r="D109" t="s">
         <v>4</v>
       </c>
       <c r="E109" t="s">
         <v>9</v>
       </c>
       <c r="F109" s="8"/>
-      <c r="G109" s="10" t="s">
+      <c r="G109" t="s">
         <v>20</v>
       </c>
       <c r="H109" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>75</v>
       </c>
@@ -3093,21 +3136,21 @@
       <c r="C110" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D110" s="10" t="s">
+      <c r="D110" t="s">
         <v>4</v>
       </c>
       <c r="E110" t="s">
         <v>9</v>
       </c>
       <c r="F110" s="8"/>
-      <c r="G110" s="10" t="s">
+      <c r="G110" t="s">
         <v>20</v>
       </c>
       <c r="H110" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>78</v>
       </c>
@@ -3117,21 +3160,21 @@
       <c r="C111" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D111" s="10" t="s">
+      <c r="D111" t="s">
         <v>4</v>
       </c>
       <c r="E111" t="s">
         <v>9</v>
       </c>
       <c r="F111" s="8"/>
-      <c r="G111" s="10" t="s">
+      <c r="G111" t="s">
         <v>20</v>
       </c>
       <c r="H111" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>82</v>
       </c>
@@ -3141,21 +3184,21 @@
       <c r="C112" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D112" s="10" t="s">
+      <c r="D112" t="s">
         <v>4</v>
       </c>
       <c r="E112" t="s">
         <v>9</v>
       </c>
       <c r="F112" s="8"/>
-      <c r="G112" s="10" t="s">
+      <c r="G112" t="s">
         <v>20</v>
       </c>
       <c r="H112" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="3"/>
@@ -3165,7 +3208,7 @@
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
         <v>0</v>
       </c>
@@ -3179,7 +3222,7 @@
       <c r="G114" s="8"/>
       <c r="H114" s="8"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="8" t="s">
         <v>2</v>
       </c>
@@ -3193,11 +3236,11 @@
       <c r="G115" s="8"/>
       <c r="H115" s="8"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B116" s="10" t="s">
+      <c r="B116" t="s">
         <v>4</v>
       </c>
       <c r="C116" s="8"/>
@@ -3207,7 +3250,7 @@
       <c r="G116" s="8"/>
       <c r="H116" s="8"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="8" t="s">
         <v>5</v>
       </c>
@@ -3221,7 +3264,7 @@
       <c r="G117" s="8"/>
       <c r="H117" s="8"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="8" t="s">
         <v>6</v>
       </c>
@@ -3235,7 +3278,7 @@
       <c r="G118" s="8"/>
       <c r="H118" s="8"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="8" t="s">
         <v>8</v>
       </c>
@@ -3249,7 +3292,7 @@
       <c r="G119" s="8"/>
       <c r="H119" s="8"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
         <v>10</v>
       </c>
@@ -3261,7 +3304,7 @@
       <c r="G120" s="8"/>
       <c r="H120" s="8"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="8" t="s">
         <v>11</v>
       </c>
@@ -3287,7 +3330,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>85</v>
       </c>
@@ -3297,7 +3340,7 @@
       <c r="C122" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D122" s="10" t="s">
+      <c r="D122" t="s">
         <v>4</v>
       </c>
       <c r="E122" t="s">
@@ -3311,7 +3354,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>88</v>
       </c>
@@ -3322,21 +3365,21 @@
       <c r="C123" t="s">
         <v>18</v>
       </c>
-      <c r="D123" s="10" t="s">
+      <c r="D123" t="s">
         <v>4</v>
       </c>
       <c r="E123" t="s">
         <v>9</v>
       </c>
       <c r="F123" s="8"/>
-      <c r="G123" s="10" t="s">
+      <c r="G123" t="s">
         <v>20</v>
       </c>
       <c r="H123" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>48</v>
       </c>
@@ -3347,79 +3390,79 @@
       <c r="C124" t="s">
         <v>18</v>
       </c>
-      <c r="D124" s="10" t="s">
+      <c r="D124" t="s">
         <v>19</v>
       </c>
       <c r="E124" t="s">
         <v>9</v>
       </c>
       <c r="F124" s="8"/>
-      <c r="G124" s="10" t="s">
+      <c r="G124" t="s">
         <v>20</v>
       </c>
       <c r="H124" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>90</v>
       </c>
-      <c r="B125" s="14">
+      <c r="B125" s="13">
         <f>0.13/1000</f>
         <v>1.3000000000000002E-4</v>
       </c>
       <c r="C125" t="s">
         <v>18</v>
       </c>
-      <c r="D125" s="10" t="s">
+      <c r="D125" t="s">
         <v>4</v>
       </c>
       <c r="E125" t="s">
         <v>9</v>
       </c>
       <c r="F125" s="8"/>
-      <c r="G125" s="10" t="s">
+      <c r="G125" t="s">
         <v>20</v>
       </c>
       <c r="H125" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>92</v>
       </c>
-      <c r="B126" s="14">
+      <c r="B126" s="13">
         <f>0.075/1000</f>
         <v>7.4999999999999993E-5</v>
       </c>
       <c r="C126" t="s">
         <v>18</v>
       </c>
-      <c r="D126" s="10" t="s">
+      <c r="D126" t="s">
         <v>4</v>
       </c>
       <c r="E126" t="s">
         <v>9</v>
       </c>
       <c r="F126" s="8"/>
-      <c r="G126" s="10" t="s">
+      <c r="G126" t="s">
         <v>20</v>
       </c>
       <c r="H126" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>35</v>
       </c>
-      <c r="B127" s="16">
+      <c r="B127" s="15">
         <f>0.21/1000</f>
         <v>2.0999999999999998E-4</v>
       </c>
-      <c r="C127" s="10" t="s">
+      <c r="C127" t="s">
         <v>30</v>
       </c>
       <c r="E127" t="s">
@@ -3428,19 +3471,19 @@
       <c r="F127" t="s">
         <v>39</v>
       </c>
-      <c r="G127" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G127" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>94</v>
       </c>
-      <c r="B128" s="16">
+      <c r="B128" s="15">
         <f>0.0305/1000</f>
         <v>3.0499999999999999E-5</v>
       </c>
-      <c r="C128" s="10" t="s">
+      <c r="C128" t="s">
         <v>30</v>
       </c>
       <c r="E128" t="s">
@@ -3449,11 +3492,11 @@
       <c r="F128" t="s">
         <v>39</v>
       </c>
-      <c r="G128" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G128" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>95</v>
       </c>
@@ -3470,14 +3513,14 @@
       <c r="E129" t="s">
         <v>9</v>
       </c>
-      <c r="G129" s="10" t="s">
+      <c r="G129" t="s">
         <v>20</v>
       </c>
       <c r="H129" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="3"/>
@@ -3487,7 +3530,7 @@
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
         <v>0</v>
       </c>
@@ -3501,7 +3544,7 @@
       <c r="G131" s="8"/>
       <c r="H131" s="8"/>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A132" s="8" t="s">
         <v>2</v>
       </c>
@@ -3515,11 +3558,11 @@
       <c r="G132" s="8"/>
       <c r="H132" s="8"/>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A133" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B133" s="10" t="s">
+      <c r="B133" t="s">
         <v>4</v>
       </c>
       <c r="C133" s="8"/>
@@ -3529,7 +3572,7 @@
       <c r="G133" s="8"/>
       <c r="H133" s="8"/>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A134" s="8" t="s">
         <v>5</v>
       </c>
@@ -3543,7 +3586,7 @@
       <c r="G134" s="8"/>
       <c r="H134" s="8"/>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A135" s="8" t="s">
         <v>6</v>
       </c>
@@ -3557,7 +3600,7 @@
       <c r="G135" s="8"/>
       <c r="H135" s="8"/>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A136" s="8" t="s">
         <v>8</v>
       </c>
@@ -3571,7 +3614,7 @@
       <c r="G136" s="8"/>
       <c r="H136" s="8"/>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
         <v>10</v>
       </c>
@@ -3583,7 +3626,7 @@
       <c r="G137" s="8"/>
       <c r="H137" s="8"/>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A138" s="8" t="s">
         <v>11</v>
       </c>
@@ -3609,7 +3652,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>97</v>
       </c>
@@ -3619,7 +3662,7 @@
       <c r="C139" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D139" s="10" t="s">
+      <c r="D139" t="s">
         <v>4</v>
       </c>
       <c r="E139" t="s">
@@ -3633,165 +3676,158 @@
         <v>99</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>100</v>
       </c>
-      <c r="B140" s="14">
+      <c r="B140" s="13">
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="C140" t="s">
         <v>30</v>
       </c>
-      <c r="D140" s="10"/>
       <c r="E140" t="s">
         <v>9</v>
       </c>
-      <c r="F140" s="10" t="s">
+      <c r="F140" t="s">
         <v>39</v>
       </c>
-      <c r="G140" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K140" s="15"/>
-    </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G140" t="s">
+        <v>31</v>
+      </c>
+      <c r="K140" s="14"/>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>37</v>
       </c>
-      <c r="B141" s="14">
+      <c r="B141" s="13">
         <v>6.3E-5</v>
       </c>
       <c r="C141" t="s">
         <v>30</v>
       </c>
-      <c r="D141" s="10"/>
       <c r="E141" t="s">
         <v>9</v>
       </c>
-      <c r="F141" s="10" t="s">
+      <c r="F141" t="s">
         <v>39</v>
       </c>
-      <c r="G141" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K141" s="15"/>
-    </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G141" t="s">
+        <v>31</v>
+      </c>
+      <c r="K141" s="14"/>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>101</v>
       </c>
-      <c r="B142" s="14">
+      <c r="B142" s="13">
         <v>3.93E-5</v>
       </c>
       <c r="C142" t="s">
         <v>30</v>
       </c>
-      <c r="D142" s="10"/>
       <c r="E142" t="s">
         <v>9</v>
       </c>
-      <c r="F142" s="10" t="s">
+      <c r="F142" t="s">
         <v>39</v>
       </c>
-      <c r="G142" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K142" s="15"/>
-    </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G142" t="s">
+        <v>31</v>
+      </c>
+      <c r="K142" s="14"/>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>102</v>
       </c>
-      <c r="B143" s="14">
+      <c r="B143" s="13">
         <v>2.5799999999999999E-6</v>
       </c>
       <c r="C143" t="s">
         <v>30</v>
       </c>
-      <c r="D143" s="10"/>
       <c r="E143" t="s">
         <v>9</v>
       </c>
-      <c r="F143" s="10" t="s">
+      <c r="F143" t="s">
         <v>39</v>
       </c>
-      <c r="G143" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K143" s="15"/>
-    </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G143" t="s">
+        <v>31</v>
+      </c>
+      <c r="K143" s="14"/>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>103</v>
       </c>
-      <c r="B144" s="14">
+      <c r="B144" s="13">
         <v>2.8099999999999999E-7</v>
       </c>
       <c r="C144" t="s">
         <v>30</v>
       </c>
-      <c r="D144" s="10"/>
       <c r="E144" t="s">
         <v>9</v>
       </c>
-      <c r="F144" s="10" t="s">
+      <c r="F144" t="s">
         <v>39</v>
       </c>
-      <c r="G144" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K144" s="15"/>
-    </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G144" t="s">
+        <v>31</v>
+      </c>
+      <c r="K144" s="14"/>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>104</v>
       </c>
-      <c r="B145" s="14">
+      <c r="B145" s="13">
         <v>8.8999999999999995E-7</v>
       </c>
       <c r="C145" t="s">
         <v>30</v>
       </c>
-      <c r="D145" s="10"/>
       <c r="E145" t="s">
         <v>9</v>
       </c>
-      <c r="F145" s="10" t="s">
+      <c r="F145" t="s">
         <v>39</v>
       </c>
-      <c r="G145" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K145" s="15"/>
-    </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G145" t="s">
+        <v>31</v>
+      </c>
+      <c r="K145" s="14"/>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>105</v>
       </c>
-      <c r="B146" s="14">
+      <c r="B146" s="13">
         <v>8.8999999999999995E-7</v>
       </c>
       <c r="C146" t="s">
         <v>30</v>
       </c>
-      <c r="D146" s="10"/>
       <c r="E146" t="s">
         <v>9</v>
       </c>
-      <c r="F146" s="10" t="s">
+      <c r="F146" t="s">
         <v>39</v>
       </c>
-      <c r="G146" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K146" s="15"/>
-    </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G146" t="s">
+        <v>31</v>
+      </c>
+      <c r="K146" s="14"/>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>106</v>
       </c>
-      <c r="B147" s="14">
+      <c r="B147" s="13">
         <v>1.5000000000000001E-12</v>
       </c>
       <c r="C147" t="s">
@@ -3800,19 +3836,19 @@
       <c r="E147" t="s">
         <v>9</v>
       </c>
-      <c r="F147" s="10" t="s">
+      <c r="F147" t="s">
         <v>39</v>
       </c>
-      <c r="G147" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K147" s="15"/>
-    </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G147" t="s">
+        <v>31</v>
+      </c>
+      <c r="K147" s="14"/>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>107</v>
       </c>
-      <c r="B148" s="14">
+      <c r="B148" s="13">
         <v>2.4999999999999999E-13</v>
       </c>
       <c r="C148" t="s">
@@ -3821,19 +3857,19 @@
       <c r="E148" t="s">
         <v>9</v>
       </c>
-      <c r="F148" s="10" t="s">
+      <c r="F148" t="s">
         <v>39</v>
       </c>
-      <c r="G148" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K148" s="15"/>
-    </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G148" t="s">
+        <v>31</v>
+      </c>
+      <c r="K148" s="14"/>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>108</v>
       </c>
-      <c r="B149" s="14">
+      <c r="B149" s="13">
         <v>9.9999999999999991E-11</v>
       </c>
       <c r="C149" t="s">
@@ -3842,19 +3878,19 @@
       <c r="E149" t="s">
         <v>9</v>
       </c>
-      <c r="F149" s="10" t="s">
+      <c r="F149" t="s">
         <v>39</v>
       </c>
-      <c r="G149" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K149" s="15"/>
-    </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G149" t="s">
+        <v>31</v>
+      </c>
+      <c r="K149" s="14"/>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>109</v>
       </c>
-      <c r="B150" s="14">
+      <c r="B150" s="13">
         <v>1.2E-10</v>
       </c>
       <c r="C150" t="s">
@@ -3863,19 +3899,19 @@
       <c r="E150" t="s">
         <v>9</v>
       </c>
-      <c r="F150" s="10" t="s">
+      <c r="F150" t="s">
         <v>39</v>
       </c>
-      <c r="G150" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K150" s="15"/>
-    </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G150" t="s">
+        <v>31</v>
+      </c>
+      <c r="K150" s="14"/>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>110</v>
       </c>
-      <c r="B151" s="14">
+      <c r="B151" s="13">
         <v>7.5999999999999999E-13</v>
       </c>
       <c r="C151" t="s">
@@ -3884,19 +3920,19 @@
       <c r="E151" t="s">
         <v>9</v>
       </c>
-      <c r="F151" s="10" t="s">
+      <c r="F151" t="s">
         <v>39</v>
       </c>
-      <c r="G151" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K151" s="15"/>
-    </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G151" t="s">
+        <v>31</v>
+      </c>
+      <c r="K151" s="14"/>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>111</v>
       </c>
-      <c r="B152" s="14">
+      <c r="B152" s="13">
         <v>7.5999999999999992E-14</v>
       </c>
       <c r="C152" t="s">
@@ -3905,19 +3941,19 @@
       <c r="E152" t="s">
         <v>9</v>
       </c>
-      <c r="F152" s="10" t="s">
+      <c r="F152" t="s">
         <v>39</v>
       </c>
-      <c r="G152" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K152" s="15"/>
-    </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G152" t="s">
+        <v>31</v>
+      </c>
+      <c r="K152" s="14"/>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>112</v>
       </c>
-      <c r="B153" s="14">
+      <c r="B153" s="13">
         <v>5.0999999999999995E-13</v>
       </c>
       <c r="C153" t="s">
@@ -3926,19 +3962,19 @@
       <c r="E153" t="s">
         <v>9</v>
       </c>
-      <c r="F153" s="10" t="s">
+      <c r="F153" t="s">
         <v>39</v>
       </c>
-      <c r="G153" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K153" s="15"/>
-    </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G153" t="s">
+        <v>31</v>
+      </c>
+      <c r="K153" s="14"/>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>113</v>
       </c>
-      <c r="B154" s="14">
+      <c r="B154" s="13">
         <v>1.1199999999999999E-11</v>
       </c>
       <c r="C154" t="s">
@@ -3947,19 +3983,19 @@
       <c r="E154" t="s">
         <v>9</v>
       </c>
-      <c r="F154" s="10" t="s">
+      <c r="F154" t="s">
         <v>39</v>
       </c>
-      <c r="G154" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K154" s="15"/>
-    </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G154" t="s">
+        <v>31</v>
+      </c>
+      <c r="K154" s="14"/>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>114</v>
       </c>
-      <c r="B155" s="14">
+      <c r="B155" s="13">
         <v>1.5000000000000001E-12</v>
       </c>
       <c r="C155" t="s">
@@ -3968,19 +4004,19 @@
       <c r="E155" t="s">
         <v>9</v>
       </c>
-      <c r="F155" s="10" t="s">
+      <c r="F155" t="s">
         <v>39</v>
       </c>
-      <c r="G155" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K155" s="15"/>
-    </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G155" t="s">
+        <v>31</v>
+      </c>
+      <c r="K155" s="14"/>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>115</v>
       </c>
-      <c r="B156" s="14">
+      <c r="B156" s="13">
         <v>5.6000000000000004E-13</v>
       </c>
       <c r="C156" t="s">
@@ -3989,19 +4025,19 @@
       <c r="E156" t="s">
         <v>9</v>
       </c>
-      <c r="F156" s="10" t="s">
+      <c r="F156" t="s">
         <v>39</v>
       </c>
-      <c r="G156" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K156" s="15"/>
-    </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G156" t="s">
+        <v>31</v>
+      </c>
+      <c r="K156" s="14"/>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>116</v>
       </c>
-      <c r="B157" s="14">
+      <c r="B157" s="13">
         <v>8.3999999999999995E-13</v>
       </c>
       <c r="C157" t="s">
@@ -4010,19 +4046,19 @@
       <c r="E157" t="s">
         <v>9</v>
       </c>
-      <c r="F157" s="10" t="s">
+      <c r="F157" t="s">
         <v>39</v>
       </c>
-      <c r="G157" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K157" s="15"/>
-    </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G157" t="s">
+        <v>31</v>
+      </c>
+      <c r="K157" s="14"/>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>117</v>
       </c>
-      <c r="B158" s="14">
+      <c r="B158" s="13">
         <v>8.3999999999999995E-13</v>
       </c>
       <c r="C158" t="s">
@@ -4031,19 +4067,19 @@
       <c r="E158" t="s">
         <v>9</v>
       </c>
-      <c r="F158" s="10" t="s">
+      <c r="F158" t="s">
         <v>39</v>
       </c>
-      <c r="G158" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K158" s="15"/>
-    </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G158" t="s">
+        <v>31</v>
+      </c>
+      <c r="K158" s="14"/>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>118</v>
       </c>
-      <c r="B159" s="14">
+      <c r="B159" s="13">
         <v>8.3999999999999995E-13</v>
       </c>
       <c r="C159" t="s">
@@ -4052,15 +4088,15 @@
       <c r="E159" t="s">
         <v>9</v>
       </c>
-      <c r="F159" s="10" t="s">
+      <c r="F159" t="s">
         <v>39</v>
       </c>
-      <c r="G159" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K159" s="15"/>
-    </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G159" t="s">
+        <v>31</v>
+      </c>
+      <c r="K159" s="14"/>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="3"/>
@@ -4070,7 +4106,7 @@
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
         <v>0</v>
       </c>
@@ -4085,11 +4121,11 @@
       <c r="H161" s="8"/>
       <c r="I161" s="8"/>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A162" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B162" s="10" t="s">
+      <c r="B162" t="s">
         <v>158</v>
       </c>
       <c r="C162" s="8"/>
@@ -4100,11 +4136,11 @@
       <c r="H162" s="8"/>
       <c r="I162" s="8"/>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A163" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B163" s="10" t="s">
+      <c r="B163" t="s">
         <v>4</v>
       </c>
       <c r="C163" s="8"/>
@@ -4115,7 +4151,7 @@
       <c r="H163" s="8"/>
       <c r="I163" s="8"/>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A164" s="8" t="s">
         <v>5</v>
       </c>
@@ -4130,7 +4166,7 @@
       <c r="H164" s="8"/>
       <c r="I164" s="8"/>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A165" s="8" t="s">
         <v>6</v>
       </c>
@@ -4145,7 +4181,7 @@
       <c r="H165" s="8"/>
       <c r="I165" s="8"/>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A166" s="8" t="s">
         <v>8</v>
       </c>
@@ -4160,7 +4196,7 @@
       <c r="H166" s="8"/>
       <c r="I166" s="8"/>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
         <v>10</v>
       </c>
@@ -4173,7 +4209,7 @@
       <c r="H167" s="8"/>
       <c r="I167" s="8"/>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A168" s="8" t="s">
         <v>11</v>
       </c>
@@ -4200,7 +4236,7 @@
       </c>
       <c r="I168" s="8"/>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A169" s="8" t="s">
         <v>29</v>
       </c>
@@ -4223,11 +4259,11 @@
       <c r="H169" s="8"/>
       <c r="I169" s="8"/>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A170" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="B170" s="14">
+      <c r="B170" s="13">
         <v>1.4039999999999999E-5</v>
       </c>
       <c r="C170" s="8" t="s">
@@ -4245,9 +4281,9 @@
       </c>
       <c r="H170" s="8"/>
       <c r="I170" s="8"/>
-      <c r="K170" s="15"/>
-    </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K170" s="14"/>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A171" s="8" t="s">
         <v>129</v>
       </c>
@@ -4269,13 +4305,13 @@
       </c>
       <c r="H171" s="8"/>
       <c r="I171" s="8"/>
-      <c r="K171" s="15"/>
-    </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K171" s="14"/>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A172" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="B172" s="14">
+      <c r="B172" s="13">
         <v>8.5109999999999986E-6</v>
       </c>
       <c r="C172" s="8" t="s">
@@ -4293,13 +4329,13 @@
       </c>
       <c r="H172" s="8"/>
       <c r="I172" s="8"/>
-      <c r="K172" s="15"/>
-    </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K172" s="14"/>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A173" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B173" s="14">
+      <c r="B173" s="13">
         <v>8.5109999999999986E-6</v>
       </c>
       <c r="C173" s="8" t="s">
@@ -4317,9 +4353,9 @@
       </c>
       <c r="H173" s="8"/>
       <c r="I173" s="8"/>
-      <c r="K173" s="15"/>
-    </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K173" s="14"/>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A174" s="8" t="s">
         <v>124</v>
       </c>
@@ -4329,7 +4365,7 @@
       <c r="C174" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D174" s="10" t="s">
+      <c r="D174" t="s">
         <v>4</v>
       </c>
       <c r="E174" s="8" t="s">
@@ -4343,13 +4379,13 @@
         <v>125</v>
       </c>
       <c r="I174" s="8"/>
-      <c r="K174" s="15"/>
-    </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K174" s="14"/>
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A175" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="B175" s="14">
+      <c r="B175" s="13">
         <v>9.8720000000000014E-6</v>
       </c>
       <c r="C175" s="8" t="s">
@@ -4369,13 +4405,13 @@
         <v>135</v>
       </c>
       <c r="I175" s="8"/>
-      <c r="K175" s="15"/>
-    </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K175" s="14"/>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A176" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="B176" s="14">
+      <c r="B176" s="13">
         <v>4.7780000000000002E-8</v>
       </c>
       <c r="C176" s="8" t="s">
@@ -4395,13 +4431,13 @@
         <v>137</v>
       </c>
       <c r="I176" s="8"/>
-      <c r="K176" s="15"/>
-    </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K176" s="14"/>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A177" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="B177" s="14">
+      <c r="B177" s="13">
         <v>1.9410000000000001E-6</v>
       </c>
       <c r="C177" s="8" t="s">
@@ -4421,9 +4457,9 @@
         <v>139</v>
       </c>
       <c r="I177" s="8"/>
-      <c r="K177" s="15"/>
-    </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K177" s="14"/>
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A178" s="8" t="s">
         <v>140</v>
       </c>
@@ -4447,13 +4483,13 @@
         <v>140</v>
       </c>
       <c r="I178" s="8"/>
-      <c r="K178" s="15"/>
-    </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K178" s="14"/>
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A179" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B179" s="14">
+      <c r="B179" s="13">
         <v>1.021E-3</v>
       </c>
       <c r="C179" s="8" t="s">
@@ -4473,13 +4509,13 @@
         <v>141</v>
       </c>
       <c r="I179" s="8"/>
-      <c r="K179" s="15"/>
-    </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K179" s="14"/>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A180" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="B180" s="14">
+      <c r="B180" s="13">
         <v>1.3140000000000001E-3</v>
       </c>
       <c r="C180" s="8" t="s">
@@ -4499,13 +4535,13 @@
         <v>144</v>
       </c>
       <c r="I180" s="8"/>
-      <c r="K180" s="15"/>
-    </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K180" s="14"/>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A181" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="B181" s="14">
+      <c r="B181" s="13">
         <v>8.2189999999999997E-8</v>
       </c>
       <c r="C181" s="8" t="s">
@@ -4525,13 +4561,13 @@
         <v>147</v>
       </c>
       <c r="I181" s="8"/>
-      <c r="K181" s="15"/>
-    </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K181" s="14"/>
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A182" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="B182" s="14">
+      <c r="B182" s="13">
         <v>1.9740000000000001E-5</v>
       </c>
       <c r="C182" s="8" t="s">
@@ -4551,13 +4587,13 @@
         <v>149</v>
       </c>
       <c r="I182" s="8"/>
-      <c r="K182" s="15"/>
-    </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K182" s="14"/>
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A183" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="B183" s="14">
+      <c r="B183" s="13">
         <v>1.021E-3</v>
       </c>
       <c r="C183" s="8" t="s">
@@ -4577,13 +4613,13 @@
         <v>151</v>
       </c>
       <c r="I183" s="8"/>
-      <c r="K183" s="15"/>
-    </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K183" s="14"/>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A184" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="B184" s="14">
+      <c r="B184" s="13">
         <v>1.7350000000000002E-5</v>
       </c>
       <c r="C184" s="8" t="s">
@@ -4603,13 +4639,13 @@
         <v>153</v>
       </c>
       <c r="I184" s="8"/>
-      <c r="K184" s="15"/>
-    </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K184" s="14"/>
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A185" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="B185" s="14">
+      <c r="B185" s="13">
         <v>3.6990000000000003E-5</v>
       </c>
       <c r="C185" s="8" t="s">
@@ -4629,9 +4665,9 @@
         <v>155</v>
       </c>
       <c r="I185" s="8"/>
-      <c r="K185" s="15"/>
-    </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K185" s="14"/>
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A186" s="8" t="s">
         <v>156</v>
       </c>
@@ -4655,9 +4691,9 @@
         <v>157</v>
       </c>
       <c r="I186" s="8"/>
-      <c r="K186" s="15"/>
-    </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K186" s="14"/>
+    </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="3"/>
@@ -4666,9 +4702,9 @@
       <c r="F187" s="2"/>
       <c r="G187" s="2"/>
       <c r="H187" s="2"/>
-      <c r="K187" s="15"/>
-    </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K187" s="14"/>
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A188" s="1" t="s">
         <v>0</v>
       </c>
@@ -4681,13 +4717,13 @@
       <c r="F188" s="8"/>
       <c r="G188" s="8"/>
       <c r="H188" s="8"/>
-      <c r="K188" s="15"/>
-    </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K188" s="14"/>
+    </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A189" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B189" s="10" t="s">
+      <c r="B189" t="s">
         <v>159</v>
       </c>
       <c r="C189" s="8"/>
@@ -4696,13 +4732,13 @@
       <c r="F189" s="8"/>
       <c r="G189" s="8"/>
       <c r="H189" s="8"/>
-      <c r="K189" s="15"/>
-    </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K189" s="14"/>
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A190" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B190" s="10" t="s">
+      <c r="B190" t="s">
         <v>4</v>
       </c>
       <c r="C190" s="8"/>
@@ -4712,7 +4748,7 @@
       <c r="G190" s="8"/>
       <c r="H190" s="8"/>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A191" s="8" t="s">
         <v>5</v>
       </c>
@@ -4726,11 +4762,11 @@
       <c r="G191" s="8"/>
       <c r="H191" s="8"/>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A192" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B192" s="10" t="s">
+      <c r="B192" t="s">
         <v>123</v>
       </c>
       <c r="C192" s="8"/>
@@ -4740,7 +4776,7 @@
       <c r="G192" s="8"/>
       <c r="H192" s="8"/>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193" s="8" t="s">
         <v>8</v>
       </c>
@@ -4754,7 +4790,7 @@
       <c r="G193" s="8"/>
       <c r="H193" s="8"/>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
         <v>10</v>
       </c>
@@ -4766,7 +4802,7 @@
       <c r="G194" s="8"/>
       <c r="H194" s="8"/>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195" s="8" t="s">
         <v>11</v>
       </c>
@@ -4792,7 +4828,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196" s="8" t="s">
         <v>123</v>
       </c>
@@ -4802,7 +4838,7 @@
       <c r="C196" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D196" s="10" t="s">
+      <c r="D196" t="s">
         <v>4</v>
       </c>
       <c r="E196" s="8" t="s">
@@ -4816,7 +4852,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A197" s="8" t="s">
         <v>124</v>
       </c>
@@ -4826,21 +4862,21 @@
       <c r="C197" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D197" s="10" t="s">
+      <c r="D197" t="s">
         <v>4</v>
       </c>
       <c r="E197" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F197" s="8"/>
-      <c r="G197" s="10" t="s">
+      <c r="G197" t="s">
         <v>20</v>
       </c>
       <c r="H197" s="8" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>55</v>
       </c>
@@ -4851,7 +4887,7 @@
       <c r="C198" t="s">
         <v>18</v>
       </c>
-      <c r="D198" s="10" t="s">
+      <c r="D198" t="s">
         <v>44</v>
       </c>
       <c r="E198" t="s">
@@ -4864,30 +4900,30 @@
         <v>43</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A199" s="10" t="s">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A199" t="s">
         <v>29</v>
       </c>
-      <c r="B199" s="18">
+      <c r="B199" s="15">
         <f>0.447/1000</f>
         <v>4.4700000000000002E-4</v>
       </c>
-      <c r="C199" s="10" t="s">
+      <c r="C199" t="s">
         <v>30</v>
       </c>
       <c r="D199" s="8"/>
-      <c r="E199" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F199" s="10" t="s">
+      <c r="E199" t="s">
+        <v>9</v>
+      </c>
+      <c r="F199" t="s">
         <v>39</v>
       </c>
-      <c r="G199" s="10" t="s">
+      <c r="G199" t="s">
         <v>31</v>
       </c>
       <c r="H199" s="8"/>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="3"/>
@@ -4897,7 +4933,7 @@
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
         <v>0</v>
       </c>
@@ -4911,11 +4947,11 @@
       <c r="G201" s="8"/>
       <c r="H201" s="8"/>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A202" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B202" s="10" t="s">
+      <c r="B202" t="s">
         <v>159</v>
       </c>
       <c r="C202" s="8"/>
@@ -4925,11 +4961,11 @@
       <c r="G202" s="8"/>
       <c r="H202" s="8"/>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A203" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B203" s="10" t="s">
+      <c r="B203" t="s">
         <v>4</v>
       </c>
       <c r="C203" s="8"/>
@@ -4939,7 +4975,7 @@
       <c r="G203" s="8"/>
       <c r="H203" s="8"/>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A204" s="8" t="s">
         <v>5</v>
       </c>
@@ -4953,11 +4989,11 @@
       <c r="G204" s="8"/>
       <c r="H204" s="8"/>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B205" s="10" t="s">
+      <c r="B205" t="s">
         <v>160</v>
       </c>
       <c r="C205" s="8"/>
@@ -4967,7 +5003,7 @@
       <c r="G205" s="8"/>
       <c r="H205" s="8"/>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206" s="8" t="s">
         <v>8</v>
       </c>
@@ -4981,7 +5017,7 @@
       <c r="G206" s="8"/>
       <c r="H206" s="8"/>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
         <v>10</v>
       </c>
@@ -4993,7 +5029,7 @@
       <c r="G207" s="8"/>
       <c r="H207" s="8"/>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208" s="8" t="s">
         <v>11</v>
       </c>
@@ -5019,7 +5055,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A209" s="8" t="s">
         <v>160</v>
       </c>
@@ -5029,7 +5065,7 @@
       <c r="C209" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D209" s="10" t="s">
+      <c r="D209" t="s">
         <v>4</v>
       </c>
       <c r="E209" s="8" t="s">
@@ -5043,7 +5079,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A210" s="8" t="s">
         <v>124</v>
       </c>
@@ -5053,21 +5089,21 @@
       <c r="C210" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D210" s="10" t="s">
+      <c r="D210" t="s">
         <v>4</v>
       </c>
       <c r="E210" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F210" s="8"/>
-      <c r="G210" s="10" t="s">
+      <c r="G210" t="s">
         <v>20</v>
       </c>
       <c r="H210" s="8" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>55</v>
       </c>
@@ -5078,7 +5114,7 @@
       <c r="C211" t="s">
         <v>18</v>
       </c>
-      <c r="D211" s="10" t="s">
+      <c r="D211" t="s">
         <v>44</v>
       </c>
       <c r="E211" t="s">
@@ -5091,30 +5127,30 @@
         <v>43</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A212" s="10" t="s">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A212" t="s">
         <v>29</v>
       </c>
-      <c r="B212" s="18">
+      <c r="B212" s="15">
         <f>0.309/1000</f>
         <v>3.0899999999999998E-4</v>
       </c>
-      <c r="C212" s="10" t="s">
+      <c r="C212" t="s">
         <v>30</v>
       </c>
       <c r="D212" s="8"/>
-      <c r="E212" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F212" s="10" t="s">
+      <c r="E212" t="s">
+        <v>9</v>
+      </c>
+      <c r="F212" t="s">
         <v>39</v>
       </c>
-      <c r="G212" s="10" t="s">
+      <c r="G212" t="s">
         <v>31</v>
       </c>
       <c r="H212" s="8"/>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="3"/>
@@ -5124,7 +5160,7 @@
       <c r="G213" s="2"/>
       <c r="H213" s="2"/>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A214" s="1" t="s">
         <v>0</v>
       </c>
@@ -5138,11 +5174,11 @@
       <c r="G214" s="8"/>
       <c r="H214" s="8"/>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A215" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B215" s="10" t="s">
+      <c r="B215" t="s">
         <v>164</v>
       </c>
       <c r="C215" s="8"/>
@@ -5152,11 +5188,11 @@
       <c r="G215" s="8"/>
       <c r="H215" s="8"/>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A216" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B216" s="10" t="s">
+      <c r="B216" t="s">
         <v>4</v>
       </c>
       <c r="C216" s="8"/>
@@ -5166,7 +5202,7 @@
       <c r="G216" s="8"/>
       <c r="H216" s="8"/>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A217" s="8" t="s">
         <v>5</v>
       </c>
@@ -5180,11 +5216,11 @@
       <c r="G217" s="8"/>
       <c r="H217" s="8"/>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A218" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B218" s="10" t="s">
+      <c r="B218" t="s">
         <v>163</v>
       </c>
       <c r="C218" s="8"/>
@@ -5194,11 +5230,11 @@
       <c r="G218" s="8"/>
       <c r="H218" s="8"/>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A219" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B219" s="10" t="s">
+      <c r="B219" t="s">
         <v>23</v>
       </c>
       <c r="C219" s="8"/>
@@ -5208,7 +5244,7 @@
       <c r="G219" s="8"/>
       <c r="H219" s="8"/>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A220" s="1" t="s">
         <v>10</v>
       </c>
@@ -5220,7 +5256,7 @@
       <c r="G220" s="8"/>
       <c r="H220" s="8"/>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A221" s="8" t="s">
         <v>11</v>
       </c>
@@ -5246,7 +5282,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A222" s="8" t="s">
         <v>163</v>
       </c>
@@ -5256,10 +5292,10 @@
       <c r="C222" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D222" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E222" s="10" t="s">
+      <c r="D222" t="s">
+        <v>4</v>
+      </c>
+      <c r="E222" t="s">
         <v>23</v>
       </c>
       <c r="F222" s="8"/>
@@ -5270,7 +5306,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>85</v>
       </c>
@@ -5280,21 +5316,21 @@
       <c r="C223" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D223" s="10" t="s">
+      <c r="D223" t="s">
         <v>4</v>
       </c>
       <c r="E223" t="s">
         <v>9</v>
       </c>
       <c r="F223" s="8"/>
-      <c r="G223" s="10" t="s">
+      <c r="G223" t="s">
         <v>20</v>
       </c>
       <c r="H223" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A224" s="8" t="s">
         <v>160</v>
       </c>
@@ -5304,21 +5340,21 @@
       <c r="C224" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D224" s="10" t="s">
+      <c r="D224" t="s">
         <v>4</v>
       </c>
       <c r="E224" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F224" s="8"/>
-      <c r="G224" s="10" t="s">
+      <c r="G224" t="s">
         <v>20</v>
       </c>
       <c r="H224" s="8" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A225" s="8" t="s">
         <v>165</v>
       </c>
@@ -5328,21 +5364,21 @@
       <c r="C225" t="s">
         <v>18</v>
       </c>
-      <c r="D225" s="10" t="s">
+      <c r="D225" t="s">
         <v>19</v>
       </c>
       <c r="E225" s="8" t="s">
         <v>23</v>
       </c>
       <c r="F225" s="8"/>
-      <c r="G225" s="10" t="s">
+      <c r="G225" t="s">
         <v>20</v>
       </c>
       <c r="H225" s="8" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A226" s="8" t="s">
         <v>161</v>
       </c>
@@ -5352,43 +5388,43 @@
       <c r="C226" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D226" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E226" s="10" t="s">
+      <c r="D226" t="s">
+        <v>4</v>
+      </c>
+      <c r="E226" t="s">
         <v>24</v>
       </c>
       <c r="F226" s="8"/>
-      <c r="G226" s="10" t="s">
+      <c r="G226" t="s">
         <v>20</v>
       </c>
       <c r="H226" s="8" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A227" s="10" t="s">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A227" t="s">
         <v>29</v>
       </c>
-      <c r="B227" s="18">
+      <c r="B227" s="15">
         <v>-6.7299999999999999E-2</v>
       </c>
-      <c r="C227" s="10" t="s">
+      <c r="C227" t="s">
         <v>30</v>
       </c>
       <c r="D227" s="8"/>
-      <c r="E227" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F227" s="10" t="s">
+      <c r="E227" t="s">
+        <v>9</v>
+      </c>
+      <c r="F227" t="s">
         <v>39</v>
       </c>
-      <c r="G227" s="10" t="s">
+      <c r="G227" t="s">
         <v>31</v>
       </c>
       <c r="H227" s="8"/>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="3"/>
@@ -5398,7 +5434,7 @@
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A229" s="1" t="s">
         <v>0</v>
       </c>
@@ -5412,11 +5448,11 @@
       <c r="G229" s="8"/>
       <c r="H229" s="8"/>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A230" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B230" s="10" t="s">
+      <c r="B230" t="s">
         <v>162</v>
       </c>
       <c r="C230" s="8"/>
@@ -5426,11 +5462,11 @@
       <c r="G230" s="8"/>
       <c r="H230" s="8"/>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A231" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B231" s="10" t="s">
+      <c r="B231" t="s">
         <v>4</v>
       </c>
       <c r="C231" s="8"/>
@@ -5440,7 +5476,7 @@
       <c r="G231" s="8"/>
       <c r="H231" s="8"/>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A232" s="8" t="s">
         <v>5</v>
       </c>
@@ -5454,11 +5490,11 @@
       <c r="G232" s="8"/>
       <c r="H232" s="8"/>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A233" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B233" s="10" t="s">
+      <c r="B233" t="s">
         <v>161</v>
       </c>
       <c r="C233" s="8"/>
@@ -5468,11 +5504,11 @@
       <c r="G233" s="8"/>
       <c r="H233" s="8"/>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A234" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B234" s="10" t="s">
+      <c r="B234" t="s">
         <v>24</v>
       </c>
       <c r="C234" s="8"/>
@@ -5482,7 +5518,7 @@
       <c r="G234" s="8"/>
       <c r="H234" s="8"/>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A235" s="1" t="s">
         <v>10</v>
       </c>
@@ -5494,7 +5530,7 @@
       <c r="G235" s="8"/>
       <c r="H235" s="8"/>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A236" s="8" t="s">
         <v>11</v>
       </c>
@@ -5520,7 +5556,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A237" s="8" t="s">
         <v>161</v>
       </c>
@@ -5530,10 +5566,10 @@
       <c r="C237" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D237" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E237" s="10" t="s">
+      <c r="D237" t="s">
+        <v>4</v>
+      </c>
+      <c r="E237" t="s">
         <v>24</v>
       </c>
       <c r="F237" s="8"/>
@@ -5544,7 +5580,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>85</v>
       </c>
@@ -5554,21 +5590,21 @@
       <c r="C238" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D238" s="10" t="s">
+      <c r="D238" t="s">
         <v>4</v>
       </c>
       <c r="E238" t="s">
         <v>9</v>
       </c>
       <c r="F238" s="8"/>
-      <c r="G238" s="10" t="s">
+      <c r="G238" t="s">
         <v>20</v>
       </c>
       <c r="H238" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A239" s="8" t="s">
         <v>160</v>
       </c>
@@ -5578,21 +5614,21 @@
       <c r="C239" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D239" s="10" t="s">
+      <c r="D239" t="s">
         <v>4</v>
       </c>
       <c r="E239" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F239" s="8"/>
-      <c r="G239" s="10" t="s">
+      <c r="G239" t="s">
         <v>20</v>
       </c>
       <c r="H239" s="8" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>55</v>
       </c>
@@ -5602,7 +5638,7 @@
       <c r="C240" t="s">
         <v>18</v>
       </c>
-      <c r="D240" s="10" t="s">
+      <c r="D240" t="s">
         <v>44</v>
       </c>
       <c r="E240" t="s">
@@ -5615,7 +5651,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A241" s="8" t="s">
         <v>163</v>
       </c>
@@ -5625,10 +5661,10 @@
       <c r="C241" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D241" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E241" s="10" t="s">
+      <c r="D241" t="s">
+        <v>4</v>
+      </c>
+      <c r="E241" t="s">
         <v>23</v>
       </c>
       <c r="F241" s="8"/>
@@ -5639,29 +5675,29 @@
         <v>163</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A242" s="10" t="s">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A242" t="s">
         <v>29</v>
       </c>
-      <c r="B242" s="18">
+      <c r="B242" s="15">
         <v>-0.36699999999999999</v>
       </c>
-      <c r="C242" s="10" t="s">
+      <c r="C242" t="s">
         <v>30</v>
       </c>
       <c r="D242" s="8"/>
-      <c r="E242" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F242" s="10" t="s">
+      <c r="E242" t="s">
+        <v>9</v>
+      </c>
+      <c r="F242" t="s">
         <v>39</v>
       </c>
-      <c r="G242" s="10" t="s">
+      <c r="G242" t="s">
         <v>31</v>
       </c>
       <c r="H242" s="8"/>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="3"/>
@@ -5671,7 +5707,7 @@
       <c r="G243" s="2"/>
       <c r="H243" s="2"/>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A244" s="1" t="s">
         <v>0</v>
       </c>
@@ -5685,7 +5721,7 @@
       <c r="G244" s="8"/>
       <c r="H244" s="8"/>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A245" s="8" t="s">
         <v>2</v>
       </c>
@@ -5699,11 +5735,11 @@
       <c r="G245" s="8"/>
       <c r="H245" s="8"/>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A246" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B246" s="10" t="s">
+      <c r="B246" t="s">
         <v>4</v>
       </c>
       <c r="C246" s="8"/>
@@ -5713,7 +5749,7 @@
       <c r="G246" s="8"/>
       <c r="H246" s="8"/>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A247" s="8" t="s">
         <v>5</v>
       </c>
@@ -5727,7 +5763,7 @@
       <c r="G247" s="8"/>
       <c r="H247" s="8"/>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A248" s="8" t="s">
         <v>6</v>
       </c>
@@ -5741,7 +5777,7 @@
       <c r="G248" s="8"/>
       <c r="H248" s="8"/>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A249" s="8" t="s">
         <v>8</v>
       </c>
@@ -5755,7 +5791,7 @@
       <c r="G249" s="8"/>
       <c r="H249" s="8"/>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A250" s="1" t="s">
         <v>10</v>
       </c>
@@ -5767,7 +5803,7 @@
       <c r="G250" s="8"/>
       <c r="H250" s="8"/>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A251" s="8" t="s">
         <v>11</v>
       </c>
@@ -5793,7 +5829,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A252" s="8" t="s">
         <v>40</v>
       </c>
@@ -5803,7 +5839,7 @@
       <c r="C252" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D252" s="10" t="s">
+      <c r="D252" t="s">
         <v>4</v>
       </c>
       <c r="E252" s="8" t="s">
@@ -5817,7 +5853,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A253" s="5" t="s">
         <v>170</v>
       </c>
@@ -5841,7 +5877,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A254" s="7" t="s">
         <v>32</v>
       </c>
@@ -5863,7 +5899,7 @@
       </c>
       <c r="H254" s="8"/>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A255" s="5" t="s">
         <v>38</v>
       </c>
@@ -5886,7 +5922,7 @@
       </c>
       <c r="H255" s="8"/>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="3"/>
@@ -5896,119 +5932,119 @@
       <c r="G256" s="2"/>
       <c r="H256" s="2"/>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A257" s="22" t="s">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A257" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B257" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="C257" s="23"/>
+      <c r="B257" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="C257" s="20"/>
       <c r="D257" s="5"/>
       <c r="E257" s="5"/>
       <c r="F257" s="5"/>
       <c r="G257" s="5"/>
       <c r="H257" s="5"/>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A258" s="22" t="s">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A258" s="19" t="s">
         <v>2</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="C258" s="23"/>
+        <v>202</v>
+      </c>
+      <c r="C258" s="20"/>
       <c r="D258" s="5"/>
       <c r="E258" s="5"/>
       <c r="F258" s="5"/>
       <c r="G258" s="5"/>
       <c r="H258" s="5"/>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A259" s="22" t="s">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A259" s="19" t="s">
         <v>3</v>
       </c>
       <c r="B259" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C259" s="23"/>
+      <c r="C259" s="20"/>
       <c r="D259" s="5"/>
       <c r="E259" s="5"/>
       <c r="F259" s="5"/>
       <c r="G259" s="5"/>
       <c r="H259" s="5"/>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A260" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B260" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="C260" s="23"/>
+      <c r="B260" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="C260" s="20"/>
       <c r="D260" s="5"/>
       <c r="E260" s="5"/>
       <c r="F260" s="5"/>
       <c r="G260" s="5"/>
       <c r="H260" s="5"/>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A261" s="22" t="s">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A261" s="19" t="s">
         <v>5</v>
       </c>
       <c r="B261" s="7">
         <v>1</v>
       </c>
-      <c r="C261" s="23"/>
-      <c r="D261" s="24"/>
+      <c r="C261" s="20"/>
+      <c r="D261" s="21"/>
       <c r="E261" s="5"/>
       <c r="F261" s="5"/>
       <c r="G261" s="5"/>
       <c r="H261" s="5"/>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A262" s="22" t="s">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A262" s="19" t="s">
         <v>8</v>
       </c>
       <c r="B262" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C262" s="23"/>
-      <c r="D262" s="24"/>
+      <c r="C262" s="20"/>
+      <c r="D262" s="21"/>
       <c r="E262" s="5"/>
       <c r="F262" s="5"/>
       <c r="G262" s="5"/>
       <c r="H262" s="5"/>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A263" s="22" t="s">
-        <v>204</v>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A263" s="19" t="s">
+        <v>203</v>
       </c>
       <c r="B263" s="5"/>
-      <c r="C263" s="23"/>
-      <c r="D263" s="24"/>
+      <c r="C263" s="20"/>
+      <c r="D263" s="21"/>
       <c r="E263" s="5"/>
       <c r="F263" s="5"/>
       <c r="G263" s="5"/>
       <c r="H263" s="5"/>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A264" s="22" t="s">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A264" s="19" t="s">
         <v>10</v>
       </c>
       <c r="B264" s="5"/>
-      <c r="C264" s="23"/>
+      <c r="C264" s="20"/>
       <c r="D264" s="5"/>
       <c r="E264" s="5"/>
       <c r="F264" s="5"/>
       <c r="G264" s="5"/>
       <c r="H264" s="5"/>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A265" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B265" s="23" t="s">
+      <c r="B265" s="20" t="s">
         <v>12</v>
       </c>
       <c r="C265" s="5" t="s">
@@ -6030,57 +6066,57 @@
         <v>6</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A266" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="B266" s="25">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A266" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="B266" s="22">
         <v>1</v>
       </c>
       <c r="C266" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D266" s="20" t="s">
+      <c r="D266" s="17" t="s">
         <v>4</v>
       </c>
       <c r="E266" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F266" s="20"/>
-      <c r="G266" s="20" t="s">
+      <c r="F266" s="17"/>
+      <c r="G266" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="H266" s="20" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A267" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="B267" s="26">
+      <c r="H266" s="17" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A267" t="s">
+        <v>47</v>
+      </c>
+      <c r="B267" s="23">
         <v>2.8998115122517001E-2</v>
       </c>
       <c r="C267" t="s">
         <v>18</v>
       </c>
-      <c r="D267" s="20" t="s">
-        <v>4</v>
+      <c r="D267" t="s">
+        <v>19</v>
       </c>
       <c r="E267" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F267" s="20"/>
-      <c r="G267" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="H267" s="5" t="s">
+      <c r="F267" s="17"/>
+      <c r="G267" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H267" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A268" s="20" t="s">
-        <v>205</v>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A268" s="17" t="s">
+        <v>204</v>
       </c>
       <c r="B268" s="6">
         <v>1.1684210526315801E-3</v>
@@ -6088,23 +6124,23 @@
       <c r="C268" t="s">
         <v>18</v>
       </c>
-      <c r="D268" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="E268" s="20" t="s">
+      <c r="D268" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="E268" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="F268" s="20"/>
-      <c r="G268" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="H268" s="21" t="s">
+      <c r="F268" s="17"/>
+      <c r="G268" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H268" s="18" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A269" s="17" t="s">
         <v>206</v>
-      </c>
-    </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A269" s="20" t="s">
-        <v>207</v>
       </c>
       <c r="B269" s="6">
         <v>2.9473684210526402E-9</v>
@@ -6112,454 +6148,841 @@
       <c r="C269" t="s">
         <v>18</v>
       </c>
-      <c r="D269" s="20" t="s">
+      <c r="D269" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="E269" s="20" t="s">
+      <c r="E269" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="F269" s="20"/>
-      <c r="G269" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="H269" s="21" t="s">
+      <c r="F269" s="17"/>
+      <c r="G269" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H269" s="18" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A270" s="17" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A270" s="20" t="s">
-        <v>209</v>
-      </c>
-      <c r="B270" s="27">
+      <c r="B270" s="24">
         <v>5.3052631578947428E-2</v>
       </c>
       <c r="C270" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D270" s="20" t="s">
+      <c r="D270" s="17" t="s">
         <v>4</v>
       </c>
       <c r="E270" t="s">
         <v>9</v>
       </c>
-      <c r="F270" s="19"/>
+      <c r="F270" s="16"/>
       <c r="G270" t="s">
         <v>20</v>
       </c>
-      <c r="H270" s="20" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H270" s="17" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>29</v>
       </c>
-      <c r="B271" s="27">
+      <c r="B271" s="24">
         <v>5.8947368421052686E-3</v>
       </c>
-      <c r="C271" s="20" t="s">
+      <c r="C271" s="17" t="s">
         <v>30</v>
       </c>
       <c r="D271" s="5"/>
       <c r="E271" t="s">
         <v>9</v>
       </c>
-      <c r="F271" s="28" t="s">
-        <v>190</v>
+      <c r="F271" s="25" t="s">
+        <v>189</v>
       </c>
       <c r="G271" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>101</v>
       </c>
-      <c r="B272" s="16">
+      <c r="B272" s="15">
         <v>2.2105263157894801E-6</v>
       </c>
-      <c r="C272" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D272" s="20"/>
-      <c r="E272" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F272" s="28" t="s">
-        <v>190</v>
+      <c r="C272" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D272" s="17"/>
+      <c r="E272" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F272" s="25" t="s">
+        <v>189</v>
       </c>
       <c r="G272" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>100</v>
       </c>
-      <c r="B273" s="16">
+      <c r="B273" s="15">
         <v>2.10526315789474E-6</v>
       </c>
-      <c r="C273" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D273" s="20"/>
-      <c r="E273" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F273" s="28" t="s">
-        <v>190</v>
+      <c r="C273" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D273" s="17"/>
+      <c r="E273" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F273" s="25" t="s">
+        <v>189</v>
       </c>
       <c r="G273" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A274" s="21" t="s">
-        <v>210</v>
-      </c>
-      <c r="B274" s="16">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A274" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="B274" s="15">
         <v>1.05263157894737E-7</v>
       </c>
-      <c r="C274" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D274" s="20"/>
-      <c r="E274" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F274" s="20" t="s">
-        <v>190</v>
+      <c r="C274" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D274" s="17"/>
+      <c r="E274" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F274" s="17" t="s">
+        <v>189</v>
       </c>
       <c r="G274" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>37</v>
       </c>
-      <c r="B275" s="16">
+      <c r="B275" s="15">
         <v>1.8842105263157901E-5</v>
       </c>
-      <c r="C275" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D275" s="20"/>
+      <c r="C275" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D275" s="17"/>
       <c r="E275" t="s">
         <v>9</v>
       </c>
-      <c r="F275" s="28" t="s">
-        <v>190</v>
+      <c r="F275" s="25" t="s">
+        <v>189</v>
       </c>
       <c r="G275" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A276" s="21" t="s">
-        <v>198</v>
-      </c>
-      <c r="B276" s="16">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A276" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="B276" s="15">
         <v>5.7894736842105305E-7</v>
       </c>
-      <c r="C276" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D276" s="20"/>
-      <c r="E276" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F276" s="28" t="s">
-        <v>190</v>
+      <c r="C276" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D276" s="17"/>
+      <c r="E276" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F276" s="25" t="s">
+        <v>189</v>
       </c>
       <c r="G276" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A277" s="21" t="s">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A277" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="B277" s="16">
+      <c r="B277" s="15">
         <v>2.1052631578947401E-7</v>
       </c>
-      <c r="C277" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D277" s="20"/>
-      <c r="E277" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F277" s="20" t="s">
-        <v>190</v>
+      <c r="C277" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D277" s="17"/>
+      <c r="E277" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F277" s="17" t="s">
+        <v>189</v>
       </c>
       <c r="G277" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A278" s="21" t="s">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A278" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="B278" s="15">
+        <v>1.05263157894737E-9</v>
+      </c>
+      <c r="C278" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D278" s="17"/>
+      <c r="E278" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F278" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="G278" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A279" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="B278" s="16">
-        <v>1.05263157894737E-9</v>
-      </c>
-      <c r="C278" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D278" s="20"/>
-      <c r="E278" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F278" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="G278" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A279" s="21" t="s">
+      <c r="B279" s="15">
+        <v>1.5789473684210501E-7</v>
+      </c>
+      <c r="C279" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D279" s="17"/>
+      <c r="E279" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F279" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="G279" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A280" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="B279" s="16">
-        <v>1.5789473684210501E-7</v>
-      </c>
-      <c r="C279" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D279" s="20"/>
-      <c r="E279" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F279" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="G279" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A280" s="21" t="s">
+      <c r="B280" s="15">
+        <v>4.2105263157894802E-7</v>
+      </c>
+      <c r="C280" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D280" s="17"/>
+      <c r="E280" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F280" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="G280" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A281" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="B281" s="15">
+        <v>1.0526315789473699E-11</v>
+      </c>
+      <c r="C281" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D281" s="17"/>
+      <c r="E281" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F281" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="G281" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A282" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="B280" s="16">
-        <v>4.2105263157894802E-7</v>
-      </c>
-      <c r="C280" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D280" s="20"/>
-      <c r="E280" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F280" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="G280" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A281" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="B281" s="16">
-        <v>1.0526315789473699E-11</v>
-      </c>
-      <c r="C281" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D281" s="20"/>
-      <c r="E281" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F281" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="G281" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A282" s="21" t="s">
+      <c r="B282" s="15">
+        <v>7.3684210526315899E-7</v>
+      </c>
+      <c r="C282" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D282" s="17"/>
+      <c r="E282" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F282" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="G282" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A283" s="18" t="s">
         <v>214</v>
-      </c>
-      <c r="B282" s="16">
-        <v>7.3684210526315899E-7</v>
-      </c>
-      <c r="C282" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D282" s="20"/>
-      <c r="E282" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F282" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="G282" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A283" s="21" t="s">
-        <v>215</v>
       </c>
       <c r="B283" s="6">
         <v>0</v>
       </c>
-      <c r="C283" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E283" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F283" s="20" t="s">
-        <v>190</v>
+      <c r="C283" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E283" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F283" s="17" t="s">
+        <v>189</v>
       </c>
       <c r="G283" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A284" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="B284" s="16">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A284" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="B284" s="15">
         <v>1.05263157894737E-7</v>
       </c>
-      <c r="C284" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E284" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F284" s="20" t="s">
-        <v>190</v>
+      <c r="C284" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E284" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F284" s="17" t="s">
+        <v>189</v>
       </c>
       <c r="G284" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A285" s="21" t="s">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A285" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="B285" s="16">
+      <c r="B285" s="15">
         <v>3.1578947368421103E-11</v>
       </c>
-      <c r="C285" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E285" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F285" s="20" t="s">
-        <v>190</v>
+      <c r="C285" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E285" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F285" s="17" t="s">
+        <v>189</v>
       </c>
       <c r="G285" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A286" s="21" t="s">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A286" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="B286" s="15">
+        <v>1.0526315789473701E-8</v>
+      </c>
+      <c r="C286" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E286" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F286" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="G286" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A287" s="18" t="s">
         <v>216</v>
       </c>
-      <c r="B286" s="16">
-        <v>1.0526315789473701E-8</v>
-      </c>
-      <c r="C286" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E286" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F286" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="G286" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A287" s="21" t="s">
+      <c r="B287" s="15">
+        <v>1.2631578947368401E-6</v>
+      </c>
+      <c r="C287" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E287" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F287" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="G287" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A288" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="B287" s="16">
-        <v>1.2631578947368401E-6</v>
-      </c>
-      <c r="C287" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E287" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F287" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="G287" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A288" s="21" t="s">
+      <c r="B288" s="15">
+        <v>2.1052631578947401E-7</v>
+      </c>
+      <c r="C288" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E288" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F288" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="G288" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A289" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="B288" s="16">
+      <c r="B289" s="15">
+        <v>2.1052631578947401E-8</v>
+      </c>
+      <c r="C289" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E289" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F289" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="G289" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A290" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="B290" s="15">
         <v>2.1052631578947401E-7</v>
       </c>
-      <c r="C288" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E288" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F288" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="G288" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A289" s="21" t="s">
-        <v>219</v>
-      </c>
-      <c r="B289" s="16">
-        <v>2.1052631578947401E-8</v>
-      </c>
-      <c r="C289" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E289" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F289" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="G289" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A290" s="21" t="s">
-        <v>220</v>
-      </c>
-      <c r="B290" s="16">
-        <v>2.1052631578947401E-7</v>
-      </c>
       <c r="C290" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E290" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F290" s="20" t="s">
-        <v>190</v>
+      <c r="E290" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F290" s="17" t="s">
+        <v>189</v>
       </c>
       <c r="G290" s="5" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A291" s="2"/>
+      <c r="B291" s="2"/>
+      <c r="C291" s="3"/>
+      <c r="D291" s="2"/>
+      <c r="E291" s="2"/>
+      <c r="F291" s="2"/>
+      <c r="G291" s="2"/>
+      <c r="H291" s="2"/>
+    </row>
+    <row r="292" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A292" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B292" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="C292" s="20"/>
+      <c r="D292" s="5"/>
+      <c r="E292" s="5"/>
+      <c r="F292" s="5"/>
+      <c r="G292" s="5"/>
+      <c r="H292" s="5"/>
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A293" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B293" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="C293" s="20"/>
+      <c r="D293" s="5"/>
+      <c r="E293" s="5"/>
+      <c r="F293" s="5"/>
+      <c r="G293" s="5"/>
+      <c r="H293" s="5"/>
+    </row>
+    <row r="294" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A294" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B294" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C294" s="20"/>
+      <c r="D294" s="5"/>
+      <c r="E294" s="5"/>
+      <c r="F294" s="5"/>
+      <c r="G294" s="5"/>
+      <c r="H294" s="5"/>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A295" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B295" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="C295" s="20"/>
+      <c r="D295" s="5"/>
+      <c r="E295" s="5"/>
+      <c r="F295" s="5"/>
+      <c r="G295" s="5"/>
+      <c r="H295" s="5"/>
+    </row>
+    <row r="296" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A296" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B296" s="7">
+        <v>1</v>
+      </c>
+      <c r="C296" s="20"/>
+      <c r="D296" s="21"/>
+      <c r="E296" s="5"/>
+      <c r="F296" s="5"/>
+      <c r="G296" s="5"/>
+      <c r="H296" s="5"/>
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A297" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B297" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C297" s="20"/>
+      <c r="D297" s="21"/>
+      <c r="E297" s="5"/>
+      <c r="F297" s="5"/>
+      <c r="G297" s="5"/>
+      <c r="H297" s="5"/>
+    </row>
+    <row r="298" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A298" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B298" s="5"/>
+      <c r="C298" s="20"/>
+      <c r="D298" s="21"/>
+      <c r="E298" s="5"/>
+      <c r="F298" s="5"/>
+      <c r="G298" s="5"/>
+      <c r="H298" s="5"/>
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A299" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B299" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C299" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D299" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E299" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F299" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G299" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H299" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A300" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="B300" s="22">
+        <v>1</v>
+      </c>
+      <c r="C300" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D300" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="E300" t="s">
+        <v>9</v>
+      </c>
+      <c r="F300" s="17"/>
+      <c r="G300" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="H300" s="17" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A301" t="s">
+        <v>55</v>
+      </c>
+      <c r="B301" s="22">
+        <v>0.38400000000000001</v>
+      </c>
+      <c r="C301" t="s">
+        <v>18</v>
+      </c>
+      <c r="D301" t="s">
+        <v>4</v>
+      </c>
+      <c r="E301" t="s">
+        <v>24</v>
+      </c>
+      <c r="F301" s="17"/>
+      <c r="G301" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H301" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A302" t="s">
+        <v>221</v>
+      </c>
+      <c r="B302" s="15">
+        <v>8.2699999999999996E-11</v>
+      </c>
+      <c r="C302" t="s">
+        <v>18</v>
+      </c>
+      <c r="D302" t="s">
+        <v>19</v>
+      </c>
+      <c r="E302" t="s">
+        <v>8</v>
+      </c>
+      <c r="G302" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H302" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A303" t="s">
+        <v>223</v>
+      </c>
+      <c r="B303" s="15">
+        <v>7.4400000000000002E-10</v>
+      </c>
+      <c r="C303" t="s">
+        <v>18</v>
+      </c>
+      <c r="D303" t="s">
+        <v>4</v>
+      </c>
+      <c r="E303" t="s">
+        <v>8</v>
+      </c>
+      <c r="G303" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H303" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A304" t="s">
+        <v>225</v>
+      </c>
+      <c r="B304" s="15">
+        <v>8.2600000000000002E-5</v>
+      </c>
+      <c r="C304" t="s">
+        <v>18</v>
+      </c>
+      <c r="D304" t="s">
+        <v>4</v>
+      </c>
+      <c r="E304" t="s">
+        <v>9</v>
+      </c>
+      <c r="G304" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H304" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A305" t="s">
+        <v>227</v>
+      </c>
+      <c r="B305" s="15">
+        <v>3.3099999999999999E-10</v>
+      </c>
+      <c r="C305" t="s">
+        <v>18</v>
+      </c>
+      <c r="D305" t="s">
+        <v>4</v>
+      </c>
+      <c r="E305" t="s">
+        <v>8</v>
+      </c>
+      <c r="G305" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H305" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A306" t="s">
+        <v>229</v>
+      </c>
+      <c r="B306" s="15">
+        <v>5.1400000000000003E-12</v>
+      </c>
+      <c r="C306" t="s">
+        <v>18</v>
+      </c>
+      <c r="D306" t="s">
+        <v>4</v>
+      </c>
+      <c r="E306" t="s">
+        <v>8</v>
+      </c>
+      <c r="G306" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H306" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A307" t="s">
+        <v>88</v>
+      </c>
+      <c r="B307" s="15">
+        <v>2.8400000000000002E-4</v>
+      </c>
+      <c r="C307" t="s">
+        <v>18</v>
+      </c>
+      <c r="D307" t="s">
+        <v>4</v>
+      </c>
+      <c r="E307" t="s">
+        <v>9</v>
+      </c>
+      <c r="G307" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H307" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A308" t="s">
+        <v>231</v>
+      </c>
+      <c r="B308" s="15">
+        <v>5.7899999999999997E-10</v>
+      </c>
+      <c r="C308" t="s">
+        <v>18</v>
+      </c>
+      <c r="D308" t="s">
+        <v>4</v>
+      </c>
+      <c r="E308" t="s">
+        <v>8</v>
+      </c>
+      <c r="G308" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H308" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A309" t="s">
+        <v>90</v>
+      </c>
+      <c r="B309" s="15">
+        <v>3.0400000000000002E-4</v>
+      </c>
+      <c r="C309" t="s">
+        <v>18</v>
+      </c>
+      <c r="D309" t="s">
+        <v>4</v>
+      </c>
+      <c r="E309" t="s">
+        <v>9</v>
+      </c>
+      <c r="G309" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H309" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A310" t="s">
+        <v>95</v>
+      </c>
+      <c r="B310" s="15">
+        <v>-2.2699999999999999E-4</v>
+      </c>
+      <c r="C310" t="s">
+        <v>18</v>
+      </c>
+      <c r="D310" t="s">
+        <v>233</v>
+      </c>
+      <c r="E310" t="s">
+        <v>9</v>
+      </c>
+      <c r="G310" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H310" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -6571,17 +6994,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD968991-55C9-4627-9323-29F50518FFEB}">
   <dimension ref="A1:H97"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="86.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="86.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6595,7 +7018,7 @@
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>2</v>
       </c>
@@ -6609,11 +7032,11 @@
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="8"/>
@@ -6623,7 +7046,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>5</v>
       </c>
@@ -6637,7 +7060,7 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
@@ -6651,7 +7074,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>8</v>
       </c>
@@ -6665,7 +7088,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -6677,7 +7100,7 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>11</v>
       </c>
@@ -6703,7 +7126,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -6713,7 +7136,7 @@
       <c r="C9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" t="s">
         <v>4</v>
       </c>
       <c r="E9" t="s">
@@ -6727,7 +7150,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>47</v>
       </c>
@@ -6737,21 +7160,21 @@
       <c r="C10" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" t="s">
         <v>19</v>
       </c>
       <c r="E10" t="s">
         <v>21</v>
       </c>
       <c r="F10" s="8"/>
-      <c r="G10" s="10" t="s">
+      <c r="G10" t="s">
         <v>20</v>
       </c>
       <c r="H10" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>48</v>
       </c>
@@ -6761,21 +7184,21 @@
       <c r="C11" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" t="s">
         <v>19</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" s="8"/>
-      <c r="G11" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" s="10" t="s">
+      <c r="G11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>49</v>
       </c>
@@ -6785,69 +7208,69 @@
       <c r="C12" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" t="s">
         <v>19</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
       </c>
       <c r="F12" s="8"/>
-      <c r="G12" s="10" t="s">
+      <c r="G12" t="s">
         <v>20</v>
       </c>
       <c r="H12" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="13">
         <v>4.0000000000000001E-10</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" t="s">
         <v>4</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" s="8"/>
-      <c r="G13" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H13" s="10" t="s">
+      <c r="G13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>172</v>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="13">
         <v>3.2499999999999999E-4</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" t="s">
         <v>4</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
       </c>
       <c r="F14" s="8"/>
-      <c r="G14" s="10" t="s">
+      <c r="G14" t="s">
         <v>20</v>
       </c>
       <c r="H14" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>85</v>
       </c>
@@ -6857,66 +7280,65 @@
       <c r="C15" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" t="s">
         <v>4</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
       </c>
       <c r="F15" s="8"/>
-      <c r="G15" s="10" t="s">
+      <c r="G15" t="s">
         <v>20</v>
       </c>
       <c r="H15" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>120</v>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="13">
         <v>-8.7600000000000002E-5</v>
       </c>
       <c r="C16" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" t="s">
         <v>19</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
       </c>
       <c r="F16" s="8"/>
-      <c r="G16" s="10" t="s">
+      <c r="G16" t="s">
         <v>20</v>
       </c>
       <c r="H16" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="17">
+      <c r="B17" s="4">
         <v>0.56200000000000006</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="10"/>
+      <c r="C17" t="s">
+        <v>30</v>
+      </c>
       <c r="E17" t="s">
         <v>21</v>
       </c>
       <c r="F17" t="s">
         <v>33</v>
       </c>
-      <c r="G17" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>97</v>
       </c>
@@ -6926,21 +7348,21 @@
       <c r="C18" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" t="s">
         <v>4</v>
       </c>
       <c r="E18" t="s">
         <v>23</v>
       </c>
       <c r="F18" s="8"/>
-      <c r="G18" s="10" t="s">
+      <c r="G18" t="s">
         <v>20</v>
       </c>
       <c r="H18" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>55</v>
       </c>
@@ -6950,7 +7372,7 @@
       <c r="C19" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" t="s">
         <v>44</v>
       </c>
       <c r="E19" t="s">
@@ -6963,14 +7385,14 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="16">
+      <c r="B20" s="15">
         <v>1.06E-3</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" t="s">
         <v>30</v>
       </c>
       <c r="E20" t="s">
@@ -6979,18 +7401,18 @@
       <c r="F20" t="s">
         <v>39</v>
       </c>
-      <c r="G20" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G20" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="16">
+      <c r="B21" s="15">
         <v>2.0100000000000001E-3</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" t="s">
         <v>30</v>
       </c>
       <c r="E21" t="s">
@@ -6999,18 +7421,18 @@
       <c r="F21" t="s">
         <v>39</v>
       </c>
-      <c r="G21" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G21" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>100</v>
       </c>
-      <c r="B22" s="16">
+      <c r="B22" s="15">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" t="s">
         <v>30</v>
       </c>
       <c r="E22" t="s">
@@ -7019,18 +7441,18 @@
       <c r="F22" t="s">
         <v>39</v>
       </c>
-      <c r="G22" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>101</v>
       </c>
-      <c r="B23" s="16">
+      <c r="B23" s="15">
         <v>4.8500000000000002E-6</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" t="s">
         <v>30</v>
       </c>
       <c r="E23" t="s">
@@ -7039,18 +7461,18 @@
       <c r="F23" t="s">
         <v>39</v>
       </c>
-      <c r="G23" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G23" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>29</v>
       </c>
       <c r="B24" s="4">
         <v>1.43</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" t="s">
         <v>30</v>
       </c>
       <c r="E24" t="s">
@@ -7059,18 +7481,18 @@
       <c r="F24" t="s">
         <v>39</v>
       </c>
-      <c r="G24" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G24" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="16">
+      <c r="B25" s="15">
         <v>1E-3</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" t="s">
         <v>30</v>
       </c>
       <c r="E25" t="s">
@@ -7079,19 +7501,19 @@
       <c r="F25" t="s">
         <v>39</v>
       </c>
-      <c r="G25" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="16">
+      <c r="B26" s="15">
         <f>149/1000</f>
         <v>0.14899999999999999</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" t="s">
         <v>30</v>
       </c>
       <c r="E26" t="s">
@@ -7100,18 +7522,18 @@
       <c r="F26" t="s">
         <v>39</v>
       </c>
-      <c r="G26" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G26" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>36</v>
       </c>
-      <c r="B27" s="16">
+      <c r="B27" s="15">
         <v>1.5099999999999999E-5</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" t="s">
         <v>30</v>
       </c>
       <c r="E27" t="s">
@@ -7120,18 +7542,18 @@
       <c r="F27" t="s">
         <v>42</v>
       </c>
-      <c r="G27" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>94</v>
       </c>
-      <c r="B28" s="16">
+      <c r="B28" s="15">
         <v>1.15E-7</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" t="s">
         <v>30</v>
       </c>
       <c r="E28" t="s">
@@ -7140,19 +7562,19 @@
       <c r="F28" t="s">
         <v>42</v>
       </c>
-      <c r="G28" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G28" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="16">
+      <c r="B29" s="15">
         <f>422/1000</f>
         <v>0.42199999999999999</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" t="s">
         <v>30</v>
       </c>
       <c r="E29" t="s">
@@ -7161,15 +7583,15 @@
       <c r="F29" t="s">
         <v>42</v>
       </c>
-      <c r="G29" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="B30" s="16">
+      <c r="B30" s="15">
         <v>-3.2499999999999999E-4</v>
       </c>
       <c r="C30" t="s">
@@ -7181,18 +7603,18 @@
       <c r="E30" t="s">
         <v>9</v>
       </c>
-      <c r="G30" s="10" t="s">
+      <c r="G30" t="s">
         <v>20</v>
       </c>
       <c r="H30" s="8" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="B31" s="14">
+      <c r="B31" s="13">
         <v>-1.56E-4</v>
       </c>
       <c r="C31" s="8" t="s">
@@ -7205,14 +7627,14 @@
         <v>21</v>
       </c>
       <c r="F31" s="8"/>
-      <c r="G31" s="10" t="s">
+      <c r="G31" t="s">
         <v>20</v>
       </c>
       <c r="H31" s="8" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="3"/>
@@ -7222,7 +7644,7 @@
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>0</v>
       </c>
@@ -7236,7 +7658,7 @@
       <c r="G33" s="8"/>
       <c r="H33" s="8"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
         <v>2</v>
       </c>
@@ -7250,11 +7672,11 @@
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B35" t="s">
         <v>4</v>
       </c>
       <c r="C35" s="8"/>
@@ -7264,7 +7686,7 @@
       <c r="G35" s="8"/>
       <c r="H35" s="8"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
         <v>5</v>
       </c>
@@ -7278,7 +7700,7 @@
       <c r="G36" s="8"/>
       <c r="H36" s="8"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="8" t="s">
         <v>6</v>
       </c>
@@ -7292,7 +7714,7 @@
       <c r="G37" s="8"/>
       <c r="H37" s="8"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="8" t="s">
         <v>8</v>
       </c>
@@ -7306,7 +7728,7 @@
       <c r="G38" s="8"/>
       <c r="H38" s="8"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>10</v>
       </c>
@@ -7318,7 +7740,7 @@
       <c r="G39" s="8"/>
       <c r="H39" s="8"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="8" t="s">
         <v>11</v>
       </c>
@@ -7344,7 +7766,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>167</v>
       </c>
@@ -7354,7 +7776,7 @@
       <c r="C41" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D41" s="10" t="s">
+      <c r="D41" t="s">
         <v>4</v>
       </c>
       <c r="E41" t="s">
@@ -7368,7 +7790,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>47</v>
       </c>
@@ -7378,21 +7800,21 @@
       <c r="C42" t="s">
         <v>18</v>
       </c>
-      <c r="D42" s="10" t="s">
+      <c r="D42" t="s">
         <v>19</v>
       </c>
       <c r="E42" t="s">
         <v>21</v>
       </c>
       <c r="F42" s="8"/>
-      <c r="G42" s="10" t="s">
+      <c r="G42" t="s">
         <v>20</v>
       </c>
       <c r="H42" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>48</v>
       </c>
@@ -7402,21 +7824,21 @@
       <c r="C43" t="s">
         <v>18</v>
       </c>
-      <c r="D43" s="10" t="s">
+      <c r="D43" t="s">
         <v>19</v>
       </c>
       <c r="E43" t="s">
         <v>9</v>
       </c>
       <c r="F43" s="8"/>
-      <c r="G43" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H43" s="10" t="s">
+      <c r="G43" t="s">
+        <v>20</v>
+      </c>
+      <c r="H43" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -7426,69 +7848,69 @@
       <c r="C44" t="s">
         <v>18</v>
       </c>
-      <c r="D44" s="10" t="s">
+      <c r="D44" t="s">
         <v>19</v>
       </c>
       <c r="E44" t="s">
         <v>9</v>
       </c>
       <c r="F44" s="8"/>
-      <c r="G44" s="10" t="s">
+      <c r="G44" t="s">
         <v>20</v>
       </c>
       <c r="H44" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>27</v>
       </c>
-      <c r="B45" s="14">
+      <c r="B45" s="13">
         <v>4.0000000000000001E-10</v>
       </c>
       <c r="C45" t="s">
         <v>18</v>
       </c>
-      <c r="D45" s="10" t="s">
+      <c r="D45" t="s">
         <v>4</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
       </c>
       <c r="F45" s="8"/>
-      <c r="G45" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H45" s="10" t="s">
+      <c r="G45" t="s">
+        <v>20</v>
+      </c>
+      <c r="H45" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>172</v>
       </c>
-      <c r="B46" s="14">
+      <c r="B46" s="13">
         <v>3.2499999999999999E-4</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D46" s="10" t="s">
+      <c r="D46" t="s">
         <v>4</v>
       </c>
       <c r="E46" t="s">
         <v>9</v>
       </c>
       <c r="F46" s="8"/>
-      <c r="G46" s="10" t="s">
+      <c r="G46" t="s">
         <v>20</v>
       </c>
       <c r="H46" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>85</v>
       </c>
@@ -7498,21 +7920,21 @@
       <c r="C47" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D47" s="10" t="s">
+      <c r="D47" t="s">
         <v>4</v>
       </c>
       <c r="E47" t="s">
         <v>9</v>
       </c>
       <c r="F47" s="8"/>
-      <c r="G47" s="10" t="s">
+      <c r="G47" t="s">
         <v>20</v>
       </c>
       <c r="H47" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="8" t="s">
         <v>123</v>
       </c>
@@ -7522,42 +7944,41 @@
       <c r="C48" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D48" s="10" t="s">
+      <c r="D48" t="s">
         <v>4</v>
       </c>
       <c r="E48" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F48" s="8"/>
-      <c r="G48" s="10" t="s">
+      <c r="G48" t="s">
         <v>20</v>
       </c>
       <c r="H48" s="8" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>32</v>
       </c>
-      <c r="B49" s="17">
+      <c r="B49" s="4">
         <v>0.57199999999999995</v>
       </c>
-      <c r="C49" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D49" s="10"/>
+      <c r="C49" t="s">
+        <v>30</v>
+      </c>
       <c r="E49" t="s">
         <v>21</v>
       </c>
       <c r="F49" t="s">
         <v>33</v>
       </c>
-      <c r="G49" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G49" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>97</v>
       </c>
@@ -7567,21 +7988,21 @@
       <c r="C50" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D50" s="10" t="s">
+      <c r="D50" t="s">
         <v>4</v>
       </c>
       <c r="E50" t="s">
         <v>23</v>
       </c>
       <c r="F50" s="8"/>
-      <c r="G50" s="10" t="s">
+      <c r="G50" t="s">
         <v>20</v>
       </c>
       <c r="H50" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
         <v>161</v>
       </c>
@@ -7591,21 +8012,21 @@
       <c r="C51" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D51" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E51" s="10" t="s">
+      <c r="D51" t="s">
+        <v>4</v>
+      </c>
+      <c r="E51" t="s">
         <v>24</v>
       </c>
       <c r="F51" s="8"/>
-      <c r="G51" s="10" t="s">
+      <c r="G51" t="s">
         <v>20</v>
       </c>
       <c r="H51" s="8" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
         <v>163</v>
       </c>
@@ -7615,28 +8036,28 @@
       <c r="C52" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D52" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E52" s="10" t="s">
+      <c r="D52" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" t="s">
         <v>23</v>
       </c>
       <c r="F52" s="8"/>
-      <c r="G52" s="10" t="s">
+      <c r="G52" t="s">
         <v>20</v>
       </c>
       <c r="H52" s="8" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>34</v>
       </c>
-      <c r="B53" s="16">
+      <c r="B53" s="15">
         <v>7.36E-4</v>
       </c>
-      <c r="C53" s="10" t="s">
+      <c r="C53" t="s">
         <v>30</v>
       </c>
       <c r="E53" t="s">
@@ -7645,18 +8066,18 @@
       <c r="F53" t="s">
         <v>39</v>
       </c>
-      <c r="G53" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G53" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>35</v>
       </c>
-      <c r="B54" s="16">
+      <c r="B54" s="15">
         <v>2.0100000000000001E-3</v>
       </c>
-      <c r="C54" s="10" t="s">
+      <c r="C54" t="s">
         <v>30</v>
       </c>
       <c r="E54" t="s">
@@ -7665,18 +8086,18 @@
       <c r="F54" t="s">
         <v>39</v>
       </c>
-      <c r="G54" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G54" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>100</v>
       </c>
-      <c r="B55" s="16">
+      <c r="B55" s="15">
         <v>8.61E-4</v>
       </c>
-      <c r="C55" s="10" t="s">
+      <c r="C55" t="s">
         <v>30</v>
       </c>
       <c r="E55" t="s">
@@ -7685,18 +8106,18 @@
       <c r="F55" t="s">
         <v>39</v>
       </c>
-      <c r="G55" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G55" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>101</v>
       </c>
-      <c r="B56" s="16">
+      <c r="B56" s="15">
         <v>7.7599999999999999E-16</v>
       </c>
-      <c r="C56" s="10" t="s">
+      <c r="C56" t="s">
         <v>30</v>
       </c>
       <c r="E56" t="s">
@@ -7705,18 +8126,18 @@
       <c r="F56" t="s">
         <v>39</v>
       </c>
-      <c r="G56" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G56" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>29</v>
       </c>
       <c r="B57" s="4">
         <v>2.6499999999999999E-2</v>
       </c>
-      <c r="C57" s="10" t="s">
+      <c r="C57" t="s">
         <v>30</v>
       </c>
       <c r="E57" t="s">
@@ -7725,18 +8146,18 @@
       <c r="F57" t="s">
         <v>39</v>
       </c>
-      <c r="G57" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G57" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>37</v>
       </c>
-      <c r="B58" s="16">
+      <c r="B58" s="15">
         <v>1E-3</v>
       </c>
-      <c r="C58" s="10" t="s">
+      <c r="C58" t="s">
         <v>30</v>
       </c>
       <c r="E58" t="s">
@@ -7745,19 +8166,19 @@
       <c r="F58" t="s">
         <v>39</v>
       </c>
-      <c r="G58" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G58" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>38</v>
       </c>
-      <c r="B59" s="16">
+      <c r="B59" s="15">
         <f>153.04/1000</f>
         <v>0.15303999999999998</v>
       </c>
-      <c r="C59" s="10" t="s">
+      <c r="C59" t="s">
         <v>30</v>
       </c>
       <c r="E59" t="s">
@@ -7766,18 +8187,18 @@
       <c r="F59" t="s">
         <v>39</v>
       </c>
-      <c r="G59" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G59" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>36</v>
       </c>
-      <c r="B60" s="16">
+      <c r="B60" s="15">
         <v>1.5099999999999999E-5</v>
       </c>
-      <c r="C60" s="10" t="s">
+      <c r="C60" t="s">
         <v>30</v>
       </c>
       <c r="E60" t="s">
@@ -7786,18 +8207,18 @@
       <c r="F60" t="s">
         <v>42</v>
       </c>
-      <c r="G60" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G60" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>94</v>
       </c>
-      <c r="B61" s="16">
+      <c r="B61" s="15">
         <v>1.15E-7</v>
       </c>
-      <c r="C61" s="10" t="s">
+      <c r="C61" t="s">
         <v>30</v>
       </c>
       <c r="E61" t="s">
@@ -7806,19 +8227,19 @@
       <c r="F61" t="s">
         <v>42</v>
       </c>
-      <c r="G61" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G61" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>38</v>
       </c>
-      <c r="B62" s="16">
+      <c r="B62" s="15">
         <f>419/1000</f>
         <v>0.41899999999999998</v>
       </c>
-      <c r="C62" s="10" t="s">
+      <c r="C62" t="s">
         <v>30</v>
       </c>
       <c r="E62" t="s">
@@ -7827,15 +8248,15 @@
       <c r="F62" t="s">
         <v>42</v>
       </c>
-      <c r="G62" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G62" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="B63" s="16">
+      <c r="B63" s="15">
         <v>-3.2499999999999999E-4</v>
       </c>
       <c r="C63" t="s">
@@ -7847,18 +8268,18 @@
       <c r="E63" t="s">
         <v>9</v>
       </c>
-      <c r="G63" s="10" t="s">
+      <c r="G63" t="s">
         <v>20</v>
       </c>
       <c r="H63" s="8" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="B64" s="14">
+      <c r="B64" s="13">
         <v>-1.56E-4</v>
       </c>
       <c r="C64" s="8" t="s">
@@ -7871,14 +8292,14 @@
         <v>21</v>
       </c>
       <c r="F64" s="8"/>
-      <c r="G64" s="10" t="s">
+      <c r="G64" t="s">
         <v>20</v>
       </c>
       <c r="H64" s="8" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="3"/>
@@ -7888,7 +8309,7 @@
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>0</v>
       </c>
@@ -7902,7 +8323,7 @@
       <c r="G66" s="8"/>
       <c r="H66" s="8"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="8" t="s">
         <v>2</v>
       </c>
@@ -7916,11 +8337,11 @@
       <c r="G67" s="8"/>
       <c r="H67" s="8"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B68" s="10" t="s">
+      <c r="B68" t="s">
         <v>4</v>
       </c>
       <c r="C68" s="8"/>
@@ -7930,7 +8351,7 @@
       <c r="G68" s="8"/>
       <c r="H68" s="8"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="8" t="s">
         <v>5</v>
       </c>
@@ -7944,7 +8365,7 @@
       <c r="G69" s="8"/>
       <c r="H69" s="8"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="8" t="s">
         <v>6</v>
       </c>
@@ -7958,7 +8379,7 @@
       <c r="G70" s="8"/>
       <c r="H70" s="8"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="8" t="s">
         <v>8</v>
       </c>
@@ -7972,7 +8393,7 @@
       <c r="G71" s="8"/>
       <c r="H71" s="8"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>10</v>
       </c>
@@ -7984,7 +8405,7 @@
       <c r="G72" s="8"/>
       <c r="H72" s="8"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="8" t="s">
         <v>11</v>
       </c>
@@ -8010,7 +8431,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>173</v>
       </c>
@@ -8020,7 +8441,7 @@
       <c r="C74" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D74" s="10" t="s">
+      <c r="D74" t="s">
         <v>4</v>
       </c>
       <c r="E74" t="s">
@@ -8034,7 +8455,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="8" t="s">
         <v>40</v>
       </c>
@@ -8044,91 +8465,89 @@
       <c r="C75" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D75" s="10" t="s">
+      <c r="D75" t="s">
         <v>4</v>
       </c>
       <c r="E75" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F75" s="8"/>
-      <c r="G75" s="10" t="s">
+      <c r="G75" t="s">
         <v>20</v>
       </c>
       <c r="H75" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>78</v>
       </c>
-      <c r="B76" s="14">
+      <c r="B76" s="13">
         <v>5.5099999999999998E-5</v>
       </c>
       <c r="C76" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D76" s="10" t="s">
+      <c r="D76" t="s">
         <v>4</v>
       </c>
       <c r="E76" t="s">
         <v>9</v>
       </c>
       <c r="F76" s="8"/>
-      <c r="G76" s="10" t="s">
+      <c r="G76" t="s">
         <v>20</v>
       </c>
       <c r="H76" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>27</v>
       </c>
-      <c r="B77" s="14">
+      <c r="B77" s="13">
         <v>3.29E-10</v>
       </c>
       <c r="C77" t="s">
         <v>18</v>
       </c>
-      <c r="D77" s="10" t="s">
+      <c r="D77" t="s">
         <v>4</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
       </c>
       <c r="F77" s="8"/>
-      <c r="G77" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H77" s="10" t="s">
+      <c r="G77" t="s">
+        <v>20</v>
+      </c>
+      <c r="H77" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>32</v>
       </c>
-      <c r="B78" s="17">
+      <c r="B78" s="4">
         <v>0.14899999999999999</v>
       </c>
-      <c r="C78" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D78" s="10"/>
+      <c r="C78" t="s">
+        <v>30</v>
+      </c>
       <c r="E78" t="s">
         <v>21</v>
       </c>
       <c r="F78" t="s">
         <v>33</v>
       </c>
-      <c r="G78" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H78" s="10"/>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G78" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>55</v>
       </c>
@@ -8138,7 +8557,7 @@
       <c r="C79" t="s">
         <v>18</v>
       </c>
-      <c r="D79" s="10" t="s">
+      <c r="D79" t="s">
         <v>44</v>
       </c>
       <c r="E79" t="s">
@@ -8151,14 +8570,14 @@
         <v>43</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>34</v>
       </c>
-      <c r="B80" s="16">
+      <c r="B80" s="15">
         <v>7.67E-4</v>
       </c>
-      <c r="C80" s="10" t="s">
+      <c r="C80" t="s">
         <v>30</v>
       </c>
       <c r="E80" t="s">
@@ -8167,18 +8586,18 @@
       <c r="F80" t="s">
         <v>39</v>
       </c>
-      <c r="G80" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G80" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>35</v>
       </c>
-      <c r="B81" s="16">
+      <c r="B81" s="15">
         <v>1.6299999999999999E-3</v>
       </c>
-      <c r="C81" s="10" t="s">
+      <c r="C81" t="s">
         <v>30</v>
       </c>
       <c r="E81" t="s">
@@ -8187,18 +8606,18 @@
       <c r="F81" t="s">
         <v>39</v>
       </c>
-      <c r="G81" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G81" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>37</v>
       </c>
-      <c r="B82" s="16">
+      <c r="B82" s="15">
         <v>1E-3</v>
       </c>
-      <c r="C82" s="10" t="s">
+      <c r="C82" t="s">
         <v>30</v>
       </c>
       <c r="E82" t="s">
@@ -8207,19 +8626,19 @@
       <c r="F82" t="s">
         <v>39</v>
       </c>
-      <c r="G82" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G82" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>38</v>
       </c>
-      <c r="B83" s="16">
+      <c r="B83" s="15">
         <f>47.6/1000</f>
         <v>4.7600000000000003E-2</v>
       </c>
-      <c r="C83" s="10" t="s">
+      <c r="C83" t="s">
         <v>30</v>
       </c>
       <c r="E83" t="s">
@@ -8228,19 +8647,19 @@
       <c r="F83" t="s">
         <v>39</v>
       </c>
-      <c r="G83" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G83" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>38</v>
       </c>
-      <c r="B84" s="16">
+      <c r="B84" s="15">
         <f>101/1000</f>
         <v>0.10100000000000001</v>
       </c>
-      <c r="C84" s="10" t="s">
+      <c r="C84" t="s">
         <v>30</v>
       </c>
       <c r="E84" t="s">
@@ -8249,15 +8668,15 @@
       <c r="F84" t="s">
         <v>42</v>
       </c>
-      <c r="G84" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G84" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="B85" s="16">
+      <c r="B85" s="15">
         <v>-5.5099999999999998E-5</v>
       </c>
       <c r="C85" t="s">
@@ -8269,75 +8688,53 @@
       <c r="E85" t="s">
         <v>9</v>
       </c>
-      <c r="G85" s="10" t="s">
+      <c r="G85" t="s">
         <v>20</v>
       </c>
       <c r="H85" s="8" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B86" s="16"/>
-      <c r="C86" s="10"/>
-      <c r="G86" s="10"/>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B87" s="16"/>
-      <c r="C87" s="10"/>
-      <c r="G87" s="10"/>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B88" s="16"/>
-      <c r="C88" s="10"/>
-      <c r="G88" s="10"/>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B89" s="16"/>
-      <c r="C89" s="10"/>
-      <c r="G89" s="10"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B86" s="15"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B87" s="15"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B88" s="15"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B89" s="15"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B90" s="4"/>
-      <c r="C90" s="10"/>
-      <c r="G90" s="10"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B91" s="16"/>
-      <c r="C91" s="10"/>
-      <c r="G91" s="10"/>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B92" s="16"/>
-      <c r="C92" s="10"/>
-      <c r="G92" s="10"/>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B93" s="16"/>
-      <c r="C93" s="10"/>
-      <c r="G93" s="10"/>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B94" s="16"/>
-      <c r="C94" s="10"/>
-      <c r="G94" s="10"/>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B95" s="16"/>
-      <c r="C95" s="10"/>
-      <c r="G95" s="10"/>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B96" s="16"/>
-      <c r="G96" s="10"/>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B91" s="15"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B92" s="15"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B93" s="15"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B94" s="15"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B95" s="15"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B96" s="15"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="8"/>
-      <c r="B97" s="14"/>
+      <c r="B97" s="13"/>
       <c r="C97" s="8"/>
       <c r="D97" s="8"/>
       <c r="E97" s="8"/>
       <c r="F97" s="8"/>
-      <c r="G97" s="10"/>
       <c r="H97" s="8"/>
     </row>
   </sheetData>
@@ -8349,17 +8746,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20D067F8-C305-44D3-8E28-CF1FDCAD7A72}">
   <dimension ref="A1:H75"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="86.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="86.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="33.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8373,7 +8770,7 @@
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>2</v>
       </c>
@@ -8387,11 +8784,11 @@
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="8"/>
@@ -8401,7 +8798,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>5</v>
       </c>
@@ -8415,7 +8812,7 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
@@ -8429,7 +8826,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>8</v>
       </c>
@@ -8443,7 +8840,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -8455,7 +8852,7 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>11</v>
       </c>
@@ -8481,7 +8878,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>174</v>
       </c>
@@ -8491,7 +8888,7 @@
       <c r="C9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" t="s">
         <v>4</v>
       </c>
       <c r="E9" t="s">
@@ -8505,7 +8902,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>47</v>
       </c>
@@ -8515,21 +8912,21 @@
       <c r="C10" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" t="s">
         <v>19</v>
       </c>
       <c r="E10" t="s">
         <v>21</v>
       </c>
       <c r="F10" s="8"/>
-      <c r="G10" s="10" t="s">
+      <c r="G10" t="s">
         <v>20</v>
       </c>
       <c r="H10" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>165</v>
       </c>
@@ -8539,21 +8936,21 @@
       <c r="C11" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" t="s">
         <v>19</v>
       </c>
       <c r="E11" t="s">
         <v>23</v>
       </c>
       <c r="F11" s="8"/>
-      <c r="G11" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" s="10" t="s">
+      <c r="G11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>55</v>
       </c>
@@ -8563,560 +8960,551 @@
       <c r="C12" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" t="s">
         <v>44</v>
       </c>
       <c r="E12" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" t="s">
         <v>20</v>
       </c>
       <c r="H12" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>178</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="13">
         <v>3.0000000000000001E-5</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="10" t="s">
+      <c r="D13" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" t="s">
         <v>9</v>
       </c>
       <c r="F13" s="8"/>
-      <c r="G13" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H13" s="10" t="s">
+      <c r="G13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>180</v>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="13">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="C14" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="10" t="s">
+      <c r="D14" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" t="s">
         <v>9</v>
       </c>
       <c r="F14" s="8"/>
-      <c r="G14" s="10" t="s">
+      <c r="G14" t="s">
         <v>20</v>
       </c>
       <c r="H14" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>73</v>
       </c>
-      <c r="B15" s="14">
+      <c r="B15" s="13">
         <v>9.0000000000000006E-5</v>
       </c>
       <c r="C15" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="10" t="s">
+      <c r="D15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" t="s">
         <v>9</v>
       </c>
       <c r="F15" s="8"/>
-      <c r="G15" s="10" t="s">
+      <c r="G15" t="s">
         <v>20</v>
       </c>
       <c r="H15" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>182</v>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="13">
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="C16" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E16" s="10" t="s">
+      <c r="D16" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" t="s">
         <v>9</v>
       </c>
       <c r="F16" s="8"/>
-      <c r="G16" s="10" t="s">
+      <c r="G16" t="s">
         <v>20</v>
       </c>
       <c r="H16" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>49</v>
       </c>
-      <c r="B17" s="17">
+      <c r="B17" s="4">
         <f>0.2+0.00071996+0.64928</f>
         <v>0.84999996</v>
       </c>
       <c r="C17" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G17" s="10" t="s">
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" t="s">
         <v>20</v>
       </c>
       <c r="H17" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>183</v>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="13">
         <f>0.00020525+0.000034749</f>
         <v>2.3999900000000002E-4</v>
       </c>
       <c r="C18" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" t="s">
         <v>19</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" t="s">
         <v>9</v>
       </c>
       <c r="F18" s="8"/>
-      <c r="G18" s="10" t="s">
+      <c r="G18" t="s">
         <v>20</v>
       </c>
       <c r="H18" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>184</v>
       </c>
-      <c r="B19" s="14">
+      <c r="B19" s="13">
         <v>3.7199999999999998E-11</v>
       </c>
       <c r="C19" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E19" s="10" t="s">
+      <c r="D19" t="s">
+        <v>4</v>
+      </c>
+      <c r="E19" t="s">
         <v>8</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" t="s">
         <v>20</v>
       </c>
       <c r="H19" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>100</v>
       </c>
-      <c r="B20" s="14">
+      <c r="B20" s="13">
         <v>9.7999999999999997E-4</v>
       </c>
-      <c r="C20" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" s="10"/>
-      <c r="E20" s="20" t="s">
+      <c r="C20" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="17" t="s">
         <v>9</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+        <v>189</v>
+      </c>
+      <c r="G20" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="14">
+      <c r="B21" s="13">
         <v>8.1600000000000006E-3</v>
       </c>
-      <c r="C21" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" s="10"/>
+      <c r="C21" s="17" t="s">
+        <v>30</v>
+      </c>
       <c r="E21" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G21" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G21" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>191</v>
-      </c>
-      <c r="B22" s="14">
+        <v>190</v>
+      </c>
+      <c r="B22" s="13">
         <v>1.9999999999999999E-6</v>
       </c>
-      <c r="C22" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="10"/>
+      <c r="C22" s="17" t="s">
+        <v>30</v>
+      </c>
       <c r="E22" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="G22" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="14">
+      <c r="B23" s="13">
         <v>1.4999999999999999E-4</v>
       </c>
-      <c r="C23" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" s="10"/>
+      <c r="C23" s="17" t="s">
+        <v>30</v>
+      </c>
       <c r="E23" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+        <v>189</v>
+      </c>
+      <c r="G23" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="14">
+      <c r="B24" s="13">
         <v>5.67375E-3</v>
       </c>
-      <c r="C24" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D24" s="10"/>
+      <c r="C24" s="17" t="s">
+        <v>30</v>
+      </c>
       <c r="E24" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="G24" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G24" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>192</v>
-      </c>
-      <c r="B25" s="14">
+        <v>191</v>
+      </c>
+      <c r="B25" s="13">
         <v>1.8000000000000001E-4</v>
       </c>
-      <c r="C25" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D25" s="10"/>
+      <c r="C25" s="17" t="s">
+        <v>30</v>
+      </c>
       <c r="E25" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="G25" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>193</v>
-      </c>
-      <c r="B26" s="16">
+        <v>192</v>
+      </c>
+      <c r="B26" s="15">
         <v>3.0000000000000001E-5</v>
       </c>
-      <c r="C26" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D26" s="10"/>
+      <c r="C26" s="17" t="s">
+        <v>30</v>
+      </c>
       <c r="E26" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="G26" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G26" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>193</v>
+      </c>
+      <c r="B27" s="15">
+        <v>2.4000000000000001E-4</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
         <v>194</v>
       </c>
-      <c r="B27" s="16">
-        <v>2.4000000000000001E-4</v>
-      </c>
-      <c r="C27" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D27" s="10"/>
-      <c r="E27" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" s="20" t="s">
+      <c r="B28" s="15">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="G27" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>195</v>
-      </c>
-      <c r="B28" s="16">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="C28" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D28" s="10"/>
-      <c r="E28" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="G28" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G28" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>193</v>
-      </c>
-      <c r="B29" s="16">
+        <v>192</v>
+      </c>
+      <c r="B29" s="15">
         <v>5.2999999999999998E-4</v>
       </c>
-      <c r="C29" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E29" s="20" t="s">
+      <c r="C29" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E29" s="17" t="s">
         <v>9</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+        <v>189</v>
+      </c>
+      <c r="G29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>38</v>
       </c>
       <c r="B30" s="4">
         <v>3.3362499999999998E-3</v>
       </c>
-      <c r="C30" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E30" s="20" t="s">
+      <c r="C30" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="20" t="s">
+      <c r="F30" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G30" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
+        <v>195</v>
+      </c>
+      <c r="B31" s="15">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
         <v>196</v>
       </c>
-      <c r="B31" s="16">
-        <v>2.0000000000000002E-5</v>
-      </c>
-      <c r="C31" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E31" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" s="20" t="s">
+      <c r="B32" s="15">
+        <v>2.4000000000000001E-4</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="G31" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="G32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
         <v>197</v>
       </c>
-      <c r="B32" s="16">
-        <v>2.4000000000000001E-4</v>
-      </c>
-      <c r="C32" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E32" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" s="20" t="s">
+      <c r="B33" s="15">
+        <v>1.38E-5</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="G33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>198</v>
+      </c>
+      <c r="B34" s="15">
+        <v>1E-4</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="G32" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>198</v>
-      </c>
-      <c r="B33" s="16">
-        <v>1.38E-5</v>
-      </c>
-      <c r="C33" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E33" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="G34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
         <v>199</v>
       </c>
-      <c r="B34" s="16">
-        <v>1E-4</v>
-      </c>
-      <c r="C34" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E34" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" s="20" t="s">
+      <c r="B35" s="15">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="G34" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="G35" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="B35" s="16">
+      <c r="B36" s="15">
+        <v>4.8999999999999998E-4</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G36" t="s">
+        <v>31</v>
+      </c>
+      <c r="H36" s="8"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="B37" s="13">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="C35" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E35" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" s="20" t="s">
+      <c r="C37" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D37" s="8"/>
+      <c r="E37" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="G35" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="B36" s="16">
-        <v>4.8999999999999998E-4</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E36" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="G36" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H36" s="8"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="B37" s="14">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="C37" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D37" s="8"/>
-      <c r="E37" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="G37" s="10" t="s">
+      <c r="G37" t="s">
         <v>31</v>
       </c>
       <c r="H37" s="8"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="3"/>
@@ -9126,7 +9514,7 @@
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>0</v>
       </c>
@@ -9140,12 +9528,12 @@
       <c r="G39" s="8"/>
       <c r="H39" s="8"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B40" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
@@ -9154,11 +9542,11 @@
       <c r="G40" s="8"/>
       <c r="H40" s="8"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B41" s="10" t="s">
+      <c r="B41" t="s">
         <v>4</v>
       </c>
       <c r="C41" s="8"/>
@@ -9168,7 +9556,7 @@
       <c r="G41" s="8"/>
       <c r="H41" s="8"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="8" t="s">
         <v>5</v>
       </c>
@@ -9182,7 +9570,7 @@
       <c r="G42" s="8"/>
       <c r="H42" s="8"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="8" t="s">
         <v>6</v>
       </c>
@@ -9196,7 +9584,7 @@
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
         <v>8</v>
       </c>
@@ -9210,7 +9598,7 @@
       <c r="G44" s="8"/>
       <c r="H44" s="8"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>10</v>
       </c>
@@ -9222,7 +9610,7 @@
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="8" t="s">
         <v>11</v>
       </c>
@@ -9248,7 +9636,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>177</v>
       </c>
@@ -9258,7 +9646,7 @@
       <c r="C47" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D47" s="10" t="s">
+      <c r="D47" t="s">
         <v>4</v>
       </c>
       <c r="E47" t="s">
@@ -9272,7 +9660,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>47</v>
       </c>
@@ -9282,45 +9670,45 @@
       <c r="C48" t="s">
         <v>18</v>
       </c>
-      <c r="D48" s="10" t="s">
+      <c r="D48" t="s">
         <v>19</v>
       </c>
       <c r="E48" t="s">
         <v>21</v>
       </c>
       <c r="F48" s="8"/>
-      <c r="G48" s="10" t="s">
+      <c r="G48" t="s">
         <v>20</v>
       </c>
       <c r="H48" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="B49" s="25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A49" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="B49" s="22">
         <v>6.93</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D49" s="20" t="s">
+      <c r="D49" s="17" t="s">
         <v>4</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F49" s="20"/>
-      <c r="G49" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H49" s="20" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F49" s="17"/>
+      <c r="G49" t="s">
+        <v>20</v>
+      </c>
+      <c r="H49" s="17" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>55</v>
       </c>
@@ -9330,555 +9718,546 @@
       <c r="C50" t="s">
         <v>18</v>
       </c>
-      <c r="D50" s="10" t="s">
+      <c r="D50" t="s">
         <v>44</v>
       </c>
       <c r="E50" t="s">
         <v>24</v>
       </c>
-      <c r="G50" s="10" t="s">
+      <c r="G50" t="s">
         <v>20</v>
       </c>
       <c r="H50" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>178</v>
       </c>
-      <c r="B51" s="14">
+      <c r="B51" s="13">
         <v>3.0000000000000001E-5</v>
       </c>
       <c r="C51" t="s">
         <v>18</v>
       </c>
-      <c r="D51" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E51" s="10" t="s">
+      <c r="D51" t="s">
+        <v>4</v>
+      </c>
+      <c r="E51" t="s">
         <v>9</v>
       </c>
       <c r="F51" s="8"/>
-      <c r="G51" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H51" s="10" t="s">
+      <c r="G51" t="s">
+        <v>20</v>
+      </c>
+      <c r="H51" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>180</v>
       </c>
-      <c r="B52" s="14">
+      <c r="B52" s="13">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="C52" t="s">
         <v>18</v>
       </c>
-      <c r="D52" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E52" s="10" t="s">
+      <c r="D52" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" t="s">
         <v>9</v>
       </c>
       <c r="F52" s="8"/>
-      <c r="G52" s="10" t="s">
+      <c r="G52" t="s">
         <v>20</v>
       </c>
       <c r="H52" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>73</v>
       </c>
-      <c r="B53" s="14">
+      <c r="B53" s="13">
         <v>9.0000000000000006E-5</v>
       </c>
       <c r="C53" t="s">
         <v>18</v>
       </c>
-      <c r="D53" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E53" s="10" t="s">
+      <c r="D53" t="s">
+        <v>4</v>
+      </c>
+      <c r="E53" t="s">
         <v>9</v>
       </c>
       <c r="F53" s="8"/>
-      <c r="G53" s="10" t="s">
+      <c r="G53" t="s">
         <v>20</v>
       </c>
       <c r="H53" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>182</v>
       </c>
-      <c r="B54" s="14">
+      <c r="B54" s="13">
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="C54" t="s">
         <v>18</v>
       </c>
-      <c r="D54" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E54" s="10" t="s">
+      <c r="D54" t="s">
+        <v>4</v>
+      </c>
+      <c r="E54" t="s">
         <v>9</v>
       </c>
       <c r="F54" s="8"/>
-      <c r="G54" s="10" t="s">
+      <c r="G54" t="s">
         <v>20</v>
       </c>
       <c r="H54" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>49</v>
       </c>
-      <c r="B55" s="17">
+      <c r="B55" s="4">
         <f>0.2+0.00071996+0.64928</f>
         <v>0.84999996</v>
       </c>
       <c r="C55" t="s">
         <v>18</v>
       </c>
-      <c r="D55" s="10" t="s">
+      <c r="D55" t="s">
         <v>19</v>
       </c>
-      <c r="E55" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G55" s="10" t="s">
+      <c r="E55" t="s">
+        <v>9</v>
+      </c>
+      <c r="G55" t="s">
         <v>20</v>
       </c>
       <c r="H55" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>183</v>
       </c>
-      <c r="B56" s="14">
+      <c r="B56" s="13">
         <f>0.00020525+0.000034749</f>
         <v>2.3999900000000002E-4</v>
       </c>
       <c r="C56" t="s">
         <v>18</v>
       </c>
-      <c r="D56" s="10" t="s">
+      <c r="D56" t="s">
         <v>19</v>
       </c>
-      <c r="E56" s="10" t="s">
+      <c r="E56" t="s">
         <v>9</v>
       </c>
       <c r="F56" s="8"/>
-      <c r="G56" s="10" t="s">
+      <c r="G56" t="s">
         <v>20</v>
       </c>
       <c r="H56" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>184</v>
       </c>
-      <c r="B57" s="14">
+      <c r="B57" s="13">
         <v>3.7199999999999998E-11</v>
       </c>
       <c r="C57" t="s">
         <v>18</v>
       </c>
-      <c r="D57" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E57" s="10" t="s">
+      <c r="D57" t="s">
+        <v>4</v>
+      </c>
+      <c r="E57" t="s">
         <v>8</v>
       </c>
-      <c r="G57" s="10" t="s">
+      <c r="G57" t="s">
         <v>20</v>
       </c>
       <c r="H57" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>100</v>
       </c>
-      <c r="B58" s="14">
+      <c r="B58" s="13">
         <v>9.7999999999999997E-4</v>
       </c>
-      <c r="C58" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D58" s="10"/>
-      <c r="E58" s="20" t="s">
+      <c r="C58" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E58" s="17" t="s">
         <v>9</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="G58" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+        <v>189</v>
+      </c>
+      <c r="G58" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>32</v>
       </c>
-      <c r="B59" s="14">
+      <c r="B59" s="13">
         <v>8.1600000000000006E-3</v>
       </c>
-      <c r="C59" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D59" s="10"/>
+      <c r="C59" s="17" t="s">
+        <v>30</v>
+      </c>
       <c r="E59" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G59" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G59" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>191</v>
-      </c>
-      <c r="B60" s="14">
+        <v>190</v>
+      </c>
+      <c r="B60" s="13">
         <v>1.9999999999999999E-6</v>
       </c>
-      <c r="C60" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D60" s="10"/>
+      <c r="C60" s="17" t="s">
+        <v>30</v>
+      </c>
       <c r="E60" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F60" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="G60" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G60" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>37</v>
       </c>
-      <c r="B61" s="14">
+      <c r="B61" s="13">
         <v>1.4999999999999999E-4</v>
       </c>
-      <c r="C61" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D61" s="10"/>
+      <c r="C61" s="17" t="s">
+        <v>30</v>
+      </c>
       <c r="E61" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="G61" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+        <v>189</v>
+      </c>
+      <c r="G61" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>38</v>
       </c>
-      <c r="B62" s="14">
+      <c r="B62" s="13">
         <v>5.67375E-3</v>
       </c>
-      <c r="C62" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D62" s="10"/>
+      <c r="C62" s="17" t="s">
+        <v>30</v>
+      </c>
       <c r="E62" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F62" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="G62" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G62" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>192</v>
-      </c>
-      <c r="B63" s="14">
+        <v>191</v>
+      </c>
+      <c r="B63" s="13">
         <v>1.8000000000000001E-4</v>
       </c>
-      <c r="C63" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D63" s="10"/>
+      <c r="C63" s="17" t="s">
+        <v>30</v>
+      </c>
       <c r="E63" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="G63" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G63" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>193</v>
-      </c>
-      <c r="B64" s="16">
+        <v>192</v>
+      </c>
+      <c r="B64" s="15">
         <v>3.0000000000000001E-5</v>
       </c>
-      <c r="C64" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D64" s="10"/>
+      <c r="C64" s="17" t="s">
+        <v>30</v>
+      </c>
       <c r="E64" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="G64" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G64" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
+        <v>193</v>
+      </c>
+      <c r="B65" s="15">
+        <v>2.4000000000000001E-4</v>
+      </c>
+      <c r="C65" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E65" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F65" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G65" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
         <v>194</v>
       </c>
-      <c r="B65" s="16">
-        <v>2.4000000000000001E-4</v>
-      </c>
-      <c r="C65" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D65" s="10"/>
-      <c r="E65" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F65" s="20" t="s">
+      <c r="B66" s="15">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="C66" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E66" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F66" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="G65" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>195</v>
-      </c>
-      <c r="B66" s="16">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="C66" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D66" s="10"/>
-      <c r="E66" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F66" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="G66" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G66" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>193</v>
-      </c>
-      <c r="B67" s="16">
+        <v>192</v>
+      </c>
+      <c r="B67" s="15">
         <v>5.2999999999999998E-4</v>
       </c>
-      <c r="C67" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E67" s="20" t="s">
+      <c r="C67" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E67" s="17" t="s">
         <v>9</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="G67" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+        <v>189</v>
+      </c>
+      <c r="G67" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>38</v>
       </c>
       <c r="B68" s="4">
         <v>3.3362499999999998E-3</v>
       </c>
-      <c r="C68" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E68" s="20" t="s">
+      <c r="C68" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E68" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="F68" s="20" t="s">
+      <c r="F68" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="G68" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G68" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
+        <v>195</v>
+      </c>
+      <c r="B69" s="15">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="C69" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E69" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F69" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G69" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
         <v>196</v>
       </c>
-      <c r="B69" s="16">
-        <v>2.0000000000000002E-5</v>
-      </c>
-      <c r="C69" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E69" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F69" s="20" t="s">
+      <c r="B70" s="15">
+        <v>2.4000000000000001E-4</v>
+      </c>
+      <c r="C70" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E70" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F70" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="G69" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+      <c r="G70" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
         <v>197</v>
       </c>
-      <c r="B70" s="16">
-        <v>2.4000000000000001E-4</v>
-      </c>
-      <c r="C70" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E70" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F70" s="20" t="s">
+      <c r="B71" s="15">
+        <v>1.38E-5</v>
+      </c>
+      <c r="C71" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E71" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="G71" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>198</v>
+      </c>
+      <c r="B72" s="15">
+        <v>1E-4</v>
+      </c>
+      <c r="C72" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E72" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F72" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="G70" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>198</v>
-      </c>
-      <c r="B71" s="16">
-        <v>1.38E-5</v>
-      </c>
-      <c r="C71" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E71" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F71" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="G71" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+      <c r="G72" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
         <v>199</v>
       </c>
-      <c r="B72" s="16">
-        <v>1E-4</v>
-      </c>
-      <c r="C72" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E72" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F72" s="20" t="s">
+      <c r="B73" s="15">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="C73" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E73" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F73" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="G72" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+      <c r="G73" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A74" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="B73" s="16">
+      <c r="B74" s="15">
+        <v>4.8999999999999998E-4</v>
+      </c>
+      <c r="C74" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E74" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F74" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G74" t="s">
+        <v>31</v>
+      </c>
+      <c r="H74" s="8"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A75" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="B75" s="13">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="C73" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E73" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F73" s="20" t="s">
+      <c r="C75" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D75" s="8"/>
+      <c r="E75" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F75" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="G73" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A74" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="B74" s="16">
-        <v>4.8999999999999998E-4</v>
-      </c>
-      <c r="C74" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E74" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F74" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="G74" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H74" s="8"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="B75" s="14">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="C75" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D75" s="8"/>
-      <c r="E75" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F75" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="G75" s="10" t="s">
+      <c r="G75" t="s">
         <v>31</v>
       </c>
       <c r="H75" s="8"/>

--- a/Raw data/lci-Abhi image SSP2-Base 2020 new.xlsx
+++ b/Raw data/lci-Abhi image SSP2-Base 2020 new.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Prospective LCA\Raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00B4C532-7DCD-47D2-800A-7D86D965B00E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FEA5E9C-E374-44EB-8C8B-63CF9D01C813}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17280" windowHeight="8088" activeTab="2" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17280" windowHeight="8085" activeTab="3" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
   </bookViews>
   <sheets>
     <sheet name="Utilities" sheetId="6" r:id="rId1"/>
     <sheet name="Ammonia" sheetId="5" r:id="rId2"/>
     <sheet name="Methanol" sheetId="7" r:id="rId3"/>
+    <sheet name="Ethylene" sheetId="8" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1914" uniqueCount="229">
   <si>
     <t>Activity</t>
   </si>
@@ -693,6 +694,27 @@
   </si>
   <si>
     <t>This is the activity for 1 kg of blue methanol</t>
+  </si>
+  <si>
+    <t>ethylene, fMTO; methanol, BAU</t>
+  </si>
+  <si>
+    <t>This is the activity for the production of ethylene via fMTO</t>
+  </si>
+  <si>
+    <t>ethylene, Abhi</t>
+  </si>
+  <si>
+    <t>steam production, in chemical industry</t>
+  </si>
+  <si>
+    <t>steam, in chemical industry</t>
+  </si>
+  <si>
+    <t>market for wastewater, average</t>
+  </si>
+  <si>
+    <t>ethylene, MTO; methanol, BAU</t>
   </si>
 </sst>
 </file>
@@ -773,7 +795,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -835,6 +857,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1153,19 +1178,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55E8D1F9-2651-4D58-AB8D-D63402B2F76A}">
   <dimension ref="A1:K290"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="70.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="70.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>45</v>
       </c>
@@ -1179,7 +1204,7 @@
       <c r="G1" s="13"/>
       <c r="H1" s="13"/>
     </row>
-    <row r="2" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="3"/>
@@ -1189,7 +1214,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1203,7 +1228,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
@@ -1217,7 +1242,7 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
@@ -1231,7 +1256,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>5</v>
       </c>
@@ -1245,7 +1270,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>6</v>
       </c>
@@ -1259,7 +1284,7 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>8</v>
       </c>
@@ -1273,7 +1298,7 @@
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -1285,7 +1310,7 @@
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>11</v>
       </c>
@@ -1311,7 +1336,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -1335,7 +1360,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>53</v>
       </c>
@@ -1359,7 +1384,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>55</v>
       </c>
@@ -1382,7 +1407,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="3"/>
@@ -1392,7 +1417,7 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
@@ -1406,7 +1431,7 @@
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>2</v>
       </c>
@@ -1420,7 +1445,7 @@
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>3</v>
       </c>
@@ -1434,7 +1459,7 @@
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>5</v>
       </c>
@@ -1448,7 +1473,7 @@
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>6</v>
       </c>
@@ -1462,7 +1487,7 @@
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>8</v>
       </c>
@@ -1476,7 +1501,7 @@
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
@@ -1488,7 +1513,7 @@
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>11</v>
       </c>
@@ -1514,7 +1539,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>56</v>
       </c>
@@ -1538,7 +1563,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>58</v>
       </c>
@@ -1562,7 +1587,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>60</v>
       </c>
@@ -1585,7 +1610,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -1608,7 +1633,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -1631,7 +1656,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="3"/>
@@ -1641,7 +1666,7 @@
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>0</v>
       </c>
@@ -1655,7 +1680,7 @@
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>2</v>
       </c>
@@ -1669,7 +1694,7 @@
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>3</v>
       </c>
@@ -1683,7 +1708,7 @@
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
         <v>5</v>
       </c>
@@ -1697,7 +1722,7 @@
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
         <v>6</v>
       </c>
@@ -1711,7 +1736,7 @@
       <c r="G33" s="8"/>
       <c r="H33" s="8"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
         <v>8</v>
       </c>
@@ -1725,7 +1750,7 @@
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>10</v>
       </c>
@@ -1737,7 +1762,7 @@
       <c r="G35" s="8"/>
       <c r="H35" s="8"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
         <v>11</v>
       </c>
@@ -1763,7 +1788,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>63</v>
       </c>
@@ -1787,7 +1812,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>65</v>
       </c>
@@ -1811,7 +1836,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>67</v>
       </c>
@@ -1834,7 +1859,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>69</v>
       </c>
@@ -1857,7 +1882,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>55</v>
       </c>
@@ -1880,7 +1905,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="3"/>
@@ -1890,7 +1915,7 @@
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>0</v>
       </c>
@@ -1904,7 +1929,7 @@
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
         <v>2</v>
       </c>
@@ -1918,7 +1943,7 @@
       <c r="G44" s="8"/>
       <c r="H44" s="8"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
         <v>3</v>
       </c>
@@ -1932,7 +1957,7 @@
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
         <v>5</v>
       </c>
@@ -1946,7 +1971,7 @@
       <c r="G46" s="8"/>
       <c r="H46" s="8"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
         <v>6</v>
       </c>
@@ -1960,7 +1985,7 @@
       <c r="G47" s="8"/>
       <c r="H47" s="8"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
         <v>8</v>
       </c>
@@ -1974,7 +1999,7 @@
       <c r="G48" s="8"/>
       <c r="H48" s="8"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>10</v>
       </c>
@@ -1986,7 +2011,7 @@
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
         <v>11</v>
       </c>
@@ -2012,7 +2037,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>71</v>
       </c>
@@ -2036,7 +2061,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>53</v>
       </c>
@@ -2060,7 +2085,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>73</v>
       </c>
@@ -2083,7 +2108,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>62</v>
       </c>
@@ -2106,7 +2131,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>55</v>
       </c>
@@ -2129,7 +2154,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="3"/>
@@ -2139,7 +2164,7 @@
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>0</v>
       </c>
@@ -2153,7 +2178,7 @@
       <c r="G57" s="8"/>
       <c r="H57" s="8"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
         <v>2</v>
       </c>
@@ -2167,7 +2192,7 @@
       <c r="G58" s="8"/>
       <c r="H58" s="8"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
         <v>3</v>
       </c>
@@ -2181,7 +2206,7 @@
       <c r="G59" s="8"/>
       <c r="H59" s="8"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="8" t="s">
         <v>5</v>
       </c>
@@ -2195,7 +2220,7 @@
       <c r="G60" s="8"/>
       <c r="H60" s="8"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
         <v>6</v>
       </c>
@@ -2209,7 +2234,7 @@
       <c r="G61" s="8"/>
       <c r="H61" s="8"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="8" t="s">
         <v>8</v>
       </c>
@@ -2223,7 +2248,7 @@
       <c r="G62" s="8"/>
       <c r="H62" s="8"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>10</v>
       </c>
@@ -2235,7 +2260,7 @@
       <c r="G63" s="8"/>
       <c r="H63" s="8"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="8" t="s">
         <v>11</v>
       </c>
@@ -2261,7 +2286,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>75</v>
       </c>
@@ -2285,7 +2310,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>77</v>
       </c>
@@ -2309,7 +2334,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>62</v>
       </c>
@@ -2332,7 +2357,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>55</v>
       </c>
@@ -2355,7 +2380,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="3"/>
@@ -2365,7 +2390,7 @@
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>0</v>
       </c>
@@ -2379,7 +2404,7 @@
       <c r="G70" s="8"/>
       <c r="H70" s="8"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
         <v>2</v>
       </c>
@@ -2393,7 +2418,7 @@
       <c r="G71" s="8"/>
       <c r="H71" s="8"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="8" t="s">
         <v>3</v>
       </c>
@@ -2407,7 +2432,7 @@
       <c r="G72" s="8"/>
       <c r="H72" s="8"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
         <v>5</v>
       </c>
@@ -2421,7 +2446,7 @@
       <c r="G73" s="8"/>
       <c r="H73" s="8"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="8" t="s">
         <v>6</v>
       </c>
@@ -2435,7 +2460,7 @@
       <c r="G74" s="8"/>
       <c r="H74" s="8"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
         <v>8</v>
       </c>
@@ -2449,7 +2474,7 @@
       <c r="G75" s="8"/>
       <c r="H75" s="8"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>10</v>
       </c>
@@ -2461,7 +2486,7 @@
       <c r="G76" s="8"/>
       <c r="H76" s="8"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
         <v>11</v>
       </c>
@@ -2487,7 +2512,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>78</v>
       </c>
@@ -2511,7 +2536,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>65</v>
       </c>
@@ -2535,7 +2560,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>80</v>
       </c>
@@ -2559,7 +2584,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>62</v>
       </c>
@@ -2582,7 +2607,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>55</v>
       </c>
@@ -2605,7 +2630,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="3"/>
@@ -2615,7 +2640,7 @@
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>0</v>
       </c>
@@ -2629,7 +2654,7 @@
       <c r="G84" s="8"/>
       <c r="H84" s="8"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
         <v>2</v>
       </c>
@@ -2643,7 +2668,7 @@
       <c r="G85" s="8"/>
       <c r="H85" s="8"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="8" t="s">
         <v>3</v>
       </c>
@@ -2657,7 +2682,7 @@
       <c r="G86" s="8"/>
       <c r="H86" s="8"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
         <v>5</v>
       </c>
@@ -2671,7 +2696,7 @@
       <c r="G87" s="8"/>
       <c r="H87" s="8"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="8" t="s">
         <v>6</v>
       </c>
@@ -2685,7 +2710,7 @@
       <c r="G88" s="8"/>
       <c r="H88" s="8"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
         <v>8</v>
       </c>
@@ -2699,7 +2724,7 @@
       <c r="G89" s="8"/>
       <c r="H89" s="8"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>10</v>
       </c>
@@ -2711,7 +2736,7 @@
       <c r="G90" s="8"/>
       <c r="H90" s="8"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
         <v>11</v>
       </c>
@@ -2737,7 +2762,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>82</v>
       </c>
@@ -2761,7 +2786,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>77</v>
       </c>
@@ -2785,7 +2810,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>62</v>
       </c>
@@ -2808,7 +2833,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>55</v>
       </c>
@@ -2831,7 +2856,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="3"/>
@@ -2841,7 +2866,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>0</v>
       </c>
@@ -2855,7 +2880,7 @@
       <c r="G97" s="8"/>
       <c r="H97" s="8"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="8" t="s">
         <v>2</v>
       </c>
@@ -2869,7 +2894,7 @@
       <c r="G98" s="8"/>
       <c r="H98" s="8"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
         <v>3</v>
       </c>
@@ -2883,7 +2908,7 @@
       <c r="G99" s="8"/>
       <c r="H99" s="8"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="8" t="s">
         <v>5</v>
       </c>
@@ -2897,7 +2922,7 @@
       <c r="G100" s="8"/>
       <c r="H100" s="8"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
         <v>6</v>
       </c>
@@ -2911,7 +2936,7 @@
       <c r="G101" s="8"/>
       <c r="H101" s="8"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="8" t="s">
         <v>8</v>
       </c>
@@ -2925,7 +2950,7 @@
       <c r="G102" s="8"/>
       <c r="H102" s="8"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>10</v>
       </c>
@@ -2937,7 +2962,7 @@
       <c r="G103" s="8"/>
       <c r="H103" s="8"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="8" t="s">
         <v>11</v>
       </c>
@@ -2963,7 +2988,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>172</v>
       </c>
@@ -2987,7 +3012,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>51</v>
       </c>
@@ -3011,7 +3036,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>56</v>
       </c>
@@ -3035,7 +3060,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>63</v>
       </c>
@@ -3059,7 +3084,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>71</v>
       </c>
@@ -3083,7 +3108,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>75</v>
       </c>
@@ -3107,7 +3132,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>78</v>
       </c>
@@ -3131,7 +3156,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>82</v>
       </c>
@@ -3155,7 +3180,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="3"/>
@@ -3165,7 +3190,7 @@
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>0</v>
       </c>
@@ -3179,7 +3204,7 @@
       <c r="G114" s="8"/>
       <c r="H114" s="8"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
         <v>2</v>
       </c>
@@ -3193,7 +3218,7 @@
       <c r="G115" s="8"/>
       <c r="H115" s="8"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="8" t="s">
         <v>3</v>
       </c>
@@ -3207,7 +3232,7 @@
       <c r="G116" s="8"/>
       <c r="H116" s="8"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
         <v>5</v>
       </c>
@@ -3221,7 +3246,7 @@
       <c r="G117" s="8"/>
       <c r="H117" s="8"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="8" t="s">
         <v>6</v>
       </c>
@@ -3235,7 +3260,7 @@
       <c r="G118" s="8"/>
       <c r="H118" s="8"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
         <v>8</v>
       </c>
@@ -3249,7 +3274,7 @@
       <c r="G119" s="8"/>
       <c r="H119" s="8"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>10</v>
       </c>
@@ -3261,7 +3286,7 @@
       <c r="G120" s="8"/>
       <c r="H120" s="8"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
         <v>11</v>
       </c>
@@ -3287,7 +3312,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>85</v>
       </c>
@@ -3311,7 +3336,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>88</v>
       </c>
@@ -3336,7 +3361,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>48</v>
       </c>
@@ -3361,7 +3386,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>90</v>
       </c>
@@ -3386,7 +3411,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>92</v>
       </c>
@@ -3411,7 +3436,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>35</v>
       </c>
@@ -3432,7 +3457,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>94</v>
       </c>
@@ -3453,7 +3478,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>95</v>
       </c>
@@ -3477,7 +3502,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="3"/>
@@ -3487,7 +3512,7 @@
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>0</v>
       </c>
@@ -3501,7 +3526,7 @@
       <c r="G131" s="8"/>
       <c r="H131" s="8"/>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" s="8" t="s">
         <v>2</v>
       </c>
@@ -3515,7 +3540,7 @@
       <c r="G132" s="8"/>
       <c r="H132" s="8"/>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
         <v>3</v>
       </c>
@@ -3529,7 +3554,7 @@
       <c r="G133" s="8"/>
       <c r="H133" s="8"/>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" s="8" t="s">
         <v>5</v>
       </c>
@@ -3543,7 +3568,7 @@
       <c r="G134" s="8"/>
       <c r="H134" s="8"/>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
         <v>6</v>
       </c>
@@ -3557,7 +3582,7 @@
       <c r="G135" s="8"/>
       <c r="H135" s="8"/>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" s="8" t="s">
         <v>8</v>
       </c>
@@ -3571,7 +3596,7 @@
       <c r="G136" s="8"/>
       <c r="H136" s="8"/>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>10</v>
       </c>
@@ -3583,7 +3608,7 @@
       <c r="G137" s="8"/>
       <c r="H137" s="8"/>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" s="8" t="s">
         <v>11</v>
       </c>
@@ -3609,7 +3634,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>97</v>
       </c>
@@ -3633,7 +3658,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>100</v>
       </c>
@@ -3655,7 +3680,7 @@
       </c>
       <c r="K140" s="15"/>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>37</v>
       </c>
@@ -3677,7 +3702,7 @@
       </c>
       <c r="K141" s="15"/>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>101</v>
       </c>
@@ -3699,7 +3724,7 @@
       </c>
       <c r="K142" s="15"/>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>102</v>
       </c>
@@ -3721,7 +3746,7 @@
       </c>
       <c r="K143" s="15"/>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>103</v>
       </c>
@@ -3743,7 +3768,7 @@
       </c>
       <c r="K144" s="15"/>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>104</v>
       </c>
@@ -3765,7 +3790,7 @@
       </c>
       <c r="K145" s="15"/>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>105</v>
       </c>
@@ -3787,7 +3812,7 @@
       </c>
       <c r="K146" s="15"/>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>106</v>
       </c>
@@ -3808,7 +3833,7 @@
       </c>
       <c r="K147" s="15"/>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>107</v>
       </c>
@@ -3829,7 +3854,7 @@
       </c>
       <c r="K148" s="15"/>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>108</v>
       </c>
@@ -3850,7 +3875,7 @@
       </c>
       <c r="K149" s="15"/>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>109</v>
       </c>
@@ -3871,7 +3896,7 @@
       </c>
       <c r="K150" s="15"/>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>110</v>
       </c>
@@ -3892,7 +3917,7 @@
       </c>
       <c r="K151" s="15"/>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>111</v>
       </c>
@@ -3913,7 +3938,7 @@
       </c>
       <c r="K152" s="15"/>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>112</v>
       </c>
@@ -3934,7 +3959,7 @@
       </c>
       <c r="K153" s="15"/>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>113</v>
       </c>
@@ -3955,7 +3980,7 @@
       </c>
       <c r="K154" s="15"/>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>114</v>
       </c>
@@ -3976,7 +4001,7 @@
       </c>
       <c r="K155" s="15"/>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>115</v>
       </c>
@@ -3997,7 +4022,7 @@
       </c>
       <c r="K156" s="15"/>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>116</v>
       </c>
@@ -4018,7 +4043,7 @@
       </c>
       <c r="K157" s="15"/>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>117</v>
       </c>
@@ -4039,7 +4064,7 @@
       </c>
       <c r="K158" s="15"/>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>118</v>
       </c>
@@ -4060,7 +4085,7 @@
       </c>
       <c r="K159" s="15"/>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="3"/>
@@ -4070,7 +4095,7 @@
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>0</v>
       </c>
@@ -4085,7 +4110,7 @@
       <c r="H161" s="8"/>
       <c r="I161" s="8"/>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" s="8" t="s">
         <v>2</v>
       </c>
@@ -4100,7 +4125,7 @@
       <c r="H162" s="8"/>
       <c r="I162" s="8"/>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
         <v>3</v>
       </c>
@@ -4115,7 +4140,7 @@
       <c r="H163" s="8"/>
       <c r="I163" s="8"/>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" s="8" t="s">
         <v>5</v>
       </c>
@@ -4130,7 +4155,7 @@
       <c r="H164" s="8"/>
       <c r="I164" s="8"/>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
         <v>6</v>
       </c>
@@ -4145,7 +4170,7 @@
       <c r="H165" s="8"/>
       <c r="I165" s="8"/>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" s="8" t="s">
         <v>8</v>
       </c>
@@ -4160,7 +4185,7 @@
       <c r="H166" s="8"/>
       <c r="I166" s="8"/>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>10</v>
       </c>
@@ -4173,7 +4198,7 @@
       <c r="H167" s="8"/>
       <c r="I167" s="8"/>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" s="8" t="s">
         <v>11</v>
       </c>
@@ -4200,7 +4225,7 @@
       </c>
       <c r="I168" s="8"/>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
         <v>29</v>
       </c>
@@ -4223,7 +4248,7 @@
       <c r="H169" s="8"/>
       <c r="I169" s="8"/>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" s="8" t="s">
         <v>126</v>
       </c>
@@ -4247,7 +4272,7 @@
       <c r="I170" s="8"/>
       <c r="K170" s="15"/>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
         <v>129</v>
       </c>
@@ -4271,7 +4296,7 @@
       <c r="I171" s="8"/>
       <c r="K171" s="15"/>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" s="8" t="s">
         <v>131</v>
       </c>
@@ -4295,7 +4320,7 @@
       <c r="I172" s="8"/>
       <c r="K172" s="15"/>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
         <v>133</v>
       </c>
@@ -4319,7 +4344,7 @@
       <c r="I173" s="8"/>
       <c r="K173" s="15"/>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" s="8" t="s">
         <v>124</v>
       </c>
@@ -4345,7 +4370,7 @@
       <c r="I174" s="8"/>
       <c r="K174" s="15"/>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
         <v>134</v>
       </c>
@@ -4371,7 +4396,7 @@
       <c r="I175" s="8"/>
       <c r="K175" s="15"/>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176" s="8" t="s">
         <v>136</v>
       </c>
@@ -4397,7 +4422,7 @@
       <c r="I176" s="8"/>
       <c r="K176" s="15"/>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
         <v>138</v>
       </c>
@@ -4423,7 +4448,7 @@
       <c r="I177" s="8"/>
       <c r="K177" s="15"/>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178" s="8" t="s">
         <v>140</v>
       </c>
@@ -4449,7 +4474,7 @@
       <c r="I178" s="8"/>
       <c r="K178" s="15"/>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
         <v>141</v>
       </c>
@@ -4475,7 +4500,7 @@
       <c r="I179" s="8"/>
       <c r="K179" s="15"/>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180" s="8" t="s">
         <v>142</v>
       </c>
@@ -4501,7 +4526,7 @@
       <c r="I180" s="8"/>
       <c r="K180" s="15"/>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
         <v>145</v>
       </c>
@@ -4527,7 +4552,7 @@
       <c r="I181" s="8"/>
       <c r="K181" s="15"/>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182" s="8" t="s">
         <v>148</v>
       </c>
@@ -4553,7 +4578,7 @@
       <c r="I182" s="8"/>
       <c r="K182" s="15"/>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
         <v>150</v>
       </c>
@@ -4579,7 +4604,7 @@
       <c r="I183" s="8"/>
       <c r="K183" s="15"/>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184" s="8" t="s">
         <v>152</v>
       </c>
@@ -4605,7 +4630,7 @@
       <c r="I184" s="8"/>
       <c r="K184" s="15"/>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
         <v>154</v>
       </c>
@@ -4631,7 +4656,7 @@
       <c r="I185" s="8"/>
       <c r="K185" s="15"/>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186" s="8" t="s">
         <v>156</v>
       </c>
@@ -4657,7 +4682,7 @@
       <c r="I186" s="8"/>
       <c r="K186" s="15"/>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="3"/>
@@ -4668,7 +4693,7 @@
       <c r="H187" s="2"/>
       <c r="K187" s="15"/>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>0</v>
       </c>
@@ -4683,7 +4708,7 @@
       <c r="H188" s="8"/>
       <c r="K188" s="15"/>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
         <v>2</v>
       </c>
@@ -4698,7 +4723,7 @@
       <c r="H189" s="8"/>
       <c r="K189" s="15"/>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190" s="8" t="s">
         <v>3</v>
       </c>
@@ -4712,7 +4737,7 @@
       <c r="G190" s="8"/>
       <c r="H190" s="8"/>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
         <v>5</v>
       </c>
@@ -4726,7 +4751,7 @@
       <c r="G191" s="8"/>
       <c r="H191" s="8"/>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192" s="8" t="s">
         <v>6</v>
       </c>
@@ -4740,7 +4765,7 @@
       <c r="G192" s="8"/>
       <c r="H192" s="8"/>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
         <v>8</v>
       </c>
@@ -4754,7 +4779,7 @@
       <c r="G193" s="8"/>
       <c r="H193" s="8"/>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>10</v>
       </c>
@@ -4766,7 +4791,7 @@
       <c r="G194" s="8"/>
       <c r="H194" s="8"/>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
         <v>11</v>
       </c>
@@ -4792,7 +4817,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="8" t="s">
         <v>123</v>
       </c>
@@ -4816,7 +4841,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
         <v>124</v>
       </c>
@@ -4840,7 +4865,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>55</v>
       </c>
@@ -4864,7 +4889,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" s="10" t="s">
         <v>29</v>
       </c>
@@ -4887,7 +4912,7 @@
       </c>
       <c r="H199" s="8"/>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="3"/>
@@ -4897,7 +4922,7 @@
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>0</v>
       </c>
@@ -4911,7 +4936,7 @@
       <c r="G201" s="8"/>
       <c r="H201" s="8"/>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" s="8" t="s">
         <v>2</v>
       </c>
@@ -4925,7 +4950,7 @@
       <c r="G202" s="8"/>
       <c r="H202" s="8"/>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
         <v>3</v>
       </c>
@@ -4939,7 +4964,7 @@
       <c r="G203" s="8"/>
       <c r="H203" s="8"/>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" s="8" t="s">
         <v>5</v>
       </c>
@@ -4953,7 +4978,7 @@
       <c r="G204" s="8"/>
       <c r="H204" s="8"/>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" s="8" t="s">
         <v>6</v>
       </c>
@@ -4967,7 +4992,7 @@
       <c r="G205" s="8"/>
       <c r="H205" s="8"/>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" s="8" t="s">
         <v>8</v>
       </c>
@@ -4981,7 +5006,7 @@
       <c r="G206" s="8"/>
       <c r="H206" s="8"/>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>10</v>
       </c>
@@ -4993,7 +5018,7 @@
       <c r="G207" s="8"/>
       <c r="H207" s="8"/>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" s="8" t="s">
         <v>11</v>
       </c>
@@ -5019,7 +5044,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
         <v>160</v>
       </c>
@@ -5043,7 +5068,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" s="8" t="s">
         <v>124</v>
       </c>
@@ -5067,7 +5092,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>55</v>
       </c>
@@ -5091,7 +5116,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" s="10" t="s">
         <v>29</v>
       </c>
@@ -5114,7 +5139,7 @@
       </c>
       <c r="H212" s="8"/>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="3"/>
@@ -5124,7 +5149,7 @@
       <c r="G213" s="2"/>
       <c r="H213" s="2"/>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>0</v>
       </c>
@@ -5138,7 +5163,7 @@
       <c r="G214" s="8"/>
       <c r="H214" s="8"/>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" s="8" t="s">
         <v>2</v>
       </c>
@@ -5152,7 +5177,7 @@
       <c r="G215" s="8"/>
       <c r="H215" s="8"/>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" s="8" t="s">
         <v>3</v>
       </c>
@@ -5166,7 +5191,7 @@
       <c r="G216" s="8"/>
       <c r="H216" s="8"/>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" s="8" t="s">
         <v>5</v>
       </c>
@@ -5180,7 +5205,7 @@
       <c r="G217" s="8"/>
       <c r="H217" s="8"/>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" s="8" t="s">
         <v>6</v>
       </c>
@@ -5194,7 +5219,7 @@
       <c r="G218" s="8"/>
       <c r="H218" s="8"/>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="8" t="s">
         <v>8</v>
       </c>
@@ -5208,7 +5233,7 @@
       <c r="G219" s="8"/>
       <c r="H219" s="8"/>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>10</v>
       </c>
@@ -5220,7 +5245,7 @@
       <c r="G220" s="8"/>
       <c r="H220" s="8"/>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" s="8" t="s">
         <v>11</v>
       </c>
@@ -5246,7 +5271,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" s="8" t="s">
         <v>163</v>
       </c>
@@ -5270,7 +5295,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>85</v>
       </c>
@@ -5294,7 +5319,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" s="8" t="s">
         <v>160</v>
       </c>
@@ -5318,7 +5343,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" s="8" t="s">
         <v>165</v>
       </c>
@@ -5342,7 +5367,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" s="8" t="s">
         <v>161</v>
       </c>
@@ -5366,7 +5391,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" s="10" t="s">
         <v>29</v>
       </c>
@@ -5388,7 +5413,7 @@
       </c>
       <c r="H227" s="8"/>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="3"/>
@@ -5398,7 +5423,7 @@
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>0</v>
       </c>
@@ -5412,7 +5437,7 @@
       <c r="G229" s="8"/>
       <c r="H229" s="8"/>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" s="8" t="s">
         <v>2</v>
       </c>
@@ -5426,7 +5451,7 @@
       <c r="G230" s="8"/>
       <c r="H230" s="8"/>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" s="8" t="s">
         <v>3</v>
       </c>
@@ -5440,7 +5465,7 @@
       <c r="G231" s="8"/>
       <c r="H231" s="8"/>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" s="8" t="s">
         <v>5</v>
       </c>
@@ -5454,7 +5479,7 @@
       <c r="G232" s="8"/>
       <c r="H232" s="8"/>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" s="8" t="s">
         <v>6</v>
       </c>
@@ -5468,7 +5493,7 @@
       <c r="G233" s="8"/>
       <c r="H233" s="8"/>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" s="8" t="s">
         <v>8</v>
       </c>
@@ -5482,7 +5507,7 @@
       <c r="G234" s="8"/>
       <c r="H234" s="8"/>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>10</v>
       </c>
@@ -5494,7 +5519,7 @@
       <c r="G235" s="8"/>
       <c r="H235" s="8"/>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" s="8" t="s">
         <v>11</v>
       </c>
@@ -5520,7 +5545,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" s="8" t="s">
         <v>161</v>
       </c>
@@ -5544,7 +5569,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>85</v>
       </c>
@@ -5568,7 +5593,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" s="8" t="s">
         <v>160</v>
       </c>
@@ -5592,7 +5617,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>55</v>
       </c>
@@ -5615,7 +5640,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" s="8" t="s">
         <v>163</v>
       </c>
@@ -5639,7 +5664,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" s="10" t="s">
         <v>29</v>
       </c>
@@ -5661,7 +5686,7 @@
       </c>
       <c r="H242" s="8"/>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="3"/>
@@ -5671,7 +5696,7 @@
       <c r="G243" s="2"/>
       <c r="H243" s="2"/>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>0</v>
       </c>
@@ -5685,7 +5710,7 @@
       <c r="G244" s="8"/>
       <c r="H244" s="8"/>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" s="8" t="s">
         <v>2</v>
       </c>
@@ -5699,7 +5724,7 @@
       <c r="G245" s="8"/>
       <c r="H245" s="8"/>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" s="8" t="s">
         <v>3</v>
       </c>
@@ -5713,7 +5738,7 @@
       <c r="G246" s="8"/>
       <c r="H246" s="8"/>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" s="8" t="s">
         <v>5</v>
       </c>
@@ -5727,7 +5752,7 @@
       <c r="G247" s="8"/>
       <c r="H247" s="8"/>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" s="8" t="s">
         <v>6</v>
       </c>
@@ -5741,7 +5766,7 @@
       <c r="G248" s="8"/>
       <c r="H248" s="8"/>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" s="8" t="s">
         <v>8</v>
       </c>
@@ -5755,7 +5780,7 @@
       <c r="G249" s="8"/>
       <c r="H249" s="8"/>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>10</v>
       </c>
@@ -5767,7 +5792,7 @@
       <c r="G250" s="8"/>
       <c r="H250" s="8"/>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" s="8" t="s">
         <v>11</v>
       </c>
@@ -5793,7 +5818,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" s="8" t="s">
         <v>40</v>
       </c>
@@ -5817,7 +5842,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" s="5" t="s">
         <v>170</v>
       </c>
@@ -5841,7 +5866,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" s="7" t="s">
         <v>32</v>
       </c>
@@ -5863,7 +5888,7 @@
       </c>
       <c r="H254" s="8"/>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" s="5" t="s">
         <v>38</v>
       </c>
@@ -5886,7 +5911,7 @@
       </c>
       <c r="H255" s="8"/>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="3"/>
@@ -5896,7 +5921,7 @@
       <c r="G256" s="2"/>
       <c r="H256" s="2"/>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" s="22" t="s">
         <v>0</v>
       </c>
@@ -5910,7 +5935,7 @@
       <c r="G257" s="5"/>
       <c r="H257" s="5"/>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" s="22" t="s">
         <v>2</v>
       </c>
@@ -5924,7 +5949,7 @@
       <c r="G258" s="5"/>
       <c r="H258" s="5"/>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" s="22" t="s">
         <v>3</v>
       </c>
@@ -5938,7 +5963,7 @@
       <c r="G259" s="5"/>
       <c r="H259" s="5"/>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>6</v>
       </c>
@@ -5952,7 +5977,7 @@
       <c r="G260" s="5"/>
       <c r="H260" s="5"/>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" s="22" t="s">
         <v>5</v>
       </c>
@@ -5966,7 +5991,7 @@
       <c r="G261" s="5"/>
       <c r="H261" s="5"/>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" s="22" t="s">
         <v>8</v>
       </c>
@@ -5980,7 +6005,7 @@
       <c r="G262" s="5"/>
       <c r="H262" s="5"/>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" s="22" t="s">
         <v>204</v>
       </c>
@@ -5992,7 +6017,7 @@
       <c r="G263" s="5"/>
       <c r="H263" s="5"/>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" s="22" t="s">
         <v>10</v>
       </c>
@@ -6004,7 +6029,7 @@
       <c r="G264" s="5"/>
       <c r="H264" s="5"/>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" s="5" t="s">
         <v>11</v>
       </c>
@@ -6030,7 +6055,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" s="20" t="s">
         <v>188</v>
       </c>
@@ -6054,7 +6079,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" s="5" t="s">
         <v>187</v>
       </c>
@@ -6078,7 +6103,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" s="20" t="s">
         <v>205</v>
       </c>
@@ -6102,7 +6127,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" s="20" t="s">
         <v>207</v>
       </c>
@@ -6126,7 +6151,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" s="20" t="s">
         <v>209</v>
       </c>
@@ -6150,7 +6175,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>29</v>
       </c>
@@ -6171,7 +6196,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>101</v>
       </c>
@@ -6192,7 +6217,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>100</v>
       </c>
@@ -6213,7 +6238,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A274" s="21" t="s">
         <v>210</v>
       </c>
@@ -6234,7 +6259,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>37</v>
       </c>
@@ -6255,7 +6280,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A276" s="21" t="s">
         <v>198</v>
       </c>
@@ -6276,7 +6301,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A277" s="21" t="s">
         <v>105</v>
       </c>
@@ -6297,7 +6322,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A278" s="21" t="s">
         <v>211</v>
       </c>
@@ -6318,7 +6343,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A279" s="21" t="s">
         <v>212</v>
       </c>
@@ -6339,7 +6364,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A280" s="21" t="s">
         <v>213</v>
       </c>
@@ -6360,7 +6385,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A281" s="21" t="s">
         <v>115</v>
       </c>
@@ -6381,7 +6406,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A282" s="21" t="s">
         <v>214</v>
       </c>
@@ -6402,7 +6427,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A283" s="21" t="s">
         <v>215</v>
       </c>
@@ -6422,7 +6447,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284" s="21" t="s">
         <v>199</v>
       </c>
@@ -6442,7 +6467,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285" s="21" t="s">
         <v>108</v>
       </c>
@@ -6462,7 +6487,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A286" s="21" t="s">
         <v>216</v>
       </c>
@@ -6482,7 +6507,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A287" s="21" t="s">
         <v>217</v>
       </c>
@@ -6502,7 +6527,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A288" s="21" t="s">
         <v>218</v>
       </c>
@@ -6522,7 +6547,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A289" s="21" t="s">
         <v>219</v>
       </c>
@@ -6542,7 +6567,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A290" s="21" t="s">
         <v>220</v>
       </c>
@@ -6571,17 +6596,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD968991-55C9-4627-9323-29F50518FFEB}">
   <dimension ref="A1:H97"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="86.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="86.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6595,7 +6620,7 @@
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>2</v>
       </c>
@@ -6609,7 +6634,7 @@
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
@@ -6623,7 +6648,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>5</v>
       </c>
@@ -6637,7 +6662,7 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
@@ -6651,7 +6676,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>8</v>
       </c>
@@ -6665,7 +6690,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -6677,7 +6702,7 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>11</v>
       </c>
@@ -6703,7 +6728,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -6727,7 +6752,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>47</v>
       </c>
@@ -6751,7 +6776,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>48</v>
       </c>
@@ -6775,7 +6800,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>49</v>
       </c>
@@ -6799,7 +6824,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -6823,7 +6848,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>172</v>
       </c>
@@ -6847,7 +6872,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>85</v>
       </c>
@@ -6871,7 +6896,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>120</v>
       </c>
@@ -6895,7 +6920,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -6916,7 +6941,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>97</v>
       </c>
@@ -6940,7 +6965,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>55</v>
       </c>
@@ -6963,7 +6988,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -6983,7 +7008,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -7003,7 +7028,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>100</v>
       </c>
@@ -7023,7 +7048,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>101</v>
       </c>
@@ -7043,7 +7068,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -7063,7 +7088,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>37</v>
       </c>
@@ -7083,7 +7108,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>38</v>
       </c>
@@ -7104,7 +7129,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>36</v>
       </c>
@@ -7124,7 +7149,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>94</v>
       </c>
@@ -7144,7 +7169,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>38</v>
       </c>
@@ -7165,7 +7190,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>156</v>
       </c>
@@ -7188,7 +7213,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>121</v>
       </c>
@@ -7212,7 +7237,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="3"/>
@@ -7222,7 +7247,7 @@
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>0</v>
       </c>
@@ -7236,7 +7261,7 @@
       <c r="G33" s="8"/>
       <c r="H33" s="8"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
         <v>2</v>
       </c>
@@ -7250,7 +7275,7 @@
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
         <v>3</v>
       </c>
@@ -7264,7 +7289,7 @@
       <c r="G35" s="8"/>
       <c r="H35" s="8"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
         <v>5</v>
       </c>
@@ -7278,7 +7303,7 @@
       <c r="G36" s="8"/>
       <c r="H36" s="8"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
         <v>6</v>
       </c>
@@ -7292,7 +7317,7 @@
       <c r="G37" s="8"/>
       <c r="H37" s="8"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
         <v>8</v>
       </c>
@@ -7306,7 +7331,7 @@
       <c r="G38" s="8"/>
       <c r="H38" s="8"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>10</v>
       </c>
@@ -7318,7 +7343,7 @@
       <c r="G39" s="8"/>
       <c r="H39" s="8"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
         <v>11</v>
       </c>
@@ -7344,7 +7369,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>167</v>
       </c>
@@ -7368,7 +7393,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>47</v>
       </c>
@@ -7392,7 +7417,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>48</v>
       </c>
@@ -7416,7 +7441,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -7440,7 +7465,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>27</v>
       </c>
@@ -7464,7 +7489,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>172</v>
       </c>
@@ -7488,7 +7513,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>85</v>
       </c>
@@ -7512,7 +7537,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
         <v>123</v>
       </c>
@@ -7536,7 +7561,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>32</v>
       </c>
@@ -7557,7 +7582,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>97</v>
       </c>
@@ -7581,7 +7606,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
         <v>161</v>
       </c>
@@ -7605,7 +7630,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
         <v>163</v>
       </c>
@@ -7629,7 +7654,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>34</v>
       </c>
@@ -7649,7 +7674,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>35</v>
       </c>
@@ -7669,7 +7694,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>100</v>
       </c>
@@ -7689,7 +7714,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>101</v>
       </c>
@@ -7709,7 +7734,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>29</v>
       </c>
@@ -7729,7 +7754,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>37</v>
       </c>
@@ -7749,7 +7774,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>38</v>
       </c>
@@ -7770,7 +7795,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>36</v>
       </c>
@@ -7790,7 +7815,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>94</v>
       </c>
@@ -7810,7 +7835,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>38</v>
       </c>
@@ -7831,7 +7856,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
         <v>156</v>
       </c>
@@ -7854,7 +7879,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="8" t="s">
         <v>121</v>
       </c>
@@ -7878,7 +7903,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="3"/>
@@ -7888,7 +7913,7 @@
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>0</v>
       </c>
@@ -7902,7 +7927,7 @@
       <c r="G66" s="8"/>
       <c r="H66" s="8"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
         <v>2</v>
       </c>
@@ -7916,7 +7941,7 @@
       <c r="G67" s="8"/>
       <c r="H67" s="8"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="8" t="s">
         <v>3</v>
       </c>
@@ -7930,7 +7955,7 @@
       <c r="G68" s="8"/>
       <c r="H68" s="8"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
         <v>5</v>
       </c>
@@ -7944,7 +7969,7 @@
       <c r="G69" s="8"/>
       <c r="H69" s="8"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
         <v>6</v>
       </c>
@@ -7958,7 +7983,7 @@
       <c r="G70" s="8"/>
       <c r="H70" s="8"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
         <v>8</v>
       </c>
@@ -7972,7 +7997,7 @@
       <c r="G71" s="8"/>
       <c r="H71" s="8"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>10</v>
       </c>
@@ -7984,7 +8009,7 @@
       <c r="G72" s="8"/>
       <c r="H72" s="8"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
         <v>11</v>
       </c>
@@ -8010,7 +8035,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>173</v>
       </c>
@@ -8034,7 +8059,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
         <v>40</v>
       </c>
@@ -8058,7 +8083,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>78</v>
       </c>
@@ -8082,7 +8107,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>27</v>
       </c>
@@ -8106,7 +8131,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>32</v>
       </c>
@@ -8128,7 +8153,7 @@
       </c>
       <c r="H78" s="10"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>55</v>
       </c>
@@ -8151,7 +8176,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>34</v>
       </c>
@@ -8171,7 +8196,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>35</v>
       </c>
@@ -8191,7 +8216,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>37</v>
       </c>
@@ -8211,7 +8236,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>38</v>
       </c>
@@ -8232,7 +8257,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>38</v>
       </c>
@@ -8253,7 +8278,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
         <v>156</v>
       </c>
@@ -8276,61 +8301,61 @@
         <v>157</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B86" s="16"/>
       <c r="C86" s="10"/>
       <c r="G86" s="10"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B87" s="16"/>
       <c r="C87" s="10"/>
       <c r="G87" s="10"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B88" s="16"/>
       <c r="C88" s="10"/>
       <c r="G88" s="10"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B89" s="16"/>
       <c r="C89" s="10"/>
       <c r="G89" s="10"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B90" s="4"/>
       <c r="C90" s="10"/>
       <c r="G90" s="10"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B91" s="16"/>
       <c r="C91" s="10"/>
       <c r="G91" s="10"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B92" s="16"/>
       <c r="C92" s="10"/>
       <c r="G92" s="10"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B93" s="16"/>
       <c r="C93" s="10"/>
       <c r="G93" s="10"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B94" s="16"/>
       <c r="C94" s="10"/>
       <c r="G94" s="10"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B95" s="16"/>
       <c r="C95" s="10"/>
       <c r="G95" s="10"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B96" s="16"/>
       <c r="G96" s="10"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="8"/>
       <c r="B97" s="14"/>
       <c r="C97" s="8"/>
@@ -8349,17 +8374,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20D067F8-C305-44D3-8E28-CF1FDCAD7A72}">
   <dimension ref="A1:H75"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="86.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="86.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8373,7 +8398,7 @@
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>2</v>
       </c>
@@ -8387,7 +8412,7 @@
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
@@ -8401,7 +8426,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>5</v>
       </c>
@@ -8415,7 +8440,7 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
@@ -8429,7 +8454,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>8</v>
       </c>
@@ -8443,7 +8468,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -8455,7 +8480,7 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>11</v>
       </c>
@@ -8481,7 +8506,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>174</v>
       </c>
@@ -8505,7 +8530,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>47</v>
       </c>
@@ -8529,7 +8554,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>165</v>
       </c>
@@ -8553,7 +8578,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>55</v>
       </c>
@@ -8576,7 +8601,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>178</v>
       </c>
@@ -8600,7 +8625,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>180</v>
       </c>
@@ -8624,7 +8649,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>73</v>
       </c>
@@ -8648,7 +8673,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>182</v>
       </c>
@@ -8672,7 +8697,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -8696,7 +8721,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>183</v>
       </c>
@@ -8721,7 +8746,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>184</v>
       </c>
@@ -8744,7 +8769,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>100</v>
       </c>
@@ -8765,7 +8790,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -8786,7 +8811,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>191</v>
       </c>
@@ -8807,7 +8832,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -8828,7 +8853,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>38</v>
       </c>
@@ -8849,7 +8874,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>192</v>
       </c>
@@ -8870,7 +8895,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>193</v>
       </c>
@@ -8891,7 +8916,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>194</v>
       </c>
@@ -8912,7 +8937,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>195</v>
       </c>
@@ -8933,7 +8958,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>193</v>
       </c>
@@ -8953,7 +8978,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -8973,7 +8998,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>196</v>
       </c>
@@ -8993,7 +9018,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>197</v>
       </c>
@@ -9013,7 +9038,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>198</v>
       </c>
@@ -9033,7 +9058,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>199</v>
       </c>
@@ -9053,7 +9078,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>200</v>
       </c>
@@ -9073,7 +9098,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
         <v>201</v>
       </c>
@@ -9094,7 +9119,7 @@
       </c>
       <c r="H36" s="8"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
         <v>202</v>
       </c>
@@ -9116,7 +9141,7 @@
       </c>
       <c r="H37" s="8"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="3"/>
@@ -9126,7 +9151,7 @@
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>0</v>
       </c>
@@ -9140,7 +9165,7 @@
       <c r="G39" s="8"/>
       <c r="H39" s="8"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
         <v>2</v>
       </c>
@@ -9154,7 +9179,7 @@
       <c r="G40" s="8"/>
       <c r="H40" s="8"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>3</v>
       </c>
@@ -9168,7 +9193,7 @@
       <c r="G41" s="8"/>
       <c r="H41" s="8"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
         <v>5</v>
       </c>
@@ -9182,7 +9207,7 @@
       <c r="G42" s="8"/>
       <c r="H42" s="8"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>6</v>
       </c>
@@ -9196,7 +9221,7 @@
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
         <v>8</v>
       </c>
@@ -9210,7 +9235,7 @@
       <c r="G44" s="8"/>
       <c r="H44" s="8"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>10</v>
       </c>
@@ -9222,7 +9247,7 @@
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
         <v>11</v>
       </c>
@@ -9248,7 +9273,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>177</v>
       </c>
@@ -9272,7 +9297,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>47</v>
       </c>
@@ -9296,7 +9321,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="20" t="s">
         <v>188</v>
       </c>
@@ -9320,7 +9345,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>55</v>
       </c>
@@ -9343,7 +9368,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>178</v>
       </c>
@@ -9367,7 +9392,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>180</v>
       </c>
@@ -9391,7 +9416,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>73</v>
       </c>
@@ -9415,7 +9440,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>182</v>
       </c>
@@ -9439,7 +9464,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>49</v>
       </c>
@@ -9463,7 +9488,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>183</v>
       </c>
@@ -9488,7 +9513,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>184</v>
       </c>
@@ -9511,7 +9536,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>100</v>
       </c>
@@ -9532,7 +9557,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>32</v>
       </c>
@@ -9553,7 +9578,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>191</v>
       </c>
@@ -9574,7 +9599,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>37</v>
       </c>
@@ -9595,7 +9620,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>38</v>
       </c>
@@ -9616,7 +9641,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>192</v>
       </c>
@@ -9637,7 +9662,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>193</v>
       </c>
@@ -9658,7 +9683,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>194</v>
       </c>
@@ -9679,7 +9704,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>195</v>
       </c>
@@ -9700,7 +9725,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>193</v>
       </c>
@@ -9720,7 +9745,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>38</v>
       </c>
@@ -9740,7 +9765,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>196</v>
       </c>
@@ -9760,7 +9785,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>197</v>
       </c>
@@ -9780,7 +9805,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>198</v>
       </c>
@@ -9800,7 +9825,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>199</v>
       </c>
@@ -9820,7 +9845,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>200</v>
       </c>
@@ -9840,7 +9865,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="8" t="s">
         <v>201</v>
       </c>
@@ -9861,7 +9886,7 @@
       </c>
       <c r="H74" s="8"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
         <v>202</v>
       </c>
@@ -9887,4 +9912,321 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{998EBEEB-B02A-47FC-B25F-8D09BAB943A0}">
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="38" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>222</v>
+      </c>
+      <c r="B9" s="4">
+        <v>1</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B10" s="4">
+        <v>2.5190000000000001</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="4">
+        <v>0.14300000000000002</v>
+      </c>
+      <c r="C11" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="20"/>
+      <c r="G11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="4">
+        <f>0.2255/1000</f>
+        <v>2.2550000000000001E-4</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="8"/>
+      <c r="E12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>225</v>
+      </c>
+      <c r="B13" s="4">
+        <v>2.2000000000000002E-2</v>
+      </c>
+      <c r="C13" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="G13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" s="16">
+        <v>2.0789999999999999E-5</v>
+      </c>
+      <c r="C14" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="G14" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="4">
+        <v>0.12100000000000001</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="4">
+        <v>1.6500000000000001E-2</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>227</v>
+      </c>
+      <c r="B17" s="4">
+        <v>-1.474E-3</v>
+      </c>
+      <c r="C17" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>94</v>
+      </c>
+      <c r="B18" s="16">
+        <v>2.0789999999999999E-5</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" t="s">
+        <v>39</v>
+      </c>
+      <c r="G18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Raw data/lci-Abhi image SSP2-Base 2020 new.xlsx
+++ b/Raw data/lci-Abhi image SSP2-Base 2020 new.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20401"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Prospective LCA\Raw data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abhinabera/Desktop/Prospective-LCA/Raw data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FEA5E9C-E374-44EB-8C8B-63CF9D01C813}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{417855A0-DD6F-6646-AE1D-7A011EC5751E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17280" windowHeight="8085" activeTab="3" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
   </bookViews>
   <sheets>
     <sheet name="Utilities" sheetId="6" r:id="rId1"/>
@@ -23,12 +23,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1914" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2000" uniqueCount="241">
   <si>
     <t>Activity</t>
   </si>
@@ -591,9 +602,6 @@
     <t>aluminium oxide, non-metallurgical</t>
   </si>
   <si>
-    <t>market group for natural gas, high pressure</t>
-  </si>
-  <si>
     <t>natural gas heating, with CCS</t>
   </si>
   <si>
@@ -696,9 +704,6 @@
     <t>This is the activity for 1 kg of blue methanol</t>
   </si>
   <si>
-    <t>ethylene, fMTO; methanol, BAU</t>
-  </si>
-  <si>
     <t>This is the activity for the production of ethylene via fMTO</t>
   </si>
   <si>
@@ -715,6 +720,48 @@
   </si>
   <si>
     <t>ethylene, MTO; methanol, BAU</t>
+  </si>
+  <si>
+    <t>heat pump production, heat and power co-generation unit, 160kW electrical</t>
+  </si>
+  <si>
+    <t>heat pump, heat and power co-generation unit, 160kW electrical</t>
+  </si>
+  <si>
+    <t>market for absorption chiller, 100kW</t>
+  </si>
+  <si>
+    <t>absorption chiller, 100kW</t>
+  </si>
+  <si>
+    <t>market for charcoal</t>
+  </si>
+  <si>
+    <t>charcoal</t>
+  </si>
+  <si>
+    <t>market for gas turbine, 10MW electrical</t>
+  </si>
+  <si>
+    <t>gas turbine, 10MW electrical</t>
+  </si>
+  <si>
+    <t>market for liquid storage tank, chemicals, organics</t>
+  </si>
+  <si>
+    <t>liquid storage tank, chemicals, organics</t>
+  </si>
+  <si>
+    <t>market for pump, 40W</t>
+  </si>
+  <si>
+    <t>pump, 40W</t>
+  </si>
+  <si>
+    <t>CH</t>
+  </si>
+  <si>
+    <t>This is the activity for the carbon dioxide storage</t>
   </si>
 </sst>
 </file>
@@ -795,7 +842,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -816,7 +863,6 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -827,12 +873,6 @@
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1177,34 +1217,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55E8D1F9-2651-4D58-AB8D-D63402B2F76A}">
-  <dimension ref="A1:K290"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K310"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="70.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="70.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" customWidth="1"/>
+    <col min="3" max="3" width="38.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-    </row>
-    <row r="2" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C1" s="11"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+    </row>
+    <row r="2" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="3"/>
@@ -1214,7 +1254,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1228,7 +1268,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
@@ -1242,11 +1282,11 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="8"/>
@@ -1256,7 +1296,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>5</v>
       </c>
@@ -1270,7 +1310,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
         <v>6</v>
       </c>
@@ -1284,7 +1324,7 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>8</v>
       </c>
@@ -1298,7 +1338,7 @@
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -1310,7 +1350,7 @@
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
         <v>11</v>
       </c>
@@ -1336,7 +1376,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -1346,7 +1386,7 @@
       <c r="C11" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" t="s">
         <v>4</v>
       </c>
       <c r="E11" t="s">
@@ -1360,7 +1400,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>53</v>
       </c>
@@ -1370,21 +1410,21 @@
       <c r="C12" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" t="s">
         <v>4</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
       </c>
       <c r="F12" s="8"/>
-      <c r="G12" s="10" t="s">
+      <c r="G12" t="s">
         <v>20</v>
       </c>
       <c r="H12" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>55</v>
       </c>
@@ -1394,7 +1434,7 @@
       <c r="C13" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" t="s">
         <v>44</v>
       </c>
       <c r="E13" t="s">
@@ -1407,7 +1447,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="3"/>
@@ -1417,7 +1457,7 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
@@ -1431,7 +1471,7 @@
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
         <v>2</v>
       </c>
@@ -1445,11 +1485,11 @@
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" t="s">
         <v>4</v>
       </c>
       <c r="C17" s="8"/>
@@ -1459,7 +1499,7 @@
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
         <v>5</v>
       </c>
@@ -1473,7 +1513,7 @@
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
         <v>6</v>
       </c>
@@ -1487,7 +1527,7 @@
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
         <v>8</v>
       </c>
@@ -1501,7 +1541,7 @@
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
@@ -1513,7 +1553,7 @@
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
         <v>11</v>
       </c>
@@ -1539,7 +1579,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>56</v>
       </c>
@@ -1549,7 +1589,7 @@
       <c r="C23" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" t="s">
         <v>4</v>
       </c>
       <c r="E23" t="s">
@@ -1563,7 +1603,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>58</v>
       </c>
@@ -1573,21 +1613,21 @@
       <c r="C24" t="s">
         <v>18</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" t="s">
         <v>4</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
       </c>
       <c r="F24" s="8"/>
-      <c r="G24" s="10" t="s">
+      <c r="G24" t="s">
         <v>20</v>
       </c>
       <c r="H24" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>60</v>
       </c>
@@ -1597,20 +1637,20 @@
       <c r="C25" t="s">
         <v>18</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" t="s">
         <v>4</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
       </c>
-      <c r="G25" s="10" t="s">
+      <c r="G25" t="s">
         <v>20</v>
       </c>
       <c r="H25" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -1620,20 +1660,20 @@
       <c r="C26" t="s">
         <v>18</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" t="s">
         <v>19</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
       </c>
-      <c r="G26" s="10" t="s">
+      <c r="G26" t="s">
         <v>20</v>
       </c>
       <c r="H26" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -1643,7 +1683,7 @@
       <c r="C27" t="s">
         <v>18</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" t="s">
         <v>44</v>
       </c>
       <c r="E27" t="s">
@@ -1656,7 +1696,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="3"/>
@@ -1666,7 +1706,7 @@
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>0</v>
       </c>
@@ -1680,7 +1720,7 @@
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
         <v>2</v>
       </c>
@@ -1694,11 +1734,11 @@
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" t="s">
         <v>4</v>
       </c>
       <c r="C31" s="8"/>
@@ -1708,7 +1748,7 @@
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
         <v>5</v>
       </c>
@@ -1722,7 +1762,7 @@
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
         <v>6</v>
       </c>
@@ -1736,7 +1776,7 @@
       <c r="G33" s="8"/>
       <c r="H33" s="8"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
         <v>8</v>
       </c>
@@ -1750,7 +1790,7 @@
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>10</v>
       </c>
@@ -1762,7 +1802,7 @@
       <c r="G35" s="8"/>
       <c r="H35" s="8"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
         <v>11</v>
       </c>
@@ -1788,7 +1828,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>63</v>
       </c>
@@ -1798,7 +1838,7 @@
       <c r="C37" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D37" s="10" t="s">
+      <c r="D37" t="s">
         <v>4</v>
       </c>
       <c r="E37" t="s">
@@ -1812,7 +1852,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>65</v>
       </c>
@@ -1822,21 +1862,21 @@
       <c r="C38" t="s">
         <v>18</v>
       </c>
-      <c r="D38" s="10" t="s">
+      <c r="D38" t="s">
         <v>4</v>
       </c>
       <c r="E38" t="s">
         <v>9</v>
       </c>
       <c r="F38" s="8"/>
-      <c r="G38" s="10" t="s">
+      <c r="G38" t="s">
         <v>20</v>
       </c>
       <c r="H38" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>67</v>
       </c>
@@ -1846,20 +1886,20 @@
       <c r="C39" t="s">
         <v>18</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="D39" t="s">
         <v>4</v>
       </c>
       <c r="E39" t="s">
         <v>9</v>
       </c>
-      <c r="G39" s="10" t="s">
+      <c r="G39" t="s">
         <v>20</v>
       </c>
       <c r="H39" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>69</v>
       </c>
@@ -1869,20 +1909,20 @@
       <c r="C40" t="s">
         <v>18</v>
       </c>
-      <c r="D40" s="10" t="s">
+      <c r="D40" t="s">
         <v>4</v>
       </c>
       <c r="E40" t="s">
         <v>9</v>
       </c>
-      <c r="G40" s="10" t="s">
+      <c r="G40" t="s">
         <v>20</v>
       </c>
       <c r="H40" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>55</v>
       </c>
@@ -1892,7 +1932,7 @@
       <c r="C41" t="s">
         <v>18</v>
       </c>
-      <c r="D41" s="10" t="s">
+      <c r="D41" t="s">
         <v>44</v>
       </c>
       <c r="E41" t="s">
@@ -1905,7 +1945,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="3"/>
@@ -1915,7 +1955,7 @@
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>0</v>
       </c>
@@ -1929,7 +1969,7 @@
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
         <v>2</v>
       </c>
@@ -1943,11 +1983,11 @@
       <c r="G44" s="8"/>
       <c r="H44" s="8"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B45" t="s">
         <v>4</v>
       </c>
       <c r="C45" s="8"/>
@@ -1957,7 +1997,7 @@
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="8" t="s">
         <v>5</v>
       </c>
@@ -1971,7 +2011,7 @@
       <c r="G46" s="8"/>
       <c r="H46" s="8"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
         <v>6</v>
       </c>
@@ -1985,7 +2025,7 @@
       <c r="G47" s="8"/>
       <c r="H47" s="8"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="8" t="s">
         <v>8</v>
       </c>
@@ -1999,7 +2039,7 @@
       <c r="G48" s="8"/>
       <c r="H48" s="8"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>10</v>
       </c>
@@ -2011,7 +2051,7 @@
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
         <v>11</v>
       </c>
@@ -2037,7 +2077,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>71</v>
       </c>
@@ -2047,7 +2087,7 @@
       <c r="C51" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D51" s="10" t="s">
+      <c r="D51" t="s">
         <v>4</v>
       </c>
       <c r="E51" t="s">
@@ -2061,7 +2101,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>53</v>
       </c>
@@ -2071,21 +2111,21 @@
       <c r="C52" t="s">
         <v>18</v>
       </c>
-      <c r="D52" s="10" t="s">
+      <c r="D52" t="s">
         <v>4</v>
       </c>
       <c r="E52" t="s">
         <v>9</v>
       </c>
       <c r="F52" s="8"/>
-      <c r="G52" s="10" t="s">
+      <c r="G52" t="s">
         <v>20</v>
       </c>
       <c r="H52" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>73</v>
       </c>
@@ -2095,20 +2135,20 @@
       <c r="C53" t="s">
         <v>18</v>
       </c>
-      <c r="D53" s="10" t="s">
+      <c r="D53" t="s">
         <v>4</v>
       </c>
       <c r="E53" t="s">
         <v>9</v>
       </c>
-      <c r="G53" s="10" t="s">
+      <c r="G53" t="s">
         <v>20</v>
       </c>
       <c r="H53" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>62</v>
       </c>
@@ -2118,20 +2158,20 @@
       <c r="C54" t="s">
         <v>18</v>
       </c>
-      <c r="D54" s="10" t="s">
+      <c r="D54" t="s">
         <v>19</v>
       </c>
       <c r="E54" t="s">
         <v>9</v>
       </c>
-      <c r="G54" s="10" t="s">
+      <c r="G54" t="s">
         <v>20</v>
       </c>
       <c r="H54" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>55</v>
       </c>
@@ -2141,7 +2181,7 @@
       <c r="C55" t="s">
         <v>18</v>
       </c>
-      <c r="D55" s="10" t="s">
+      <c r="D55" t="s">
         <v>44</v>
       </c>
       <c r="E55" t="s">
@@ -2154,7 +2194,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="3"/>
@@ -2164,7 +2204,7 @@
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>0</v>
       </c>
@@ -2178,7 +2218,7 @@
       <c r="G57" s="8"/>
       <c r="H57" s="8"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="8" t="s">
         <v>2</v>
       </c>
@@ -2192,11 +2232,11 @@
       <c r="G58" s="8"/>
       <c r="H58" s="8"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B59" s="10" t="s">
+      <c r="B59" t="s">
         <v>4</v>
       </c>
       <c r="C59" s="8"/>
@@ -2206,7 +2246,7 @@
       <c r="G59" s="8"/>
       <c r="H59" s="8"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="8" t="s">
         <v>5</v>
       </c>
@@ -2220,7 +2260,7 @@
       <c r="G60" s="8"/>
       <c r="H60" s="8"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="8" t="s">
         <v>6</v>
       </c>
@@ -2234,7 +2274,7 @@
       <c r="G61" s="8"/>
       <c r="H61" s="8"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="8" t="s">
         <v>8</v>
       </c>
@@ -2248,7 +2288,7 @@
       <c r="G62" s="8"/>
       <c r="H62" s="8"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>10</v>
       </c>
@@ -2260,7 +2300,7 @@
       <c r="G63" s="8"/>
       <c r="H63" s="8"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="8" t="s">
         <v>11</v>
       </c>
@@ -2286,7 +2326,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>75</v>
       </c>
@@ -2296,7 +2336,7 @@
       <c r="C65" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D65" s="10" t="s">
+      <c r="D65" t="s">
         <v>4</v>
       </c>
       <c r="E65" t="s">
@@ -2310,7 +2350,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>77</v>
       </c>
@@ -2320,21 +2360,21 @@
       <c r="C66" t="s">
         <v>18</v>
       </c>
-      <c r="D66" s="10" t="s">
+      <c r="D66" t="s">
         <v>4</v>
       </c>
       <c r="E66" t="s">
         <v>9</v>
       </c>
       <c r="F66" s="8"/>
-      <c r="G66" s="10" t="s">
+      <c r="G66" t="s">
         <v>20</v>
       </c>
       <c r="H66" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>62</v>
       </c>
@@ -2344,20 +2384,20 @@
       <c r="C67" t="s">
         <v>18</v>
       </c>
-      <c r="D67" s="10" t="s">
+      <c r="D67" t="s">
         <v>19</v>
       </c>
       <c r="E67" t="s">
         <v>9</v>
       </c>
-      <c r="G67" s="10" t="s">
+      <c r="G67" t="s">
         <v>20</v>
       </c>
       <c r="H67" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>55</v>
       </c>
@@ -2367,7 +2407,7 @@
       <c r="C68" t="s">
         <v>18</v>
       </c>
-      <c r="D68" s="10" t="s">
+      <c r="D68" t="s">
         <v>44</v>
       </c>
       <c r="E68" t="s">
@@ -2380,7 +2420,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="3"/>
@@ -2390,7 +2430,7 @@
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>0</v>
       </c>
@@ -2404,7 +2444,7 @@
       <c r="G70" s="8"/>
       <c r="H70" s="8"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="8" t="s">
         <v>2</v>
       </c>
@@ -2418,11 +2458,11 @@
       <c r="G71" s="8"/>
       <c r="H71" s="8"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B72" s="10" t="s">
+      <c r="B72" t="s">
         <v>4</v>
       </c>
       <c r="C72" s="8"/>
@@ -2432,7 +2472,7 @@
       <c r="G72" s="8"/>
       <c r="H72" s="8"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="8" t="s">
         <v>5</v>
       </c>
@@ -2446,7 +2486,7 @@
       <c r="G73" s="8"/>
       <c r="H73" s="8"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="8" t="s">
         <v>6</v>
       </c>
@@ -2460,7 +2500,7 @@
       <c r="G74" s="8"/>
       <c r="H74" s="8"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="8" t="s">
         <v>8</v>
       </c>
@@ -2474,7 +2514,7 @@
       <c r="G75" s="8"/>
       <c r="H75" s="8"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>10</v>
       </c>
@@ -2486,7 +2526,7 @@
       <c r="G76" s="8"/>
       <c r="H76" s="8"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="8" t="s">
         <v>11</v>
       </c>
@@ -2512,7 +2552,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>78</v>
       </c>
@@ -2522,7 +2562,7 @@
       <c r="C78" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D78" s="10" t="s">
+      <c r="D78" t="s">
         <v>4</v>
       </c>
       <c r="E78" t="s">
@@ -2536,7 +2576,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>65</v>
       </c>
@@ -2546,21 +2586,21 @@
       <c r="C79" t="s">
         <v>18</v>
       </c>
-      <c r="D79" s="10" t="s">
+      <c r="D79" t="s">
         <v>4</v>
       </c>
       <c r="E79" t="s">
         <v>9</v>
       </c>
       <c r="F79" s="8"/>
-      <c r="G79" s="10" t="s">
+      <c r="G79" t="s">
         <v>20</v>
       </c>
       <c r="H79" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>80</v>
       </c>
@@ -2570,21 +2610,21 @@
       <c r="C80" t="s">
         <v>18</v>
       </c>
-      <c r="D80" s="10" t="s">
+      <c r="D80" t="s">
         <v>19</v>
       </c>
       <c r="E80" t="s">
         <v>9</v>
       </c>
       <c r="F80" s="8"/>
-      <c r="G80" s="10" t="s">
+      <c r="G80" t="s">
         <v>20</v>
       </c>
       <c r="H80" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>62</v>
       </c>
@@ -2594,20 +2634,20 @@
       <c r="C81" t="s">
         <v>18</v>
       </c>
-      <c r="D81" s="10" t="s">
+      <c r="D81" t="s">
         <v>19</v>
       </c>
       <c r="E81" t="s">
         <v>9</v>
       </c>
-      <c r="G81" s="10" t="s">
+      <c r="G81" t="s">
         <v>20</v>
       </c>
       <c r="H81" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>55</v>
       </c>
@@ -2617,7 +2657,7 @@
       <c r="C82" t="s">
         <v>18</v>
       </c>
-      <c r="D82" s="10" t="s">
+      <c r="D82" t="s">
         <v>44</v>
       </c>
       <c r="E82" t="s">
@@ -2630,7 +2670,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="3"/>
@@ -2640,7 +2680,7 @@
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>0</v>
       </c>
@@ -2654,7 +2694,7 @@
       <c r="G84" s="8"/>
       <c r="H84" s="8"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="8" t="s">
         <v>2</v>
       </c>
@@ -2668,11 +2708,11 @@
       <c r="G85" s="8"/>
       <c r="H85" s="8"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B86" s="10" t="s">
+      <c r="B86" t="s">
         <v>4</v>
       </c>
       <c r="C86" s="8"/>
@@ -2682,7 +2722,7 @@
       <c r="G86" s="8"/>
       <c r="H86" s="8"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="8" t="s">
         <v>5</v>
       </c>
@@ -2696,7 +2736,7 @@
       <c r="G87" s="8"/>
       <c r="H87" s="8"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="8" t="s">
         <v>6</v>
       </c>
@@ -2710,7 +2750,7 @@
       <c r="G88" s="8"/>
       <c r="H88" s="8"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="8" t="s">
         <v>8</v>
       </c>
@@ -2724,7 +2764,7 @@
       <c r="G89" s="8"/>
       <c r="H89" s="8"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>10</v>
       </c>
@@ -2736,7 +2776,7 @@
       <c r="G90" s="8"/>
       <c r="H90" s="8"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="8" t="s">
         <v>11</v>
       </c>
@@ -2762,7 +2802,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>82</v>
       </c>
@@ -2772,7 +2812,7 @@
       <c r="C92" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D92" s="10" t="s">
+      <c r="D92" t="s">
         <v>4</v>
       </c>
       <c r="E92" t="s">
@@ -2786,7 +2826,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>77</v>
       </c>
@@ -2796,21 +2836,21 @@
       <c r="C93" t="s">
         <v>18</v>
       </c>
-      <c r="D93" s="10" t="s">
+      <c r="D93" t="s">
         <v>4</v>
       </c>
       <c r="E93" t="s">
         <v>9</v>
       </c>
       <c r="F93" s="8"/>
-      <c r="G93" s="10" t="s">
+      <c r="G93" t="s">
         <v>20</v>
       </c>
       <c r="H93" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>62</v>
       </c>
@@ -2820,20 +2860,20 @@
       <c r="C94" t="s">
         <v>18</v>
       </c>
-      <c r="D94" s="10" t="s">
+      <c r="D94" t="s">
         <v>19</v>
       </c>
       <c r="E94" t="s">
         <v>9</v>
       </c>
-      <c r="G94" s="10" t="s">
+      <c r="G94" t="s">
         <v>20</v>
       </c>
       <c r="H94" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>55</v>
       </c>
@@ -2843,7 +2883,7 @@
       <c r="C95" t="s">
         <v>18</v>
       </c>
-      <c r="D95" s="10" t="s">
+      <c r="D95" t="s">
         <v>44</v>
       </c>
       <c r="E95" t="s">
@@ -2856,7 +2896,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="3"/>
@@ -2866,7 +2906,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>0</v>
       </c>
@@ -2880,7 +2920,7 @@
       <c r="G97" s="8"/>
       <c r="H97" s="8"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="8" t="s">
         <v>2</v>
       </c>
@@ -2894,11 +2934,11 @@
       <c r="G98" s="8"/>
       <c r="H98" s="8"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B99" s="10" t="s">
+      <c r="B99" t="s">
         <v>4</v>
       </c>
       <c r="C99" s="8"/>
@@ -2908,7 +2948,7 @@
       <c r="G99" s="8"/>
       <c r="H99" s="8"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="8" t="s">
         <v>5</v>
       </c>
@@ -2922,7 +2962,7 @@
       <c r="G100" s="8"/>
       <c r="H100" s="8"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="8" t="s">
         <v>6</v>
       </c>
@@ -2936,7 +2976,7 @@
       <c r="G101" s="8"/>
       <c r="H101" s="8"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="8" t="s">
         <v>8</v>
       </c>
@@ -2950,7 +2990,7 @@
       <c r="G102" s="8"/>
       <c r="H102" s="8"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
         <v>10</v>
       </c>
@@ -2962,7 +3002,7 @@
       <c r="G103" s="8"/>
       <c r="H103" s="8"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="8" t="s">
         <v>11</v>
       </c>
@@ -2988,7 +3028,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>172</v>
       </c>
@@ -2998,7 +3038,7 @@
       <c r="C105" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D105" s="10" t="s">
+      <c r="D105" t="s">
         <v>4</v>
       </c>
       <c r="E105" t="s">
@@ -3012,7 +3052,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>51</v>
       </c>
@@ -3022,21 +3062,21 @@
       <c r="C106" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D106" s="10" t="s">
+      <c r="D106" t="s">
         <v>4</v>
       </c>
       <c r="E106" t="s">
         <v>9</v>
       </c>
       <c r="F106" s="8"/>
-      <c r="G106" s="10" t="s">
+      <c r="G106" t="s">
         <v>20</v>
       </c>
       <c r="H106" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>56</v>
       </c>
@@ -3046,21 +3086,21 @@
       <c r="C107" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D107" s="10" t="s">
+      <c r="D107" t="s">
         <v>4</v>
       </c>
       <c r="E107" t="s">
         <v>9</v>
       </c>
       <c r="F107" s="8"/>
-      <c r="G107" s="10" t="s">
+      <c r="G107" t="s">
         <v>20</v>
       </c>
       <c r="H107" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>63</v>
       </c>
@@ -3070,21 +3110,21 @@
       <c r="C108" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D108" s="10" t="s">
+      <c r="D108" t="s">
         <v>4</v>
       </c>
       <c r="E108" t="s">
         <v>9</v>
       </c>
       <c r="F108" s="8"/>
-      <c r="G108" s="10" t="s">
+      <c r="G108" t="s">
         <v>20</v>
       </c>
       <c r="H108" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>71</v>
       </c>
@@ -3094,21 +3134,21 @@
       <c r="C109" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D109" s="10" t="s">
+      <c r="D109" t="s">
         <v>4</v>
       </c>
       <c r="E109" t="s">
         <v>9</v>
       </c>
       <c r="F109" s="8"/>
-      <c r="G109" s="10" t="s">
+      <c r="G109" t="s">
         <v>20</v>
       </c>
       <c r="H109" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>75</v>
       </c>
@@ -3118,21 +3158,21 @@
       <c r="C110" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D110" s="10" t="s">
+      <c r="D110" t="s">
         <v>4</v>
       </c>
       <c r="E110" t="s">
         <v>9</v>
       </c>
       <c r="F110" s="8"/>
-      <c r="G110" s="10" t="s">
+      <c r="G110" t="s">
         <v>20</v>
       </c>
       <c r="H110" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>78</v>
       </c>
@@ -3142,21 +3182,21 @@
       <c r="C111" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D111" s="10" t="s">
+      <c r="D111" t="s">
         <v>4</v>
       </c>
       <c r="E111" t="s">
         <v>9</v>
       </c>
       <c r="F111" s="8"/>
-      <c r="G111" s="10" t="s">
+      <c r="G111" t="s">
         <v>20</v>
       </c>
       <c r="H111" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>82</v>
       </c>
@@ -3166,21 +3206,21 @@
       <c r="C112" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D112" s="10" t="s">
+      <c r="D112" t="s">
         <v>4</v>
       </c>
       <c r="E112" t="s">
         <v>9</v>
       </c>
       <c r="F112" s="8"/>
-      <c r="G112" s="10" t="s">
+      <c r="G112" t="s">
         <v>20</v>
       </c>
       <c r="H112" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="3"/>
@@ -3190,7 +3230,7 @@
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
         <v>0</v>
       </c>
@@ -3204,7 +3244,7 @@
       <c r="G114" s="8"/>
       <c r="H114" s="8"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="8" t="s">
         <v>2</v>
       </c>
@@ -3218,11 +3258,11 @@
       <c r="G115" s="8"/>
       <c r="H115" s="8"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B116" s="10" t="s">
+      <c r="B116" t="s">
         <v>4</v>
       </c>
       <c r="C116" s="8"/>
@@ -3232,7 +3272,7 @@
       <c r="G116" s="8"/>
       <c r="H116" s="8"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="8" t="s">
         <v>5</v>
       </c>
@@ -3246,7 +3286,7 @@
       <c r="G117" s="8"/>
       <c r="H117" s="8"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="8" t="s">
         <v>6</v>
       </c>
@@ -3260,7 +3300,7 @@
       <c r="G118" s="8"/>
       <c r="H118" s="8"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="8" t="s">
         <v>8</v>
       </c>
@@ -3274,7 +3314,7 @@
       <c r="G119" s="8"/>
       <c r="H119" s="8"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
         <v>10</v>
       </c>
@@ -3286,7 +3326,7 @@
       <c r="G120" s="8"/>
       <c r="H120" s="8"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="8" t="s">
         <v>11</v>
       </c>
@@ -3312,7 +3352,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>85</v>
       </c>
@@ -3322,7 +3362,7 @@
       <c r="C122" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D122" s="10" t="s">
+      <c r="D122" t="s">
         <v>4</v>
       </c>
       <c r="E122" t="s">
@@ -3336,7 +3376,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>88</v>
       </c>
@@ -3347,21 +3387,21 @@
       <c r="C123" t="s">
         <v>18</v>
       </c>
-      <c r="D123" s="10" t="s">
+      <c r="D123" t="s">
         <v>4</v>
       </c>
       <c r="E123" t="s">
         <v>9</v>
       </c>
       <c r="F123" s="8"/>
-      <c r="G123" s="10" t="s">
+      <c r="G123" t="s">
         <v>20</v>
       </c>
       <c r="H123" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>48</v>
       </c>
@@ -3372,79 +3412,79 @@
       <c r="C124" t="s">
         <v>18</v>
       </c>
-      <c r="D124" s="10" t="s">
+      <c r="D124" t="s">
         <v>19</v>
       </c>
       <c r="E124" t="s">
         <v>9</v>
       </c>
       <c r="F124" s="8"/>
-      <c r="G124" s="10" t="s">
+      <c r="G124" t="s">
         <v>20</v>
       </c>
       <c r="H124" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>90</v>
       </c>
-      <c r="B125" s="14">
+      <c r="B125" s="13">
         <f>0.13/1000</f>
         <v>1.3000000000000002E-4</v>
       </c>
       <c r="C125" t="s">
         <v>18</v>
       </c>
-      <c r="D125" s="10" t="s">
+      <c r="D125" t="s">
         <v>4</v>
       </c>
       <c r="E125" t="s">
         <v>9</v>
       </c>
       <c r="F125" s="8"/>
-      <c r="G125" s="10" t="s">
+      <c r="G125" t="s">
         <v>20</v>
       </c>
       <c r="H125" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>92</v>
       </c>
-      <c r="B126" s="14">
+      <c r="B126" s="13">
         <f>0.075/1000</f>
         <v>7.4999999999999993E-5</v>
       </c>
       <c r="C126" t="s">
         <v>18</v>
       </c>
-      <c r="D126" s="10" t="s">
+      <c r="D126" t="s">
         <v>4</v>
       </c>
       <c r="E126" t="s">
         <v>9</v>
       </c>
       <c r="F126" s="8"/>
-      <c r="G126" s="10" t="s">
+      <c r="G126" t="s">
         <v>20</v>
       </c>
       <c r="H126" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>35</v>
       </c>
-      <c r="B127" s="16">
+      <c r="B127" s="15">
         <f>0.21/1000</f>
         <v>2.0999999999999998E-4</v>
       </c>
-      <c r="C127" s="10" t="s">
+      <c r="C127" t="s">
         <v>30</v>
       </c>
       <c r="E127" t="s">
@@ -3453,19 +3493,19 @@
       <c r="F127" t="s">
         <v>39</v>
       </c>
-      <c r="G127" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G127" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>94</v>
       </c>
-      <c r="B128" s="16">
+      <c r="B128" s="15">
         <f>0.0305/1000</f>
         <v>3.0499999999999999E-5</v>
       </c>
-      <c r="C128" s="10" t="s">
+      <c r="C128" t="s">
         <v>30</v>
       </c>
       <c r="E128" t="s">
@@ -3474,11 +3514,11 @@
       <c r="F128" t="s">
         <v>39</v>
       </c>
-      <c r="G128" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G128" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>95</v>
       </c>
@@ -3495,14 +3535,14 @@
       <c r="E129" t="s">
         <v>9</v>
       </c>
-      <c r="G129" s="10" t="s">
+      <c r="G129" t="s">
         <v>20</v>
       </c>
       <c r="H129" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="3"/>
@@ -3512,7 +3552,7 @@
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
         <v>0</v>
       </c>
@@ -3526,7 +3566,7 @@
       <c r="G131" s="8"/>
       <c r="H131" s="8"/>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A132" s="8" t="s">
         <v>2</v>
       </c>
@@ -3540,11 +3580,11 @@
       <c r="G132" s="8"/>
       <c r="H132" s="8"/>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A133" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B133" s="10" t="s">
+      <c r="B133" t="s">
         <v>4</v>
       </c>
       <c r="C133" s="8"/>
@@ -3554,7 +3594,7 @@
       <c r="G133" s="8"/>
       <c r="H133" s="8"/>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A134" s="8" t="s">
         <v>5</v>
       </c>
@@ -3568,7 +3608,7 @@
       <c r="G134" s="8"/>
       <c r="H134" s="8"/>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A135" s="8" t="s">
         <v>6</v>
       </c>
@@ -3582,7 +3622,7 @@
       <c r="G135" s="8"/>
       <c r="H135" s="8"/>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A136" s="8" t="s">
         <v>8</v>
       </c>
@@ -3596,7 +3636,7 @@
       <c r="G136" s="8"/>
       <c r="H136" s="8"/>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
         <v>10</v>
       </c>
@@ -3608,7 +3648,7 @@
       <c r="G137" s="8"/>
       <c r="H137" s="8"/>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A138" s="8" t="s">
         <v>11</v>
       </c>
@@ -3634,7 +3674,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>97</v>
       </c>
@@ -3644,7 +3684,7 @@
       <c r="C139" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D139" s="10" t="s">
+      <c r="D139" t="s">
         <v>4</v>
       </c>
       <c r="E139" t="s">
@@ -3658,165 +3698,158 @@
         <v>99</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>100</v>
       </c>
-      <c r="B140" s="14">
+      <c r="B140" s="13">
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="C140" t="s">
         <v>30</v>
       </c>
-      <c r="D140" s="10"/>
       <c r="E140" t="s">
         <v>9</v>
       </c>
-      <c r="F140" s="10" t="s">
+      <c r="F140" t="s">
         <v>39</v>
       </c>
-      <c r="G140" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K140" s="15"/>
-    </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G140" t="s">
+        <v>31</v>
+      </c>
+      <c r="K140" s="14"/>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>37</v>
       </c>
-      <c r="B141" s="14">
+      <c r="B141" s="13">
         <v>6.3E-5</v>
       </c>
       <c r="C141" t="s">
         <v>30</v>
       </c>
-      <c r="D141" s="10"/>
       <c r="E141" t="s">
         <v>9</v>
       </c>
-      <c r="F141" s="10" t="s">
+      <c r="F141" t="s">
         <v>39</v>
       </c>
-      <c r="G141" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K141" s="15"/>
-    </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G141" t="s">
+        <v>31</v>
+      </c>
+      <c r="K141" s="14"/>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>101</v>
       </c>
-      <c r="B142" s="14">
+      <c r="B142" s="13">
         <v>3.93E-5</v>
       </c>
       <c r="C142" t="s">
         <v>30</v>
       </c>
-      <c r="D142" s="10"/>
       <c r="E142" t="s">
         <v>9</v>
       </c>
-      <c r="F142" s="10" t="s">
+      <c r="F142" t="s">
         <v>39</v>
       </c>
-      <c r="G142" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K142" s="15"/>
-    </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G142" t="s">
+        <v>31</v>
+      </c>
+      <c r="K142" s="14"/>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>102</v>
       </c>
-      <c r="B143" s="14">
+      <c r="B143" s="13">
         <v>2.5799999999999999E-6</v>
       </c>
       <c r="C143" t="s">
         <v>30</v>
       </c>
-      <c r="D143" s="10"/>
       <c r="E143" t="s">
         <v>9</v>
       </c>
-      <c r="F143" s="10" t="s">
+      <c r="F143" t="s">
         <v>39</v>
       </c>
-      <c r="G143" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K143" s="15"/>
-    </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G143" t="s">
+        <v>31</v>
+      </c>
+      <c r="K143" s="14"/>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>103</v>
       </c>
-      <c r="B144" s="14">
+      <c r="B144" s="13">
         <v>2.8099999999999999E-7</v>
       </c>
       <c r="C144" t="s">
         <v>30</v>
       </c>
-      <c r="D144" s="10"/>
       <c r="E144" t="s">
         <v>9</v>
       </c>
-      <c r="F144" s="10" t="s">
+      <c r="F144" t="s">
         <v>39</v>
       </c>
-      <c r="G144" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K144" s="15"/>
-    </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G144" t="s">
+        <v>31</v>
+      </c>
+      <c r="K144" s="14"/>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>104</v>
       </c>
-      <c r="B145" s="14">
+      <c r="B145" s="13">
         <v>8.8999999999999995E-7</v>
       </c>
       <c r="C145" t="s">
         <v>30</v>
       </c>
-      <c r="D145" s="10"/>
       <c r="E145" t="s">
         <v>9</v>
       </c>
-      <c r="F145" s="10" t="s">
+      <c r="F145" t="s">
         <v>39</v>
       </c>
-      <c r="G145" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K145" s="15"/>
-    </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G145" t="s">
+        <v>31</v>
+      </c>
+      <c r="K145" s="14"/>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>105</v>
       </c>
-      <c r="B146" s="14">
+      <c r="B146" s="13">
         <v>8.8999999999999995E-7</v>
       </c>
       <c r="C146" t="s">
         <v>30</v>
       </c>
-      <c r="D146" s="10"/>
       <c r="E146" t="s">
         <v>9</v>
       </c>
-      <c r="F146" s="10" t="s">
+      <c r="F146" t="s">
         <v>39</v>
       </c>
-      <c r="G146" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K146" s="15"/>
-    </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G146" t="s">
+        <v>31</v>
+      </c>
+      <c r="K146" s="14"/>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>106</v>
       </c>
-      <c r="B147" s="14">
+      <c r="B147" s="13">
         <v>1.5000000000000001E-12</v>
       </c>
       <c r="C147" t="s">
@@ -3825,19 +3858,19 @@
       <c r="E147" t="s">
         <v>9</v>
       </c>
-      <c r="F147" s="10" t="s">
+      <c r="F147" t="s">
         <v>39</v>
       </c>
-      <c r="G147" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K147" s="15"/>
-    </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G147" t="s">
+        <v>31</v>
+      </c>
+      <c r="K147" s="14"/>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>107</v>
       </c>
-      <c r="B148" s="14">
+      <c r="B148" s="13">
         <v>2.4999999999999999E-13</v>
       </c>
       <c r="C148" t="s">
@@ -3846,19 +3879,19 @@
       <c r="E148" t="s">
         <v>9</v>
       </c>
-      <c r="F148" s="10" t="s">
+      <c r="F148" t="s">
         <v>39</v>
       </c>
-      <c r="G148" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K148" s="15"/>
-    </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G148" t="s">
+        <v>31</v>
+      </c>
+      <c r="K148" s="14"/>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>108</v>
       </c>
-      <c r="B149" s="14">
+      <c r="B149" s="13">
         <v>9.9999999999999991E-11</v>
       </c>
       <c r="C149" t="s">
@@ -3867,19 +3900,19 @@
       <c r="E149" t="s">
         <v>9</v>
       </c>
-      <c r="F149" s="10" t="s">
+      <c r="F149" t="s">
         <v>39</v>
       </c>
-      <c r="G149" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K149" s="15"/>
-    </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G149" t="s">
+        <v>31</v>
+      </c>
+      <c r="K149" s="14"/>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>109</v>
       </c>
-      <c r="B150" s="14">
+      <c r="B150" s="13">
         <v>1.2E-10</v>
       </c>
       <c r="C150" t="s">
@@ -3888,19 +3921,19 @@
       <c r="E150" t="s">
         <v>9</v>
       </c>
-      <c r="F150" s="10" t="s">
+      <c r="F150" t="s">
         <v>39</v>
       </c>
-      <c r="G150" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K150" s="15"/>
-    </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G150" t="s">
+        <v>31</v>
+      </c>
+      <c r="K150" s="14"/>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>110</v>
       </c>
-      <c r="B151" s="14">
+      <c r="B151" s="13">
         <v>7.5999999999999999E-13</v>
       </c>
       <c r="C151" t="s">
@@ -3909,19 +3942,19 @@
       <c r="E151" t="s">
         <v>9</v>
       </c>
-      <c r="F151" s="10" t="s">
+      <c r="F151" t="s">
         <v>39</v>
       </c>
-      <c r="G151" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K151" s="15"/>
-    </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G151" t="s">
+        <v>31</v>
+      </c>
+      <c r="K151" s="14"/>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>111</v>
       </c>
-      <c r="B152" s="14">
+      <c r="B152" s="13">
         <v>7.5999999999999992E-14</v>
       </c>
       <c r="C152" t="s">
@@ -3930,19 +3963,19 @@
       <c r="E152" t="s">
         <v>9</v>
       </c>
-      <c r="F152" s="10" t="s">
+      <c r="F152" t="s">
         <v>39</v>
       </c>
-      <c r="G152" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K152" s="15"/>
-    </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G152" t="s">
+        <v>31</v>
+      </c>
+      <c r="K152" s="14"/>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>112</v>
       </c>
-      <c r="B153" s="14">
+      <c r="B153" s="13">
         <v>5.0999999999999995E-13</v>
       </c>
       <c r="C153" t="s">
@@ -3951,19 +3984,19 @@
       <c r="E153" t="s">
         <v>9</v>
       </c>
-      <c r="F153" s="10" t="s">
+      <c r="F153" t="s">
         <v>39</v>
       </c>
-      <c r="G153" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K153" s="15"/>
-    </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G153" t="s">
+        <v>31</v>
+      </c>
+      <c r="K153" s="14"/>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>113</v>
       </c>
-      <c r="B154" s="14">
+      <c r="B154" s="13">
         <v>1.1199999999999999E-11</v>
       </c>
       <c r="C154" t="s">
@@ -3972,19 +4005,19 @@
       <c r="E154" t="s">
         <v>9</v>
       </c>
-      <c r="F154" s="10" t="s">
+      <c r="F154" t="s">
         <v>39</v>
       </c>
-      <c r="G154" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K154" s="15"/>
-    </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G154" t="s">
+        <v>31</v>
+      </c>
+      <c r="K154" s="14"/>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>114</v>
       </c>
-      <c r="B155" s="14">
+      <c r="B155" s="13">
         <v>1.5000000000000001E-12</v>
       </c>
       <c r="C155" t="s">
@@ -3993,19 +4026,19 @@
       <c r="E155" t="s">
         <v>9</v>
       </c>
-      <c r="F155" s="10" t="s">
+      <c r="F155" t="s">
         <v>39</v>
       </c>
-      <c r="G155" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K155" s="15"/>
-    </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G155" t="s">
+        <v>31</v>
+      </c>
+      <c r="K155" s="14"/>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>115</v>
       </c>
-      <c r="B156" s="14">
+      <c r="B156" s="13">
         <v>5.6000000000000004E-13</v>
       </c>
       <c r="C156" t="s">
@@ -4014,19 +4047,19 @@
       <c r="E156" t="s">
         <v>9</v>
       </c>
-      <c r="F156" s="10" t="s">
+      <c r="F156" t="s">
         <v>39</v>
       </c>
-      <c r="G156" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K156" s="15"/>
-    </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G156" t="s">
+        <v>31</v>
+      </c>
+      <c r="K156" s="14"/>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>116</v>
       </c>
-      <c r="B157" s="14">
+      <c r="B157" s="13">
         <v>8.3999999999999995E-13</v>
       </c>
       <c r="C157" t="s">
@@ -4035,19 +4068,19 @@
       <c r="E157" t="s">
         <v>9</v>
       </c>
-      <c r="F157" s="10" t="s">
+      <c r="F157" t="s">
         <v>39</v>
       </c>
-      <c r="G157" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K157" s="15"/>
-    </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G157" t="s">
+        <v>31</v>
+      </c>
+      <c r="K157" s="14"/>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>117</v>
       </c>
-      <c r="B158" s="14">
+      <c r="B158" s="13">
         <v>8.3999999999999995E-13</v>
       </c>
       <c r="C158" t="s">
@@ -4056,19 +4089,19 @@
       <c r="E158" t="s">
         <v>9</v>
       </c>
-      <c r="F158" s="10" t="s">
+      <c r="F158" t="s">
         <v>39</v>
       </c>
-      <c r="G158" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K158" s="15"/>
-    </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G158" t="s">
+        <v>31</v>
+      </c>
+      <c r="K158" s="14"/>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>118</v>
       </c>
-      <c r="B159" s="14">
+      <c r="B159" s="13">
         <v>8.3999999999999995E-13</v>
       </c>
       <c r="C159" t="s">
@@ -4077,15 +4110,15 @@
       <c r="E159" t="s">
         <v>9</v>
       </c>
-      <c r="F159" s="10" t="s">
+      <c r="F159" t="s">
         <v>39</v>
       </c>
-      <c r="G159" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K159" s="15"/>
-    </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G159" t="s">
+        <v>31</v>
+      </c>
+      <c r="K159" s="14"/>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="3"/>
@@ -4095,7 +4128,7 @@
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
         <v>0</v>
       </c>
@@ -4110,11 +4143,11 @@
       <c r="H161" s="8"/>
       <c r="I161" s="8"/>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A162" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B162" s="10" t="s">
+      <c r="B162" t="s">
         <v>158</v>
       </c>
       <c r="C162" s="8"/>
@@ -4125,11 +4158,11 @@
       <c r="H162" s="8"/>
       <c r="I162" s="8"/>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A163" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B163" s="10" t="s">
+      <c r="B163" t="s">
         <v>4</v>
       </c>
       <c r="C163" s="8"/>
@@ -4140,7 +4173,7 @@
       <c r="H163" s="8"/>
       <c r="I163" s="8"/>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A164" s="8" t="s">
         <v>5</v>
       </c>
@@ -4155,7 +4188,7 @@
       <c r="H164" s="8"/>
       <c r="I164" s="8"/>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A165" s="8" t="s">
         <v>6</v>
       </c>
@@ -4170,7 +4203,7 @@
       <c r="H165" s="8"/>
       <c r="I165" s="8"/>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A166" s="8" t="s">
         <v>8</v>
       </c>
@@ -4185,7 +4218,7 @@
       <c r="H166" s="8"/>
       <c r="I166" s="8"/>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
         <v>10</v>
       </c>
@@ -4198,7 +4231,7 @@
       <c r="H167" s="8"/>
       <c r="I167" s="8"/>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A168" s="8" t="s">
         <v>11</v>
       </c>
@@ -4225,7 +4258,7 @@
       </c>
       <c r="I168" s="8"/>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A169" s="8" t="s">
         <v>29</v>
       </c>
@@ -4248,11 +4281,11 @@
       <c r="H169" s="8"/>
       <c r="I169" s="8"/>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A170" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="B170" s="14">
+      <c r="B170" s="13">
         <v>1.4039999999999999E-5</v>
       </c>
       <c r="C170" s="8" t="s">
@@ -4270,9 +4303,9 @@
       </c>
       <c r="H170" s="8"/>
       <c r="I170" s="8"/>
-      <c r="K170" s="15"/>
-    </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K170" s="14"/>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A171" s="8" t="s">
         <v>129</v>
       </c>
@@ -4294,13 +4327,13 @@
       </c>
       <c r="H171" s="8"/>
       <c r="I171" s="8"/>
-      <c r="K171" s="15"/>
-    </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K171" s="14"/>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A172" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="B172" s="14">
+      <c r="B172" s="13">
         <v>8.5109999999999986E-6</v>
       </c>
       <c r="C172" s="8" t="s">
@@ -4318,13 +4351,13 @@
       </c>
       <c r="H172" s="8"/>
       <c r="I172" s="8"/>
-      <c r="K172" s="15"/>
-    </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K172" s="14"/>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A173" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B173" s="14">
+      <c r="B173" s="13">
         <v>8.5109999999999986E-6</v>
       </c>
       <c r="C173" s="8" t="s">
@@ -4342,9 +4375,9 @@
       </c>
       <c r="H173" s="8"/>
       <c r="I173" s="8"/>
-      <c r="K173" s="15"/>
-    </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K173" s="14"/>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A174" s="8" t="s">
         <v>124</v>
       </c>
@@ -4354,7 +4387,7 @@
       <c r="C174" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D174" s="10" t="s">
+      <c r="D174" t="s">
         <v>4</v>
       </c>
       <c r="E174" s="8" t="s">
@@ -4368,13 +4401,13 @@
         <v>125</v>
       </c>
       <c r="I174" s="8"/>
-      <c r="K174" s="15"/>
-    </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K174" s="14"/>
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A175" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="B175" s="14">
+      <c r="B175" s="13">
         <v>9.8720000000000014E-6</v>
       </c>
       <c r="C175" s="8" t="s">
@@ -4394,13 +4427,13 @@
         <v>135</v>
       </c>
       <c r="I175" s="8"/>
-      <c r="K175" s="15"/>
-    </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K175" s="14"/>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A176" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="B176" s="14">
+      <c r="B176" s="13">
         <v>4.7780000000000002E-8</v>
       </c>
       <c r="C176" s="8" t="s">
@@ -4420,13 +4453,13 @@
         <v>137</v>
       </c>
       <c r="I176" s="8"/>
-      <c r="K176" s="15"/>
-    </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K176" s="14"/>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A177" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="B177" s="14">
+      <c r="B177" s="13">
         <v>1.9410000000000001E-6</v>
       </c>
       <c r="C177" s="8" t="s">
@@ -4446,9 +4479,9 @@
         <v>139</v>
       </c>
       <c r="I177" s="8"/>
-      <c r="K177" s="15"/>
-    </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K177" s="14"/>
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A178" s="8" t="s">
         <v>140</v>
       </c>
@@ -4472,13 +4505,13 @@
         <v>140</v>
       </c>
       <c r="I178" s="8"/>
-      <c r="K178" s="15"/>
-    </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K178" s="14"/>
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A179" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B179" s="14">
+      <c r="B179" s="13">
         <v>1.021E-3</v>
       </c>
       <c r="C179" s="8" t="s">
@@ -4498,13 +4531,13 @@
         <v>141</v>
       </c>
       <c r="I179" s="8"/>
-      <c r="K179" s="15"/>
-    </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K179" s="14"/>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A180" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="B180" s="14">
+      <c r="B180" s="13">
         <v>1.3140000000000001E-3</v>
       </c>
       <c r="C180" s="8" t="s">
@@ -4524,13 +4557,13 @@
         <v>144</v>
       </c>
       <c r="I180" s="8"/>
-      <c r="K180" s="15"/>
-    </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K180" s="14"/>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A181" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="B181" s="14">
+      <c r="B181" s="13">
         <v>8.2189999999999997E-8</v>
       </c>
       <c r="C181" s="8" t="s">
@@ -4550,13 +4583,13 @@
         <v>147</v>
       </c>
       <c r="I181" s="8"/>
-      <c r="K181" s="15"/>
-    </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K181" s="14"/>
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A182" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="B182" s="14">
+      <c r="B182" s="13">
         <v>1.9740000000000001E-5</v>
       </c>
       <c r="C182" s="8" t="s">
@@ -4576,13 +4609,13 @@
         <v>149</v>
       </c>
       <c r="I182" s="8"/>
-      <c r="K182" s="15"/>
-    </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K182" s="14"/>
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A183" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="B183" s="14">
+      <c r="B183" s="13">
         <v>1.021E-3</v>
       </c>
       <c r="C183" s="8" t="s">
@@ -4602,13 +4635,13 @@
         <v>151</v>
       </c>
       <c r="I183" s="8"/>
-      <c r="K183" s="15"/>
-    </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K183" s="14"/>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A184" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="B184" s="14">
+      <c r="B184" s="13">
         <v>1.7350000000000002E-5</v>
       </c>
       <c r="C184" s="8" t="s">
@@ -4628,13 +4661,13 @@
         <v>153</v>
       </c>
       <c r="I184" s="8"/>
-      <c r="K184" s="15"/>
-    </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K184" s="14"/>
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A185" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="B185" s="14">
+      <c r="B185" s="13">
         <v>3.6990000000000003E-5</v>
       </c>
       <c r="C185" s="8" t="s">
@@ -4654,9 +4687,9 @@
         <v>155</v>
       </c>
       <c r="I185" s="8"/>
-      <c r="K185" s="15"/>
-    </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K185" s="14"/>
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A186" s="8" t="s">
         <v>156</v>
       </c>
@@ -4680,9 +4713,9 @@
         <v>157</v>
       </c>
       <c r="I186" s="8"/>
-      <c r="K186" s="15"/>
-    </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K186" s="14"/>
+    </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="3"/>
@@ -4691,9 +4724,9 @@
       <c r="F187" s="2"/>
       <c r="G187" s="2"/>
       <c r="H187" s="2"/>
-      <c r="K187" s="15"/>
-    </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K187" s="14"/>
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A188" s="1" t="s">
         <v>0</v>
       </c>
@@ -4706,13 +4739,13 @@
       <c r="F188" s="8"/>
       <c r="G188" s="8"/>
       <c r="H188" s="8"/>
-      <c r="K188" s="15"/>
-    </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K188" s="14"/>
+    </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A189" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B189" s="10" t="s">
+      <c r="B189" t="s">
         <v>159</v>
       </c>
       <c r="C189" s="8"/>
@@ -4721,13 +4754,13 @@
       <c r="F189" s="8"/>
       <c r="G189" s="8"/>
       <c r="H189" s="8"/>
-      <c r="K189" s="15"/>
-    </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K189" s="14"/>
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A190" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B190" s="10" t="s">
+      <c r="B190" t="s">
         <v>4</v>
       </c>
       <c r="C190" s="8"/>
@@ -4737,7 +4770,7 @@
       <c r="G190" s="8"/>
       <c r="H190" s="8"/>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A191" s="8" t="s">
         <v>5</v>
       </c>
@@ -4751,11 +4784,11 @@
       <c r="G191" s="8"/>
       <c r="H191" s="8"/>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A192" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B192" s="10" t="s">
+      <c r="B192" t="s">
         <v>123</v>
       </c>
       <c r="C192" s="8"/>
@@ -4765,7 +4798,7 @@
       <c r="G192" s="8"/>
       <c r="H192" s="8"/>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193" s="8" t="s">
         <v>8</v>
       </c>
@@ -4779,7 +4812,7 @@
       <c r="G193" s="8"/>
       <c r="H193" s="8"/>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
         <v>10</v>
       </c>
@@ -4791,7 +4824,7 @@
       <c r="G194" s="8"/>
       <c r="H194" s="8"/>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195" s="8" t="s">
         <v>11</v>
       </c>
@@ -4817,7 +4850,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196" s="8" t="s">
         <v>123</v>
       </c>
@@ -4827,7 +4860,7 @@
       <c r="C196" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D196" s="10" t="s">
+      <c r="D196" t="s">
         <v>4</v>
       </c>
       <c r="E196" s="8" t="s">
@@ -4841,7 +4874,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A197" s="8" t="s">
         <v>124</v>
       </c>
@@ -4851,21 +4884,21 @@
       <c r="C197" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D197" s="10" t="s">
+      <c r="D197" t="s">
         <v>4</v>
       </c>
       <c r="E197" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F197" s="8"/>
-      <c r="G197" s="10" t="s">
+      <c r="G197" t="s">
         <v>20</v>
       </c>
       <c r="H197" s="8" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>55</v>
       </c>
@@ -4876,7 +4909,7 @@
       <c r="C198" t="s">
         <v>18</v>
       </c>
-      <c r="D198" s="10" t="s">
+      <c r="D198" t="s">
         <v>44</v>
       </c>
       <c r="E198" t="s">
@@ -4889,30 +4922,30 @@
         <v>43</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A199" s="10" t="s">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A199" t="s">
         <v>29</v>
       </c>
-      <c r="B199" s="18">
+      <c r="B199" s="15">
         <f>0.447/1000</f>
         <v>4.4700000000000002E-4</v>
       </c>
-      <c r="C199" s="10" t="s">
+      <c r="C199" t="s">
         <v>30</v>
       </c>
       <c r="D199" s="8"/>
-      <c r="E199" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F199" s="10" t="s">
+      <c r="E199" t="s">
+        <v>9</v>
+      </c>
+      <c r="F199" t="s">
         <v>39</v>
       </c>
-      <c r="G199" s="10" t="s">
+      <c r="G199" t="s">
         <v>31</v>
       </c>
       <c r="H199" s="8"/>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="3"/>
@@ -4922,7 +4955,7 @@
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
         <v>0</v>
       </c>
@@ -4936,11 +4969,11 @@
       <c r="G201" s="8"/>
       <c r="H201" s="8"/>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A202" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B202" s="10" t="s">
+      <c r="B202" t="s">
         <v>159</v>
       </c>
       <c r="C202" s="8"/>
@@ -4950,11 +4983,11 @@
       <c r="G202" s="8"/>
       <c r="H202" s="8"/>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A203" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B203" s="10" t="s">
+      <c r="B203" t="s">
         <v>4</v>
       </c>
       <c r="C203" s="8"/>
@@ -4964,7 +4997,7 @@
       <c r="G203" s="8"/>
       <c r="H203" s="8"/>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A204" s="8" t="s">
         <v>5</v>
       </c>
@@ -4978,11 +5011,11 @@
       <c r="G204" s="8"/>
       <c r="H204" s="8"/>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B205" s="10" t="s">
+      <c r="B205" t="s">
         <v>160</v>
       </c>
       <c r="C205" s="8"/>
@@ -4992,7 +5025,7 @@
       <c r="G205" s="8"/>
       <c r="H205" s="8"/>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206" s="8" t="s">
         <v>8</v>
       </c>
@@ -5006,7 +5039,7 @@
       <c r="G206" s="8"/>
       <c r="H206" s="8"/>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
         <v>10</v>
       </c>
@@ -5018,7 +5051,7 @@
       <c r="G207" s="8"/>
       <c r="H207" s="8"/>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208" s="8" t="s">
         <v>11</v>
       </c>
@@ -5044,7 +5077,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A209" s="8" t="s">
         <v>160</v>
       </c>
@@ -5054,7 +5087,7 @@
       <c r="C209" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D209" s="10" t="s">
+      <c r="D209" t="s">
         <v>4</v>
       </c>
       <c r="E209" s="8" t="s">
@@ -5068,7 +5101,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A210" s="8" t="s">
         <v>124</v>
       </c>
@@ -5078,21 +5111,21 @@
       <c r="C210" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D210" s="10" t="s">
+      <c r="D210" t="s">
         <v>4</v>
       </c>
       <c r="E210" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F210" s="8"/>
-      <c r="G210" s="10" t="s">
+      <c r="G210" t="s">
         <v>20</v>
       </c>
       <c r="H210" s="8" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>55</v>
       </c>
@@ -5103,7 +5136,7 @@
       <c r="C211" t="s">
         <v>18</v>
       </c>
-      <c r="D211" s="10" t="s">
+      <c r="D211" t="s">
         <v>44</v>
       </c>
       <c r="E211" t="s">
@@ -5116,30 +5149,30 @@
         <v>43</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A212" s="10" t="s">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A212" t="s">
         <v>29</v>
       </c>
-      <c r="B212" s="18">
+      <c r="B212" s="15">
         <f>0.309/1000</f>
         <v>3.0899999999999998E-4</v>
       </c>
-      <c r="C212" s="10" t="s">
+      <c r="C212" t="s">
         <v>30</v>
       </c>
       <c r="D212" s="8"/>
-      <c r="E212" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F212" s="10" t="s">
+      <c r="E212" t="s">
+        <v>9</v>
+      </c>
+      <c r="F212" t="s">
         <v>39</v>
       </c>
-      <c r="G212" s="10" t="s">
+      <c r="G212" t="s">
         <v>31</v>
       </c>
       <c r="H212" s="8"/>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="3"/>
@@ -5149,7 +5182,7 @@
       <c r="G213" s="2"/>
       <c r="H213" s="2"/>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A214" s="1" t="s">
         <v>0</v>
       </c>
@@ -5163,11 +5196,11 @@
       <c r="G214" s="8"/>
       <c r="H214" s="8"/>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A215" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B215" s="10" t="s">
+      <c r="B215" t="s">
         <v>164</v>
       </c>
       <c r="C215" s="8"/>
@@ -5177,11 +5210,11 @@
       <c r="G215" s="8"/>
       <c r="H215" s="8"/>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A216" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B216" s="10" t="s">
+      <c r="B216" t="s">
         <v>4</v>
       </c>
       <c r="C216" s="8"/>
@@ -5191,7 +5224,7 @@
       <c r="G216" s="8"/>
       <c r="H216" s="8"/>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A217" s="8" t="s">
         <v>5</v>
       </c>
@@ -5205,11 +5238,11 @@
       <c r="G217" s="8"/>
       <c r="H217" s="8"/>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A218" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B218" s="10" t="s">
+      <c r="B218" t="s">
         <v>163</v>
       </c>
       <c r="C218" s="8"/>
@@ -5219,11 +5252,11 @@
       <c r="G218" s="8"/>
       <c r="H218" s="8"/>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A219" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B219" s="10" t="s">
+      <c r="B219" t="s">
         <v>23</v>
       </c>
       <c r="C219" s="8"/>
@@ -5233,7 +5266,7 @@
       <c r="G219" s="8"/>
       <c r="H219" s="8"/>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A220" s="1" t="s">
         <v>10</v>
       </c>
@@ -5245,7 +5278,7 @@
       <c r="G220" s="8"/>
       <c r="H220" s="8"/>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A221" s="8" t="s">
         <v>11</v>
       </c>
@@ -5271,7 +5304,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A222" s="8" t="s">
         <v>163</v>
       </c>
@@ -5281,10 +5314,10 @@
       <c r="C222" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D222" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E222" s="10" t="s">
+      <c r="D222" t="s">
+        <v>4</v>
+      </c>
+      <c r="E222" t="s">
         <v>23</v>
       </c>
       <c r="F222" s="8"/>
@@ -5295,7 +5328,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>85</v>
       </c>
@@ -5305,21 +5338,21 @@
       <c r="C223" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D223" s="10" t="s">
+      <c r="D223" t="s">
         <v>4</v>
       </c>
       <c r="E223" t="s">
         <v>9</v>
       </c>
       <c r="F223" s="8"/>
-      <c r="G223" s="10" t="s">
+      <c r="G223" t="s">
         <v>20</v>
       </c>
       <c r="H223" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A224" s="8" t="s">
         <v>160</v>
       </c>
@@ -5329,21 +5362,21 @@
       <c r="C224" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D224" s="10" t="s">
+      <c r="D224" t="s">
         <v>4</v>
       </c>
       <c r="E224" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F224" s="8"/>
-      <c r="G224" s="10" t="s">
+      <c r="G224" t="s">
         <v>20</v>
       </c>
       <c r="H224" s="8" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A225" s="8" t="s">
         <v>165</v>
       </c>
@@ -5353,21 +5386,21 @@
       <c r="C225" t="s">
         <v>18</v>
       </c>
-      <c r="D225" s="10" t="s">
+      <c r="D225" t="s">
         <v>19</v>
       </c>
       <c r="E225" s="8" t="s">
         <v>23</v>
       </c>
       <c r="F225" s="8"/>
-      <c r="G225" s="10" t="s">
+      <c r="G225" t="s">
         <v>20</v>
       </c>
       <c r="H225" s="8" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A226" s="8" t="s">
         <v>161</v>
       </c>
@@ -5377,43 +5410,43 @@
       <c r="C226" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D226" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E226" s="10" t="s">
+      <c r="D226" t="s">
+        <v>4</v>
+      </c>
+      <c r="E226" t="s">
         <v>24</v>
       </c>
       <c r="F226" s="8"/>
-      <c r="G226" s="10" t="s">
+      <c r="G226" t="s">
         <v>20</v>
       </c>
       <c r="H226" s="8" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A227" s="10" t="s">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A227" t="s">
         <v>29</v>
       </c>
-      <c r="B227" s="18">
+      <c r="B227" s="15">
         <v>-6.7299999999999999E-2</v>
       </c>
-      <c r="C227" s="10" t="s">
+      <c r="C227" t="s">
         <v>30</v>
       </c>
       <c r="D227" s="8"/>
-      <c r="E227" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F227" s="10" t="s">
+      <c r="E227" t="s">
+        <v>9</v>
+      </c>
+      <c r="F227" t="s">
         <v>39</v>
       </c>
-      <c r="G227" s="10" t="s">
+      <c r="G227" t="s">
         <v>31</v>
       </c>
       <c r="H227" s="8"/>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="3"/>
@@ -5423,7 +5456,7 @@
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A229" s="1" t="s">
         <v>0</v>
       </c>
@@ -5437,11 +5470,11 @@
       <c r="G229" s="8"/>
       <c r="H229" s="8"/>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A230" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B230" s="10" t="s">
+      <c r="B230" t="s">
         <v>162</v>
       </c>
       <c r="C230" s="8"/>
@@ -5451,11 +5484,11 @@
       <c r="G230" s="8"/>
       <c r="H230" s="8"/>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A231" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B231" s="10" t="s">
+      <c r="B231" t="s">
         <v>4</v>
       </c>
       <c r="C231" s="8"/>
@@ -5465,7 +5498,7 @@
       <c r="G231" s="8"/>
       <c r="H231" s="8"/>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A232" s="8" t="s">
         <v>5</v>
       </c>
@@ -5479,11 +5512,11 @@
       <c r="G232" s="8"/>
       <c r="H232" s="8"/>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A233" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B233" s="10" t="s">
+      <c r="B233" t="s">
         <v>161</v>
       </c>
       <c r="C233" s="8"/>
@@ -5493,11 +5526,11 @@
       <c r="G233" s="8"/>
       <c r="H233" s="8"/>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A234" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B234" s="10" t="s">
+      <c r="B234" t="s">
         <v>24</v>
       </c>
       <c r="C234" s="8"/>
@@ -5507,7 +5540,7 @@
       <c r="G234" s="8"/>
       <c r="H234" s="8"/>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A235" s="1" t="s">
         <v>10</v>
       </c>
@@ -5519,7 +5552,7 @@
       <c r="G235" s="8"/>
       <c r="H235" s="8"/>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A236" s="8" t="s">
         <v>11</v>
       </c>
@@ -5545,7 +5578,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A237" s="8" t="s">
         <v>161</v>
       </c>
@@ -5555,10 +5588,10 @@
       <c r="C237" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D237" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E237" s="10" t="s">
+      <c r="D237" t="s">
+        <v>4</v>
+      </c>
+      <c r="E237" t="s">
         <v>24</v>
       </c>
       <c r="F237" s="8"/>
@@ -5569,7 +5602,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>85</v>
       </c>
@@ -5579,21 +5612,21 @@
       <c r="C238" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D238" s="10" t="s">
+      <c r="D238" t="s">
         <v>4</v>
       </c>
       <c r="E238" t="s">
         <v>9</v>
       </c>
       <c r="F238" s="8"/>
-      <c r="G238" s="10" t="s">
+      <c r="G238" t="s">
         <v>20</v>
       </c>
       <c r="H238" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A239" s="8" t="s">
         <v>160</v>
       </c>
@@ -5603,21 +5636,21 @@
       <c r="C239" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D239" s="10" t="s">
+      <c r="D239" t="s">
         <v>4</v>
       </c>
       <c r="E239" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F239" s="8"/>
-      <c r="G239" s="10" t="s">
+      <c r="G239" t="s">
         <v>20</v>
       </c>
       <c r="H239" s="8" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>55</v>
       </c>
@@ -5627,7 +5660,7 @@
       <c r="C240" t="s">
         <v>18</v>
       </c>
-      <c r="D240" s="10" t="s">
+      <c r="D240" t="s">
         <v>44</v>
       </c>
       <c r="E240" t="s">
@@ -5640,7 +5673,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A241" s="8" t="s">
         <v>163</v>
       </c>
@@ -5650,10 +5683,10 @@
       <c r="C241" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D241" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E241" s="10" t="s">
+      <c r="D241" t="s">
+        <v>4</v>
+      </c>
+      <c r="E241" t="s">
         <v>23</v>
       </c>
       <c r="F241" s="8"/>
@@ -5664,29 +5697,29 @@
         <v>163</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A242" s="10" t="s">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A242" t="s">
         <v>29</v>
       </c>
-      <c r="B242" s="18">
+      <c r="B242" s="15">
         <v>-0.36699999999999999</v>
       </c>
-      <c r="C242" s="10" t="s">
+      <c r="C242" t="s">
         <v>30</v>
       </c>
       <c r="D242" s="8"/>
-      <c r="E242" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F242" s="10" t="s">
+      <c r="E242" t="s">
+        <v>9</v>
+      </c>
+      <c r="F242" t="s">
         <v>39</v>
       </c>
-      <c r="G242" s="10" t="s">
+      <c r="G242" t="s">
         <v>31</v>
       </c>
       <c r="H242" s="8"/>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="3"/>
@@ -5696,7 +5729,7 @@
       <c r="G243" s="2"/>
       <c r="H243" s="2"/>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A244" s="1" t="s">
         <v>0</v>
       </c>
@@ -5710,7 +5743,7 @@
       <c r="G244" s="8"/>
       <c r="H244" s="8"/>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A245" s="8" t="s">
         <v>2</v>
       </c>
@@ -5724,11 +5757,11 @@
       <c r="G245" s="8"/>
       <c r="H245" s="8"/>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A246" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B246" s="10" t="s">
+      <c r="B246" t="s">
         <v>4</v>
       </c>
       <c r="C246" s="8"/>
@@ -5738,7 +5771,7 @@
       <c r="G246" s="8"/>
       <c r="H246" s="8"/>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A247" s="8" t="s">
         <v>5</v>
       </c>
@@ -5752,7 +5785,7 @@
       <c r="G247" s="8"/>
       <c r="H247" s="8"/>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A248" s="8" t="s">
         <v>6</v>
       </c>
@@ -5766,7 +5799,7 @@
       <c r="G248" s="8"/>
       <c r="H248" s="8"/>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A249" s="8" t="s">
         <v>8</v>
       </c>
@@ -5780,7 +5813,7 @@
       <c r="G249" s="8"/>
       <c r="H249" s="8"/>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A250" s="1" t="s">
         <v>10</v>
       </c>
@@ -5792,7 +5825,7 @@
       <c r="G250" s="8"/>
       <c r="H250" s="8"/>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A251" s="8" t="s">
         <v>11</v>
       </c>
@@ -5818,7 +5851,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A252" s="8" t="s">
         <v>40</v>
       </c>
@@ -5828,7 +5861,7 @@
       <c r="C252" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D252" s="10" t="s">
+      <c r="D252" t="s">
         <v>4</v>
       </c>
       <c r="E252" s="8" t="s">
@@ -5842,7 +5875,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A253" s="5" t="s">
         <v>170</v>
       </c>
@@ -5866,7 +5899,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A254" s="7" t="s">
         <v>32</v>
       </c>
@@ -5888,7 +5921,7 @@
       </c>
       <c r="H254" s="8"/>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A255" s="5" t="s">
         <v>38</v>
       </c>
@@ -5911,7 +5944,7 @@
       </c>
       <c r="H255" s="8"/>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="3"/>
@@ -5921,119 +5954,119 @@
       <c r="G256" s="2"/>
       <c r="H256" s="2"/>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A257" s="22" t="s">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A257" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B257" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="C257" s="23"/>
+      <c r="B257" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="C257" s="20"/>
       <c r="D257" s="5"/>
       <c r="E257" s="5"/>
       <c r="F257" s="5"/>
       <c r="G257" s="5"/>
       <c r="H257" s="5"/>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A258" s="22" t="s">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A258" s="19" t="s">
         <v>2</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="C258" s="23"/>
+        <v>202</v>
+      </c>
+      <c r="C258" s="20"/>
       <c r="D258" s="5"/>
       <c r="E258" s="5"/>
       <c r="F258" s="5"/>
       <c r="G258" s="5"/>
       <c r="H258" s="5"/>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A259" s="22" t="s">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A259" s="19" t="s">
         <v>3</v>
       </c>
       <c r="B259" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C259" s="23"/>
+      <c r="C259" s="20"/>
       <c r="D259" s="5"/>
       <c r="E259" s="5"/>
       <c r="F259" s="5"/>
       <c r="G259" s="5"/>
       <c r="H259" s="5"/>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A260" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B260" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="C260" s="23"/>
+      <c r="B260" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="C260" s="20"/>
       <c r="D260" s="5"/>
       <c r="E260" s="5"/>
       <c r="F260" s="5"/>
       <c r="G260" s="5"/>
       <c r="H260" s="5"/>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A261" s="22" t="s">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A261" s="19" t="s">
         <v>5</v>
       </c>
       <c r="B261" s="7">
         <v>1</v>
       </c>
-      <c r="C261" s="23"/>
-      <c r="D261" s="24"/>
+      <c r="C261" s="20"/>
+      <c r="D261" s="21"/>
       <c r="E261" s="5"/>
       <c r="F261" s="5"/>
       <c r="G261" s="5"/>
       <c r="H261" s="5"/>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A262" s="22" t="s">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A262" s="19" t="s">
         <v>8</v>
       </c>
       <c r="B262" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C262" s="23"/>
-      <c r="D262" s="24"/>
+      <c r="C262" s="20"/>
+      <c r="D262" s="21"/>
       <c r="E262" s="5"/>
       <c r="F262" s="5"/>
       <c r="G262" s="5"/>
       <c r="H262" s="5"/>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A263" s="22" t="s">
-        <v>204</v>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A263" s="19" t="s">
+        <v>203</v>
       </c>
       <c r="B263" s="5"/>
-      <c r="C263" s="23"/>
-      <c r="D263" s="24"/>
+      <c r="C263" s="20"/>
+      <c r="D263" s="21"/>
       <c r="E263" s="5"/>
       <c r="F263" s="5"/>
       <c r="G263" s="5"/>
       <c r="H263" s="5"/>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A264" s="22" t="s">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A264" s="19" t="s">
         <v>10</v>
       </c>
       <c r="B264" s="5"/>
-      <c r="C264" s="23"/>
+      <c r="C264" s="20"/>
       <c r="D264" s="5"/>
       <c r="E264" s="5"/>
       <c r="F264" s="5"/>
       <c r="G264" s="5"/>
       <c r="H264" s="5"/>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A265" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B265" s="23" t="s">
+      <c r="B265" s="20" t="s">
         <v>12</v>
       </c>
       <c r="C265" s="5" t="s">
@@ -6055,57 +6088,57 @@
         <v>6</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A266" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="B266" s="25">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A266" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="B266" s="22">
         <v>1</v>
       </c>
       <c r="C266" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D266" s="20" t="s">
+      <c r="D266" s="17" t="s">
         <v>4</v>
       </c>
       <c r="E266" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F266" s="20"/>
-      <c r="G266" s="20" t="s">
+      <c r="F266" s="17"/>
+      <c r="G266" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="H266" s="20" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A267" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="B267" s="26">
+      <c r="H266" s="17" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A267" t="s">
+        <v>47</v>
+      </c>
+      <c r="B267" s="23">
         <v>2.8998115122517001E-2</v>
       </c>
       <c r="C267" t="s">
         <v>18</v>
       </c>
-      <c r="D267" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="E267" s="5" t="s">
+      <c r="D267" t="s">
+        <v>19</v>
+      </c>
+      <c r="E267" t="s">
         <v>21</v>
       </c>
-      <c r="F267" s="20"/>
-      <c r="G267" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="H267" s="5" t="s">
+      <c r="F267" s="8"/>
+      <c r="G267" t="s">
+        <v>20</v>
+      </c>
+      <c r="H267" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A268" s="20" t="s">
-        <v>205</v>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A268" s="17" t="s">
+        <v>204</v>
       </c>
       <c r="B268" s="6">
         <v>1.1684210526315801E-3</v>
@@ -6113,23 +6146,23 @@
       <c r="C268" t="s">
         <v>18</v>
       </c>
-      <c r="D268" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="E268" s="20" t="s">
+      <c r="D268" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="E268" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="F268" s="20"/>
-      <c r="G268" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="H268" s="21" t="s">
+      <c r="F268" s="17"/>
+      <c r="G268" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H268" s="18" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A269" s="17" t="s">
         <v>206</v>
-      </c>
-    </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A269" s="20" t="s">
-        <v>207</v>
       </c>
       <c r="B269" s="6">
         <v>2.9473684210526402E-9</v>
@@ -6137,454 +6170,841 @@
       <c r="C269" t="s">
         <v>18</v>
       </c>
-      <c r="D269" s="20" t="s">
+      <c r="D269" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="E269" s="20" t="s">
+      <c r="E269" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="F269" s="20"/>
-      <c r="G269" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="H269" s="21" t="s">
+      <c r="F269" s="17"/>
+      <c r="G269" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H269" s="18" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A270" s="17" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A270" s="20" t="s">
-        <v>209</v>
-      </c>
-      <c r="B270" s="27">
+      <c r="B270" s="24">
         <v>5.3052631578947428E-2</v>
       </c>
       <c r="C270" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D270" s="20" t="s">
+      <c r="D270" s="17" t="s">
         <v>4</v>
       </c>
       <c r="E270" t="s">
         <v>9</v>
       </c>
-      <c r="F270" s="19"/>
+      <c r="F270" s="16"/>
       <c r="G270" t="s">
         <v>20</v>
       </c>
-      <c r="H270" s="20" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H270" s="17" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>29</v>
       </c>
-      <c r="B271" s="27">
+      <c r="B271" s="24">
         <v>5.8947368421052686E-3</v>
       </c>
-      <c r="C271" s="20" t="s">
+      <c r="C271" s="17" t="s">
         <v>30</v>
       </c>
       <c r="D271" s="5"/>
       <c r="E271" t="s">
         <v>9</v>
       </c>
-      <c r="F271" s="28" t="s">
-        <v>190</v>
+      <c r="F271" s="25" t="s">
+        <v>189</v>
       </c>
       <c r="G271" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>101</v>
       </c>
-      <c r="B272" s="16">
+      <c r="B272" s="15">
         <v>2.2105263157894801E-6</v>
       </c>
-      <c r="C272" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D272" s="20"/>
-      <c r="E272" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F272" s="28" t="s">
-        <v>190</v>
+      <c r="C272" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D272" s="17"/>
+      <c r="E272" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F272" s="25" t="s">
+        <v>189</v>
       </c>
       <c r="G272" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>100</v>
       </c>
-      <c r="B273" s="16">
+      <c r="B273" s="15">
         <v>2.10526315789474E-6</v>
       </c>
-      <c r="C273" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D273" s="20"/>
-      <c r="E273" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F273" s="28" t="s">
-        <v>190</v>
+      <c r="C273" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D273" s="17"/>
+      <c r="E273" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F273" s="25" t="s">
+        <v>189</v>
       </c>
       <c r="G273" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A274" s="21" t="s">
-        <v>210</v>
-      </c>
-      <c r="B274" s="16">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A274" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="B274" s="15">
         <v>1.05263157894737E-7</v>
       </c>
-      <c r="C274" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D274" s="20"/>
-      <c r="E274" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F274" s="20" t="s">
-        <v>190</v>
+      <c r="C274" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D274" s="17"/>
+      <c r="E274" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F274" s="17" t="s">
+        <v>189</v>
       </c>
       <c r="G274" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>37</v>
       </c>
-      <c r="B275" s="16">
+      <c r="B275" s="15">
         <v>1.8842105263157901E-5</v>
       </c>
-      <c r="C275" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D275" s="20"/>
+      <c r="C275" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D275" s="17"/>
       <c r="E275" t="s">
         <v>9</v>
       </c>
-      <c r="F275" s="28" t="s">
-        <v>190</v>
+      <c r="F275" s="25" t="s">
+        <v>189</v>
       </c>
       <c r="G275" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A276" s="21" t="s">
-        <v>198</v>
-      </c>
-      <c r="B276" s="16">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A276" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="B276" s="15">
         <v>5.7894736842105305E-7</v>
       </c>
-      <c r="C276" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D276" s="20"/>
-      <c r="E276" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F276" s="28" t="s">
-        <v>190</v>
+      <c r="C276" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D276" s="17"/>
+      <c r="E276" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F276" s="25" t="s">
+        <v>189</v>
       </c>
       <c r="G276" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A277" s="21" t="s">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A277" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="B277" s="16">
+      <c r="B277" s="15">
         <v>2.1052631578947401E-7</v>
       </c>
-      <c r="C277" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D277" s="20"/>
-      <c r="E277" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F277" s="20" t="s">
-        <v>190</v>
+      <c r="C277" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D277" s="17"/>
+      <c r="E277" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F277" s="17" t="s">
+        <v>189</v>
       </c>
       <c r="G277" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A278" s="21" t="s">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A278" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="B278" s="15">
+        <v>1.05263157894737E-9</v>
+      </c>
+      <c r="C278" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D278" s="17"/>
+      <c r="E278" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F278" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="G278" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A279" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="B278" s="16">
-        <v>1.05263157894737E-9</v>
-      </c>
-      <c r="C278" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D278" s="20"/>
-      <c r="E278" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F278" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="G278" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A279" s="21" t="s">
+      <c r="B279" s="15">
+        <v>1.5789473684210501E-7</v>
+      </c>
+      <c r="C279" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D279" s="17"/>
+      <c r="E279" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F279" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="G279" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A280" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="B279" s="16">
-        <v>1.5789473684210501E-7</v>
-      </c>
-      <c r="C279" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D279" s="20"/>
-      <c r="E279" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F279" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="G279" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A280" s="21" t="s">
+      <c r="B280" s="15">
+        <v>4.2105263157894802E-7</v>
+      </c>
+      <c r="C280" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D280" s="17"/>
+      <c r="E280" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F280" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="G280" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A281" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="B281" s="15">
+        <v>1.0526315789473699E-11</v>
+      </c>
+      <c r="C281" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D281" s="17"/>
+      <c r="E281" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F281" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="G281" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A282" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="B280" s="16">
-        <v>4.2105263157894802E-7</v>
-      </c>
-      <c r="C280" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D280" s="20"/>
-      <c r="E280" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F280" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="G280" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A281" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="B281" s="16">
-        <v>1.0526315789473699E-11</v>
-      </c>
-      <c r="C281" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D281" s="20"/>
-      <c r="E281" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F281" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="G281" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A282" s="21" t="s">
+      <c r="B282" s="15">
+        <v>7.3684210526315899E-7</v>
+      </c>
+      <c r="C282" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D282" s="17"/>
+      <c r="E282" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F282" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="G282" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A283" s="18" t="s">
         <v>214</v>
-      </c>
-      <c r="B282" s="16">
-        <v>7.3684210526315899E-7</v>
-      </c>
-      <c r="C282" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D282" s="20"/>
-      <c r="E282" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F282" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="G282" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A283" s="21" t="s">
-        <v>215</v>
       </c>
       <c r="B283" s="6">
         <v>0</v>
       </c>
-      <c r="C283" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E283" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F283" s="20" t="s">
-        <v>190</v>
+      <c r="C283" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E283" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F283" s="17" t="s">
+        <v>189</v>
       </c>
       <c r="G283" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A284" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="B284" s="16">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A284" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="B284" s="15">
         <v>1.05263157894737E-7</v>
       </c>
-      <c r="C284" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E284" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F284" s="20" t="s">
-        <v>190</v>
+      <c r="C284" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E284" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F284" s="17" t="s">
+        <v>189</v>
       </c>
       <c r="G284" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A285" s="21" t="s">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A285" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="B285" s="16">
+      <c r="B285" s="15">
         <v>3.1578947368421103E-11</v>
       </c>
-      <c r="C285" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E285" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F285" s="20" t="s">
-        <v>190</v>
+      <c r="C285" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E285" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F285" s="17" t="s">
+        <v>189</v>
       </c>
       <c r="G285" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A286" s="21" t="s">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A286" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="B286" s="15">
+        <v>1.0526315789473701E-8</v>
+      </c>
+      <c r="C286" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E286" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F286" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="G286" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A287" s="18" t="s">
         <v>216</v>
       </c>
-      <c r="B286" s="16">
-        <v>1.0526315789473701E-8</v>
-      </c>
-      <c r="C286" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E286" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F286" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="G286" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A287" s="21" t="s">
+      <c r="B287" s="15">
+        <v>1.2631578947368401E-6</v>
+      </c>
+      <c r="C287" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E287" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F287" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="G287" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A288" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="B287" s="16">
-        <v>1.2631578947368401E-6</v>
-      </c>
-      <c r="C287" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E287" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F287" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="G287" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A288" s="21" t="s">
+      <c r="B288" s="15">
+        <v>2.1052631578947401E-7</v>
+      </c>
+      <c r="C288" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E288" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F288" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="G288" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A289" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="B288" s="16">
+      <c r="B289" s="15">
+        <v>2.1052631578947401E-8</v>
+      </c>
+      <c r="C289" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E289" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F289" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="G289" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A290" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="B290" s="15">
         <v>2.1052631578947401E-7</v>
       </c>
-      <c r="C288" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E288" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F288" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="G288" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A289" s="21" t="s">
-        <v>219</v>
-      </c>
-      <c r="B289" s="16">
-        <v>2.1052631578947401E-8</v>
-      </c>
-      <c r="C289" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E289" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F289" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="G289" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A290" s="21" t="s">
-        <v>220</v>
-      </c>
-      <c r="B290" s="16">
-        <v>2.1052631578947401E-7</v>
-      </c>
       <c r="C290" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E290" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F290" s="20" t="s">
-        <v>190</v>
+      <c r="E290" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F290" s="17" t="s">
+        <v>189</v>
       </c>
       <c r="G290" s="5" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A291" s="2"/>
+      <c r="B291" s="2"/>
+      <c r="C291" s="3"/>
+      <c r="D291" s="2"/>
+      <c r="E291" s="2"/>
+      <c r="F291" s="2"/>
+      <c r="G291" s="2"/>
+      <c r="H291" s="2"/>
+    </row>
+    <row r="292" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A292" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B292" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="C292" s="20"/>
+      <c r="D292" s="5"/>
+      <c r="E292" s="5"/>
+      <c r="F292" s="5"/>
+      <c r="G292" s="5"/>
+      <c r="H292" s="5"/>
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A293" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B293" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C293" s="20"/>
+      <c r="D293" s="5"/>
+      <c r="E293" s="5"/>
+      <c r="F293" s="5"/>
+      <c r="G293" s="5"/>
+      <c r="H293" s="5"/>
+    </row>
+    <row r="294" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A294" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B294" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C294" s="20"/>
+      <c r="D294" s="5"/>
+      <c r="E294" s="5"/>
+      <c r="F294" s="5"/>
+      <c r="G294" s="5"/>
+      <c r="H294" s="5"/>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A295" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B295" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="C295" s="20"/>
+      <c r="D295" s="5"/>
+      <c r="E295" s="5"/>
+      <c r="F295" s="5"/>
+      <c r="G295" s="5"/>
+      <c r="H295" s="5"/>
+    </row>
+    <row r="296" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A296" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B296" s="7">
+        <v>1</v>
+      </c>
+      <c r="C296" s="20"/>
+      <c r="D296" s="21"/>
+      <c r="E296" s="5"/>
+      <c r="F296" s="5"/>
+      <c r="G296" s="5"/>
+      <c r="H296" s="5"/>
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A297" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B297" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C297" s="20"/>
+      <c r="D297" s="21"/>
+      <c r="E297" s="5"/>
+      <c r="F297" s="5"/>
+      <c r="G297" s="5"/>
+      <c r="H297" s="5"/>
+    </row>
+    <row r="298" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A298" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B298" s="5"/>
+      <c r="C298" s="20"/>
+      <c r="D298" s="21"/>
+      <c r="E298" s="5"/>
+      <c r="F298" s="5"/>
+      <c r="G298" s="5"/>
+      <c r="H298" s="5"/>
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A299" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B299" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C299" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D299" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E299" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F299" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G299" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H299" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A300" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="B300" s="22">
+        <v>1</v>
+      </c>
+      <c r="C300" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D300" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="E300" t="s">
+        <v>9</v>
+      </c>
+      <c r="F300" s="17"/>
+      <c r="G300" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="H300" s="17" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A301" t="s">
+        <v>55</v>
+      </c>
+      <c r="B301" s="22">
+        <v>0.38400000000000001</v>
+      </c>
+      <c r="C301" t="s">
+        <v>18</v>
+      </c>
+      <c r="D301" t="s">
+        <v>44</v>
+      </c>
+      <c r="E301" t="s">
+        <v>24</v>
+      </c>
+      <c r="F301" s="17"/>
+      <c r="G301" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H301" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A302" t="s">
+        <v>227</v>
+      </c>
+      <c r="B302" s="15">
+        <v>8.2699999999999996E-11</v>
+      </c>
+      <c r="C302" t="s">
+        <v>18</v>
+      </c>
+      <c r="D302" t="s">
+        <v>19</v>
+      </c>
+      <c r="E302" t="s">
+        <v>8</v>
+      </c>
+      <c r="G302" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H302" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A303" t="s">
+        <v>229</v>
+      </c>
+      <c r="B303" s="15">
+        <v>7.4400000000000002E-10</v>
+      </c>
+      <c r="C303" t="s">
+        <v>18</v>
+      </c>
+      <c r="D303" t="s">
+        <v>4</v>
+      </c>
+      <c r="E303" t="s">
+        <v>8</v>
+      </c>
+      <c r="G303" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H303" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A304" t="s">
+        <v>231</v>
+      </c>
+      <c r="B304" s="15">
+        <v>8.2600000000000002E-5</v>
+      </c>
+      <c r="C304" t="s">
+        <v>18</v>
+      </c>
+      <c r="D304" t="s">
+        <v>4</v>
+      </c>
+      <c r="E304" t="s">
+        <v>9</v>
+      </c>
+      <c r="G304" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H304" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A305" t="s">
+        <v>233</v>
+      </c>
+      <c r="B305" s="15">
+        <v>3.3099999999999999E-10</v>
+      </c>
+      <c r="C305" t="s">
+        <v>18</v>
+      </c>
+      <c r="D305" t="s">
+        <v>4</v>
+      </c>
+      <c r="E305" t="s">
+        <v>8</v>
+      </c>
+      <c r="G305" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H305" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A306" t="s">
+        <v>235</v>
+      </c>
+      <c r="B306" s="15">
+        <v>5.1400000000000003E-12</v>
+      </c>
+      <c r="C306" t="s">
+        <v>18</v>
+      </c>
+      <c r="D306" t="s">
+        <v>4</v>
+      </c>
+      <c r="E306" t="s">
+        <v>8</v>
+      </c>
+      <c r="G306" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H306" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A307" t="s">
+        <v>88</v>
+      </c>
+      <c r="B307" s="15">
+        <v>2.8400000000000002E-4</v>
+      </c>
+      <c r="C307" t="s">
+        <v>18</v>
+      </c>
+      <c r="D307" t="s">
+        <v>4</v>
+      </c>
+      <c r="E307" t="s">
+        <v>9</v>
+      </c>
+      <c r="G307" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H307" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A308" t="s">
+        <v>237</v>
+      </c>
+      <c r="B308" s="15">
+        <v>5.7899999999999997E-10</v>
+      </c>
+      <c r="C308" t="s">
+        <v>18</v>
+      </c>
+      <c r="D308" t="s">
+        <v>4</v>
+      </c>
+      <c r="E308" t="s">
+        <v>8</v>
+      </c>
+      <c r="G308" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H308" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A309" t="s">
+        <v>90</v>
+      </c>
+      <c r="B309" s="15">
+        <v>3.0400000000000002E-4</v>
+      </c>
+      <c r="C309" t="s">
+        <v>18</v>
+      </c>
+      <c r="D309" t="s">
+        <v>4</v>
+      </c>
+      <c r="E309" t="s">
+        <v>9</v>
+      </c>
+      <c r="G309" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H309" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A310" t="s">
+        <v>95</v>
+      </c>
+      <c r="B310" s="15">
+        <v>-2.2699999999999999E-4</v>
+      </c>
+      <c r="C310" t="s">
+        <v>18</v>
+      </c>
+      <c r="D310" t="s">
+        <v>239</v>
+      </c>
+      <c r="E310" t="s">
+        <v>9</v>
+      </c>
+      <c r="G310" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H310" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -6596,17 +7016,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD968991-55C9-4627-9323-29F50518FFEB}">
   <dimension ref="A1:H97"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="86.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="86.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6620,7 +7040,7 @@
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>2</v>
       </c>
@@ -6634,11 +7054,11 @@
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="8"/>
@@ -6648,7 +7068,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>5</v>
       </c>
@@ -6662,7 +7082,7 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
@@ -6676,7 +7096,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>8</v>
       </c>
@@ -6690,7 +7110,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -6702,7 +7122,7 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>11</v>
       </c>
@@ -6728,7 +7148,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -6738,7 +7158,7 @@
       <c r="C9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" t="s">
         <v>4</v>
       </c>
       <c r="E9" t="s">
@@ -6752,7 +7172,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>47</v>
       </c>
@@ -6762,21 +7182,21 @@
       <c r="C10" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" t="s">
         <v>19</v>
       </c>
       <c r="E10" t="s">
         <v>21</v>
       </c>
       <c r="F10" s="8"/>
-      <c r="G10" s="10" t="s">
+      <c r="G10" t="s">
         <v>20</v>
       </c>
       <c r="H10" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>48</v>
       </c>
@@ -6786,21 +7206,21 @@
       <c r="C11" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" t="s">
         <v>19</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" s="8"/>
-      <c r="G11" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" s="10" t="s">
+      <c r="G11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>49</v>
       </c>
@@ -6810,69 +7230,69 @@
       <c r="C12" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" t="s">
         <v>19</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
       </c>
       <c r="F12" s="8"/>
-      <c r="G12" s="10" t="s">
+      <c r="G12" t="s">
         <v>20</v>
       </c>
       <c r="H12" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="13">
         <v>4.0000000000000001E-10</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" t="s">
         <v>4</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" s="8"/>
-      <c r="G13" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H13" s="10" t="s">
+      <c r="G13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>172</v>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="13">
         <v>3.2499999999999999E-4</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" t="s">
         <v>4</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
       </c>
       <c r="F14" s="8"/>
-      <c r="G14" s="10" t="s">
+      <c r="G14" t="s">
         <v>20</v>
       </c>
       <c r="H14" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>85</v>
       </c>
@@ -6882,66 +7302,65 @@
       <c r="C15" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" t="s">
         <v>4</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
       </c>
       <c r="F15" s="8"/>
-      <c r="G15" s="10" t="s">
+      <c r="G15" t="s">
         <v>20</v>
       </c>
       <c r="H15" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>120</v>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="13">
         <v>-8.7600000000000002E-5</v>
       </c>
       <c r="C16" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" t="s">
         <v>19</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
       </c>
       <c r="F16" s="8"/>
-      <c r="G16" s="10" t="s">
+      <c r="G16" t="s">
         <v>20</v>
       </c>
       <c r="H16" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="17">
+      <c r="B17" s="4">
         <v>0.56200000000000006</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="10"/>
+      <c r="C17" t="s">
+        <v>30</v>
+      </c>
       <c r="E17" t="s">
         <v>21</v>
       </c>
       <c r="F17" t="s">
         <v>33</v>
       </c>
-      <c r="G17" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>97</v>
       </c>
@@ -6951,21 +7370,21 @@
       <c r="C18" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" t="s">
         <v>4</v>
       </c>
       <c r="E18" t="s">
         <v>23</v>
       </c>
       <c r="F18" s="8"/>
-      <c r="G18" s="10" t="s">
+      <c r="G18" t="s">
         <v>20</v>
       </c>
       <c r="H18" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>55</v>
       </c>
@@ -6975,7 +7394,7 @@
       <c r="C19" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" t="s">
         <v>44</v>
       </c>
       <c r="E19" t="s">
@@ -6988,14 +7407,14 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="16">
+      <c r="B20" s="15">
         <v>1.06E-3</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" t="s">
         <v>30</v>
       </c>
       <c r="E20" t="s">
@@ -7004,18 +7423,18 @@
       <c r="F20" t="s">
         <v>39</v>
       </c>
-      <c r="G20" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="16">
+      <c r="B21" s="15">
         <v>2.0100000000000001E-3</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" t="s">
         <v>30</v>
       </c>
       <c r="E21" t="s">
@@ -7024,18 +7443,18 @@
       <c r="F21" t="s">
         <v>39</v>
       </c>
-      <c r="G21" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G21" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>100</v>
       </c>
-      <c r="B22" s="16">
+      <c r="B22" s="15">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" t="s">
         <v>30</v>
       </c>
       <c r="E22" t="s">
@@ -7044,18 +7463,18 @@
       <c r="F22" t="s">
         <v>39</v>
       </c>
-      <c r="G22" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>101</v>
       </c>
-      <c r="B23" s="16">
+      <c r="B23" s="15">
         <v>4.8500000000000002E-6</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" t="s">
         <v>30</v>
       </c>
       <c r="E23" t="s">
@@ -7064,18 +7483,18 @@
       <c r="F23" t="s">
         <v>39</v>
       </c>
-      <c r="G23" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G23" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>29</v>
       </c>
       <c r="B24" s="4">
         <v>1.43</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" t="s">
         <v>30</v>
       </c>
       <c r="E24" t="s">
@@ -7084,18 +7503,18 @@
       <c r="F24" t="s">
         <v>39</v>
       </c>
-      <c r="G24" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G24" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="16">
+      <c r="B25" s="15">
         <v>1E-3</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" t="s">
         <v>30</v>
       </c>
       <c r="E25" t="s">
@@ -7104,19 +7523,19 @@
       <c r="F25" t="s">
         <v>39</v>
       </c>
-      <c r="G25" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="16">
+      <c r="B26" s="15">
         <f>149/1000</f>
         <v>0.14899999999999999</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" t="s">
         <v>30</v>
       </c>
       <c r="E26" t="s">
@@ -7125,18 +7544,18 @@
       <c r="F26" t="s">
         <v>39</v>
       </c>
-      <c r="G26" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G26" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>36</v>
       </c>
-      <c r="B27" s="16">
+      <c r="B27" s="15">
         <v>1.5099999999999999E-5</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" t="s">
         <v>30</v>
       </c>
       <c r="E27" t="s">
@@ -7145,18 +7564,18 @@
       <c r="F27" t="s">
         <v>42</v>
       </c>
-      <c r="G27" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>94</v>
       </c>
-      <c r="B28" s="16">
+      <c r="B28" s="15">
         <v>1.15E-7</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" t="s">
         <v>30</v>
       </c>
       <c r="E28" t="s">
@@ -7165,19 +7584,19 @@
       <c r="F28" t="s">
         <v>42</v>
       </c>
-      <c r="G28" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G28" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="16">
+      <c r="B29" s="15">
         <f>422/1000</f>
         <v>0.42199999999999999</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" t="s">
         <v>30</v>
       </c>
       <c r="E29" t="s">
@@ -7186,15 +7605,15 @@
       <c r="F29" t="s">
         <v>42</v>
       </c>
-      <c r="G29" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="B30" s="16">
+      <c r="B30" s="15">
         <v>-3.2499999999999999E-4</v>
       </c>
       <c r="C30" t="s">
@@ -7206,18 +7625,18 @@
       <c r="E30" t="s">
         <v>9</v>
       </c>
-      <c r="G30" s="10" t="s">
+      <c r="G30" t="s">
         <v>20</v>
       </c>
       <c r="H30" s="8" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="B31" s="14">
+      <c r="B31" s="13">
         <v>-1.56E-4</v>
       </c>
       <c r="C31" s="8" t="s">
@@ -7230,14 +7649,14 @@
         <v>21</v>
       </c>
       <c r="F31" s="8"/>
-      <c r="G31" s="10" t="s">
+      <c r="G31" t="s">
         <v>20</v>
       </c>
       <c r="H31" s="8" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="3"/>
@@ -7247,7 +7666,7 @@
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>0</v>
       </c>
@@ -7261,7 +7680,7 @@
       <c r="G33" s="8"/>
       <c r="H33" s="8"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
         <v>2</v>
       </c>
@@ -7275,11 +7694,11 @@
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B35" t="s">
         <v>4</v>
       </c>
       <c r="C35" s="8"/>
@@ -7289,7 +7708,7 @@
       <c r="G35" s="8"/>
       <c r="H35" s="8"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
         <v>5</v>
       </c>
@@ -7303,7 +7722,7 @@
       <c r="G36" s="8"/>
       <c r="H36" s="8"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="8" t="s">
         <v>6</v>
       </c>
@@ -7317,7 +7736,7 @@
       <c r="G37" s="8"/>
       <c r="H37" s="8"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="8" t="s">
         <v>8</v>
       </c>
@@ -7331,7 +7750,7 @@
       <c r="G38" s="8"/>
       <c r="H38" s="8"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>10</v>
       </c>
@@ -7343,7 +7762,7 @@
       <c r="G39" s="8"/>
       <c r="H39" s="8"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="8" t="s">
         <v>11</v>
       </c>
@@ -7369,7 +7788,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>167</v>
       </c>
@@ -7379,7 +7798,7 @@
       <c r="C41" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D41" s="10" t="s">
+      <c r="D41" t="s">
         <v>4</v>
       </c>
       <c r="E41" t="s">
@@ -7393,7 +7812,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>47</v>
       </c>
@@ -7403,21 +7822,21 @@
       <c r="C42" t="s">
         <v>18</v>
       </c>
-      <c r="D42" s="10" t="s">
+      <c r="D42" t="s">
         <v>19</v>
       </c>
       <c r="E42" t="s">
         <v>21</v>
       </c>
       <c r="F42" s="8"/>
-      <c r="G42" s="10" t="s">
+      <c r="G42" t="s">
         <v>20</v>
       </c>
       <c r="H42" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>48</v>
       </c>
@@ -7427,21 +7846,21 @@
       <c r="C43" t="s">
         <v>18</v>
       </c>
-      <c r="D43" s="10" t="s">
+      <c r="D43" t="s">
         <v>19</v>
       </c>
       <c r="E43" t="s">
         <v>9</v>
       </c>
       <c r="F43" s="8"/>
-      <c r="G43" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H43" s="10" t="s">
+      <c r="G43" t="s">
+        <v>20</v>
+      </c>
+      <c r="H43" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -7451,69 +7870,69 @@
       <c r="C44" t="s">
         <v>18</v>
       </c>
-      <c r="D44" s="10" t="s">
+      <c r="D44" t="s">
         <v>19</v>
       </c>
       <c r="E44" t="s">
         <v>9</v>
       </c>
       <c r="F44" s="8"/>
-      <c r="G44" s="10" t="s">
+      <c r="G44" t="s">
         <v>20</v>
       </c>
       <c r="H44" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>27</v>
       </c>
-      <c r="B45" s="14">
+      <c r="B45" s="13">
         <v>4.0000000000000001E-10</v>
       </c>
       <c r="C45" t="s">
         <v>18</v>
       </c>
-      <c r="D45" s="10" t="s">
+      <c r="D45" t="s">
         <v>4</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
       </c>
       <c r="F45" s="8"/>
-      <c r="G45" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H45" s="10" t="s">
+      <c r="G45" t="s">
+        <v>20</v>
+      </c>
+      <c r="H45" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>172</v>
       </c>
-      <c r="B46" s="14">
+      <c r="B46" s="13">
         <v>3.2499999999999999E-4</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D46" s="10" t="s">
+      <c r="D46" t="s">
         <v>4</v>
       </c>
       <c r="E46" t="s">
         <v>9</v>
       </c>
       <c r="F46" s="8"/>
-      <c r="G46" s="10" t="s">
+      <c r="G46" t="s">
         <v>20</v>
       </c>
       <c r="H46" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>85</v>
       </c>
@@ -7523,21 +7942,21 @@
       <c r="C47" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D47" s="10" t="s">
+      <c r="D47" t="s">
         <v>4</v>
       </c>
       <c r="E47" t="s">
         <v>9</v>
       </c>
       <c r="F47" s="8"/>
-      <c r="G47" s="10" t="s">
+      <c r="G47" t="s">
         <v>20</v>
       </c>
       <c r="H47" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="8" t="s">
         <v>123</v>
       </c>
@@ -7547,42 +7966,41 @@
       <c r="C48" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D48" s="10" t="s">
+      <c r="D48" t="s">
         <v>4</v>
       </c>
       <c r="E48" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F48" s="8"/>
-      <c r="G48" s="10" t="s">
+      <c r="G48" t="s">
         <v>20</v>
       </c>
       <c r="H48" s="8" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>32</v>
       </c>
-      <c r="B49" s="17">
+      <c r="B49" s="4">
         <v>0.57199999999999995</v>
       </c>
-      <c r="C49" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D49" s="10"/>
+      <c r="C49" t="s">
+        <v>30</v>
+      </c>
       <c r="E49" t="s">
         <v>21</v>
       </c>
       <c r="F49" t="s">
         <v>33</v>
       </c>
-      <c r="G49" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G49" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>97</v>
       </c>
@@ -7592,21 +8010,21 @@
       <c r="C50" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D50" s="10" t="s">
+      <c r="D50" t="s">
         <v>4</v>
       </c>
       <c r="E50" t="s">
         <v>23</v>
       </c>
       <c r="F50" s="8"/>
-      <c r="G50" s="10" t="s">
+      <c r="G50" t="s">
         <v>20</v>
       </c>
       <c r="H50" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
         <v>161</v>
       </c>
@@ -7616,21 +8034,21 @@
       <c r="C51" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D51" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E51" s="10" t="s">
+      <c r="D51" t="s">
+        <v>4</v>
+      </c>
+      <c r="E51" t="s">
         <v>24</v>
       </c>
       <c r="F51" s="8"/>
-      <c r="G51" s="10" t="s">
+      <c r="G51" t="s">
         <v>20</v>
       </c>
       <c r="H51" s="8" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
         <v>163</v>
       </c>
@@ -7640,28 +8058,28 @@
       <c r="C52" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D52" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E52" s="10" t="s">
+      <c r="D52" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" t="s">
         <v>23</v>
       </c>
       <c r="F52" s="8"/>
-      <c r="G52" s="10" t="s">
+      <c r="G52" t="s">
         <v>20</v>
       </c>
       <c r="H52" s="8" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>34</v>
       </c>
-      <c r="B53" s="16">
+      <c r="B53" s="15">
         <v>7.36E-4</v>
       </c>
-      <c r="C53" s="10" t="s">
+      <c r="C53" t="s">
         <v>30</v>
       </c>
       <c r="E53" t="s">
@@ -7670,18 +8088,18 @@
       <c r="F53" t="s">
         <v>39</v>
       </c>
-      <c r="G53" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G53" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>35</v>
       </c>
-      <c r="B54" s="16">
+      <c r="B54" s="15">
         <v>2.0100000000000001E-3</v>
       </c>
-      <c r="C54" s="10" t="s">
+      <c r="C54" t="s">
         <v>30</v>
       </c>
       <c r="E54" t="s">
@@ -7690,18 +8108,18 @@
       <c r="F54" t="s">
         <v>39</v>
       </c>
-      <c r="G54" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G54" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>100</v>
       </c>
-      <c r="B55" s="16">
+      <c r="B55" s="15">
         <v>8.61E-4</v>
       </c>
-      <c r="C55" s="10" t="s">
+      <c r="C55" t="s">
         <v>30</v>
       </c>
       <c r="E55" t="s">
@@ -7710,18 +8128,18 @@
       <c r="F55" t="s">
         <v>39</v>
       </c>
-      <c r="G55" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G55" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>101</v>
       </c>
-      <c r="B56" s="16">
+      <c r="B56" s="15">
         <v>7.7599999999999999E-16</v>
       </c>
-      <c r="C56" s="10" t="s">
+      <c r="C56" t="s">
         <v>30</v>
       </c>
       <c r="E56" t="s">
@@ -7730,18 +8148,18 @@
       <c r="F56" t="s">
         <v>39</v>
       </c>
-      <c r="G56" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G56" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>29</v>
       </c>
       <c r="B57" s="4">
         <v>2.6499999999999999E-2</v>
       </c>
-      <c r="C57" s="10" t="s">
+      <c r="C57" t="s">
         <v>30</v>
       </c>
       <c r="E57" t="s">
@@ -7750,18 +8168,18 @@
       <c r="F57" t="s">
         <v>39</v>
       </c>
-      <c r="G57" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G57" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>37</v>
       </c>
-      <c r="B58" s="16">
+      <c r="B58" s="15">
         <v>1E-3</v>
       </c>
-      <c r="C58" s="10" t="s">
+      <c r="C58" t="s">
         <v>30</v>
       </c>
       <c r="E58" t="s">
@@ -7770,19 +8188,19 @@
       <c r="F58" t="s">
         <v>39</v>
       </c>
-      <c r="G58" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G58" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>38</v>
       </c>
-      <c r="B59" s="16">
+      <c r="B59" s="15">
         <f>153.04/1000</f>
         <v>0.15303999999999998</v>
       </c>
-      <c r="C59" s="10" t="s">
+      <c r="C59" t="s">
         <v>30</v>
       </c>
       <c r="E59" t="s">
@@ -7791,18 +8209,18 @@
       <c r="F59" t="s">
         <v>39</v>
       </c>
-      <c r="G59" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G59" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>36</v>
       </c>
-      <c r="B60" s="16">
+      <c r="B60" s="15">
         <v>1.5099999999999999E-5</v>
       </c>
-      <c r="C60" s="10" t="s">
+      <c r="C60" t="s">
         <v>30</v>
       </c>
       <c r="E60" t="s">
@@ -7811,18 +8229,18 @@
       <c r="F60" t="s">
         <v>42</v>
       </c>
-      <c r="G60" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G60" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>94</v>
       </c>
-      <c r="B61" s="16">
+      <c r="B61" s="15">
         <v>1.15E-7</v>
       </c>
-      <c r="C61" s="10" t="s">
+      <c r="C61" t="s">
         <v>30</v>
       </c>
       <c r="E61" t="s">
@@ -7831,19 +8249,19 @@
       <c r="F61" t="s">
         <v>42</v>
       </c>
-      <c r="G61" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G61" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>38</v>
       </c>
-      <c r="B62" s="16">
+      <c r="B62" s="15">
         <f>419/1000</f>
         <v>0.41899999999999998</v>
       </c>
-      <c r="C62" s="10" t="s">
+      <c r="C62" t="s">
         <v>30</v>
       </c>
       <c r="E62" t="s">
@@ -7852,15 +8270,15 @@
       <c r="F62" t="s">
         <v>42</v>
       </c>
-      <c r="G62" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G62" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="B63" s="16">
+      <c r="B63" s="15">
         <v>-3.2499999999999999E-4</v>
       </c>
       <c r="C63" t="s">
@@ -7872,18 +8290,18 @@
       <c r="E63" t="s">
         <v>9</v>
       </c>
-      <c r="G63" s="10" t="s">
+      <c r="G63" t="s">
         <v>20</v>
       </c>
       <c r="H63" s="8" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="B64" s="14">
+      <c r="B64" s="13">
         <v>-1.56E-4</v>
       </c>
       <c r="C64" s="8" t="s">
@@ -7896,14 +8314,14 @@
         <v>21</v>
       </c>
       <c r="F64" s="8"/>
-      <c r="G64" s="10" t="s">
+      <c r="G64" t="s">
         <v>20</v>
       </c>
       <c r="H64" s="8" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="3"/>
@@ -7913,7 +8331,7 @@
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>0</v>
       </c>
@@ -7927,7 +8345,7 @@
       <c r="G66" s="8"/>
       <c r="H66" s="8"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="8" t="s">
         <v>2</v>
       </c>
@@ -7941,11 +8359,11 @@
       <c r="G67" s="8"/>
       <c r="H67" s="8"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B68" s="10" t="s">
+      <c r="B68" t="s">
         <v>4</v>
       </c>
       <c r="C68" s="8"/>
@@ -7955,7 +8373,7 @@
       <c r="G68" s="8"/>
       <c r="H68" s="8"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="8" t="s">
         <v>5</v>
       </c>
@@ -7969,7 +8387,7 @@
       <c r="G69" s="8"/>
       <c r="H69" s="8"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="8" t="s">
         <v>6</v>
       </c>
@@ -7983,7 +8401,7 @@
       <c r="G70" s="8"/>
       <c r="H70" s="8"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="8" t="s">
         <v>8</v>
       </c>
@@ -7997,7 +8415,7 @@
       <c r="G71" s="8"/>
       <c r="H71" s="8"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>10</v>
       </c>
@@ -8009,7 +8427,7 @@
       <c r="G72" s="8"/>
       <c r="H72" s="8"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="8" t="s">
         <v>11</v>
       </c>
@@ -8035,7 +8453,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>173</v>
       </c>
@@ -8045,7 +8463,7 @@
       <c r="C74" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D74" s="10" t="s">
+      <c r="D74" t="s">
         <v>4</v>
       </c>
       <c r="E74" t="s">
@@ -8059,7 +8477,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="8" t="s">
         <v>40</v>
       </c>
@@ -8069,91 +8487,89 @@
       <c r="C75" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D75" s="10" t="s">
+      <c r="D75" t="s">
         <v>4</v>
       </c>
       <c r="E75" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F75" s="8"/>
-      <c r="G75" s="10" t="s">
+      <c r="G75" t="s">
         <v>20</v>
       </c>
       <c r="H75" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>78</v>
       </c>
-      <c r="B76" s="14">
+      <c r="B76" s="13">
         <v>5.5099999999999998E-5</v>
       </c>
       <c r="C76" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D76" s="10" t="s">
+      <c r="D76" t="s">
         <v>4</v>
       </c>
       <c r="E76" t="s">
         <v>9</v>
       </c>
       <c r="F76" s="8"/>
-      <c r="G76" s="10" t="s">
+      <c r="G76" t="s">
         <v>20</v>
       </c>
       <c r="H76" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>27</v>
       </c>
-      <c r="B77" s="14">
+      <c r="B77" s="13">
         <v>3.29E-10</v>
       </c>
       <c r="C77" t="s">
         <v>18</v>
       </c>
-      <c r="D77" s="10" t="s">
+      <c r="D77" t="s">
         <v>4</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
       </c>
       <c r="F77" s="8"/>
-      <c r="G77" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H77" s="10" t="s">
+      <c r="G77" t="s">
+        <v>20</v>
+      </c>
+      <c r="H77" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>32</v>
       </c>
-      <c r="B78" s="17">
+      <c r="B78" s="4">
         <v>0.14899999999999999</v>
       </c>
-      <c r="C78" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D78" s="10"/>
+      <c r="C78" t="s">
+        <v>30</v>
+      </c>
       <c r="E78" t="s">
         <v>21</v>
       </c>
       <c r="F78" t="s">
         <v>33</v>
       </c>
-      <c r="G78" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H78" s="10"/>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G78" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>55</v>
       </c>
@@ -8163,7 +8579,7 @@
       <c r="C79" t="s">
         <v>18</v>
       </c>
-      <c r="D79" s="10" t="s">
+      <c r="D79" t="s">
         <v>44</v>
       </c>
       <c r="E79" t="s">
@@ -8176,14 +8592,14 @@
         <v>43</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>34</v>
       </c>
-      <c r="B80" s="16">
+      <c r="B80" s="15">
         <v>7.67E-4</v>
       </c>
-      <c r="C80" s="10" t="s">
+      <c r="C80" t="s">
         <v>30</v>
       </c>
       <c r="E80" t="s">
@@ -8192,18 +8608,18 @@
       <c r="F80" t="s">
         <v>39</v>
       </c>
-      <c r="G80" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G80" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>35</v>
       </c>
-      <c r="B81" s="16">
+      <c r="B81" s="15">
         <v>1.6299999999999999E-3</v>
       </c>
-      <c r="C81" s="10" t="s">
+      <c r="C81" t="s">
         <v>30</v>
       </c>
       <c r="E81" t="s">
@@ -8212,18 +8628,18 @@
       <c r="F81" t="s">
         <v>39</v>
       </c>
-      <c r="G81" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G81" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>37</v>
       </c>
-      <c r="B82" s="16">
+      <c r="B82" s="15">
         <v>1E-3</v>
       </c>
-      <c r="C82" s="10" t="s">
+      <c r="C82" t="s">
         <v>30</v>
       </c>
       <c r="E82" t="s">
@@ -8232,19 +8648,19 @@
       <c r="F82" t="s">
         <v>39</v>
       </c>
-      <c r="G82" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G82" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>38</v>
       </c>
-      <c r="B83" s="16">
+      <c r="B83" s="15">
         <f>47.6/1000</f>
         <v>4.7600000000000003E-2</v>
       </c>
-      <c r="C83" s="10" t="s">
+      <c r="C83" t="s">
         <v>30</v>
       </c>
       <c r="E83" t="s">
@@ -8253,19 +8669,19 @@
       <c r="F83" t="s">
         <v>39</v>
       </c>
-      <c r="G83" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G83" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>38</v>
       </c>
-      <c r="B84" s="16">
+      <c r="B84" s="15">
         <f>101/1000</f>
         <v>0.10100000000000001</v>
       </c>
-      <c r="C84" s="10" t="s">
+      <c r="C84" t="s">
         <v>30</v>
       </c>
       <c r="E84" t="s">
@@ -8274,15 +8690,15 @@
       <c r="F84" t="s">
         <v>42</v>
       </c>
-      <c r="G84" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G84" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="B85" s="16">
+      <c r="B85" s="15">
         <v>-5.5099999999999998E-5</v>
       </c>
       <c r="C85" t="s">
@@ -8294,75 +8710,53 @@
       <c r="E85" t="s">
         <v>9</v>
       </c>
-      <c r="G85" s="10" t="s">
+      <c r="G85" t="s">
         <v>20</v>
       </c>
       <c r="H85" s="8" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B86" s="16"/>
-      <c r="C86" s="10"/>
-      <c r="G86" s="10"/>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B87" s="16"/>
-      <c r="C87" s="10"/>
-      <c r="G87" s="10"/>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B88" s="16"/>
-      <c r="C88" s="10"/>
-      <c r="G88" s="10"/>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B89" s="16"/>
-      <c r="C89" s="10"/>
-      <c r="G89" s="10"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B86" s="15"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B87" s="15"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B88" s="15"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B89" s="15"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B90" s="4"/>
-      <c r="C90" s="10"/>
-      <c r="G90" s="10"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B91" s="16"/>
-      <c r="C91" s="10"/>
-      <c r="G91" s="10"/>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B92" s="16"/>
-      <c r="C92" s="10"/>
-      <c r="G92" s="10"/>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B93" s="16"/>
-      <c r="C93" s="10"/>
-      <c r="G93" s="10"/>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B94" s="16"/>
-      <c r="C94" s="10"/>
-      <c r="G94" s="10"/>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B95" s="16"/>
-      <c r="C95" s="10"/>
-      <c r="G95" s="10"/>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B96" s="16"/>
-      <c r="G96" s="10"/>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B91" s="15"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B92" s="15"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B93" s="15"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B94" s="15"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B95" s="15"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B96" s="15"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="8"/>
-      <c r="B97" s="14"/>
+      <c r="B97" s="13"/>
       <c r="C97" s="8"/>
       <c r="D97" s="8"/>
       <c r="E97" s="8"/>
       <c r="F97" s="8"/>
-      <c r="G97" s="10"/>
       <c r="H97" s="8"/>
     </row>
   </sheetData>
@@ -8374,17 +8768,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20D067F8-C305-44D3-8E28-CF1FDCAD7A72}">
   <dimension ref="A1:H75"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="86.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="86.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8398,7 +8792,7 @@
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>2</v>
       </c>
@@ -8412,11 +8806,11 @@
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="8"/>
@@ -8426,7 +8820,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>5</v>
       </c>
@@ -8440,7 +8834,7 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
@@ -8454,7 +8848,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>8</v>
       </c>
@@ -8468,7 +8862,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -8480,7 +8874,7 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>11</v>
       </c>
@@ -8506,7 +8900,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>174</v>
       </c>
@@ -8516,7 +8910,7 @@
       <c r="C9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" t="s">
         <v>4</v>
       </c>
       <c r="E9" t="s">
@@ -8530,7 +8924,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>47</v>
       </c>
@@ -8540,21 +8934,21 @@
       <c r="C10" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" t="s">
         <v>19</v>
       </c>
       <c r="E10" t="s">
         <v>21</v>
       </c>
       <c r="F10" s="8"/>
-      <c r="G10" s="10" t="s">
+      <c r="G10" t="s">
         <v>20</v>
       </c>
       <c r="H10" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>165</v>
       </c>
@@ -8564,21 +8958,21 @@
       <c r="C11" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" t="s">
         <v>19</v>
       </c>
       <c r="E11" t="s">
         <v>23</v>
       </c>
       <c r="F11" s="8"/>
-      <c r="G11" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" s="10" t="s">
+      <c r="G11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>55</v>
       </c>
@@ -8588,560 +8982,551 @@
       <c r="C12" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" t="s">
         <v>44</v>
       </c>
       <c r="E12" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" t="s">
         <v>20</v>
       </c>
       <c r="H12" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>178</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="13">
         <v>3.0000000000000001E-5</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="10" t="s">
+      <c r="D13" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" t="s">
         <v>9</v>
       </c>
       <c r="F13" s="8"/>
-      <c r="G13" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H13" s="10" t="s">
+      <c r="G13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>180</v>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="13">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="C14" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="10" t="s">
+      <c r="D14" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" t="s">
         <v>9</v>
       </c>
       <c r="F14" s="8"/>
-      <c r="G14" s="10" t="s">
+      <c r="G14" t="s">
         <v>20</v>
       </c>
       <c r="H14" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>73</v>
       </c>
-      <c r="B15" s="14">
+      <c r="B15" s="13">
         <v>9.0000000000000006E-5</v>
       </c>
       <c r="C15" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="10" t="s">
+      <c r="D15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" t="s">
         <v>9</v>
       </c>
       <c r="F15" s="8"/>
-      <c r="G15" s="10" t="s">
+      <c r="G15" t="s">
         <v>20</v>
       </c>
       <c r="H15" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>182</v>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="13">
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="C16" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E16" s="10" t="s">
+      <c r="D16" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" t="s">
         <v>9</v>
       </c>
       <c r="F16" s="8"/>
-      <c r="G16" s="10" t="s">
+      <c r="G16" t="s">
         <v>20</v>
       </c>
       <c r="H16" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>49</v>
       </c>
-      <c r="B17" s="17">
+      <c r="B17" s="4">
         <f>0.2+0.00071996+0.64928</f>
         <v>0.84999996</v>
       </c>
       <c r="C17" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G17" s="10" t="s">
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" t="s">
         <v>20</v>
       </c>
       <c r="H17" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>183</v>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="13">
         <f>0.00020525+0.000034749</f>
         <v>2.3999900000000002E-4</v>
       </c>
       <c r="C18" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" t="s">
         <v>19</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" t="s">
         <v>9</v>
       </c>
       <c r="F18" s="8"/>
-      <c r="G18" s="10" t="s">
+      <c r="G18" t="s">
         <v>20</v>
       </c>
       <c r="H18" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>184</v>
       </c>
-      <c r="B19" s="14">
+      <c r="B19" s="13">
         <v>3.7199999999999998E-11</v>
       </c>
       <c r="C19" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E19" s="10" t="s">
+      <c r="D19" t="s">
+        <v>4</v>
+      </c>
+      <c r="E19" t="s">
         <v>8</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" t="s">
         <v>20</v>
       </c>
       <c r="H19" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>100</v>
       </c>
-      <c r="B20" s="14">
+      <c r="B20" s="13">
         <v>9.7999999999999997E-4</v>
       </c>
-      <c r="C20" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" s="10"/>
-      <c r="E20" s="20" t="s">
+      <c r="C20" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="17" t="s">
         <v>9</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+      <c r="G20" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="14">
+      <c r="B21" s="13">
         <v>8.1600000000000006E-3</v>
       </c>
-      <c r="C21" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" s="10"/>
+      <c r="C21" s="17" t="s">
+        <v>30</v>
+      </c>
       <c r="E21" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G21" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G21" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>191</v>
-      </c>
-      <c r="B22" s="14">
+        <v>190</v>
+      </c>
+      <c r="B22" s="13">
         <v>1.9999999999999999E-6</v>
       </c>
-      <c r="C22" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="10"/>
+      <c r="C22" s="17" t="s">
+        <v>30</v>
+      </c>
       <c r="E22" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="G22" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="14">
+      <c r="B23" s="13">
         <v>1.4999999999999999E-4</v>
       </c>
-      <c r="C23" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" s="10"/>
+      <c r="C23" s="17" t="s">
+        <v>30</v>
+      </c>
       <c r="E23" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+      <c r="G23" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="14">
+      <c r="B24" s="13">
         <v>5.67375E-3</v>
       </c>
-      <c r="C24" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D24" s="10"/>
+      <c r="C24" s="17" t="s">
+        <v>30</v>
+      </c>
       <c r="E24" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="G24" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G24" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>192</v>
-      </c>
-      <c r="B25" s="14">
+        <v>191</v>
+      </c>
+      <c r="B25" s="13">
         <v>1.8000000000000001E-4</v>
       </c>
-      <c r="C25" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D25" s="10"/>
+      <c r="C25" s="17" t="s">
+        <v>30</v>
+      </c>
       <c r="E25" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="G25" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>193</v>
-      </c>
-      <c r="B26" s="16">
+        <v>192</v>
+      </c>
+      <c r="B26" s="15">
         <v>3.0000000000000001E-5</v>
       </c>
-      <c r="C26" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D26" s="10"/>
+      <c r="C26" s="17" t="s">
+        <v>30</v>
+      </c>
       <c r="E26" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="G26" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G26" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>193</v>
+      </c>
+      <c r="B27" s="15">
+        <v>2.4000000000000001E-4</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
         <v>194</v>
       </c>
-      <c r="B27" s="16">
-        <v>2.4000000000000001E-4</v>
-      </c>
-      <c r="C27" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D27" s="10"/>
-      <c r="E27" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" s="20" t="s">
+      <c r="B28" s="15">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="G27" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>195</v>
-      </c>
-      <c r="B28" s="16">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="C28" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D28" s="10"/>
-      <c r="E28" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="G28" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G28" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>193</v>
-      </c>
-      <c r="B29" s="16">
+        <v>192</v>
+      </c>
+      <c r="B29" s="15">
         <v>5.2999999999999998E-4</v>
       </c>
-      <c r="C29" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E29" s="20" t="s">
+      <c r="C29" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E29" s="17" t="s">
         <v>9</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+      <c r="G29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>38</v>
       </c>
       <c r="B30" s="4">
         <v>3.3362499999999998E-3</v>
       </c>
-      <c r="C30" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E30" s="20" t="s">
+      <c r="C30" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="20" t="s">
+      <c r="F30" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G30" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
+        <v>195</v>
+      </c>
+      <c r="B31" s="15">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
         <v>196</v>
       </c>
-      <c r="B31" s="16">
-        <v>2.0000000000000002E-5</v>
-      </c>
-      <c r="C31" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E31" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" s="20" t="s">
+      <c r="B32" s="15">
+        <v>2.4000000000000001E-4</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="G31" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="G32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
         <v>197</v>
       </c>
-      <c r="B32" s="16">
-        <v>2.4000000000000001E-4</v>
-      </c>
-      <c r="C32" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E32" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" s="20" t="s">
+      <c r="B33" s="15">
+        <v>1.38E-5</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="G33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>198</v>
+      </c>
+      <c r="B34" s="15">
+        <v>1E-4</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="G32" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>198</v>
-      </c>
-      <c r="B33" s="16">
-        <v>1.38E-5</v>
-      </c>
-      <c r="C33" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E33" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="G34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
         <v>199</v>
       </c>
-      <c r="B34" s="16">
-        <v>1E-4</v>
-      </c>
-      <c r="C34" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E34" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" s="20" t="s">
+      <c r="B35" s="15">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="G34" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="G35" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="B35" s="16">
+      <c r="B36" s="15">
+        <v>4.8999999999999998E-4</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G36" t="s">
+        <v>31</v>
+      </c>
+      <c r="H36" s="8"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="B37" s="13">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="C35" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E35" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" s="20" t="s">
+      <c r="C37" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D37" s="8"/>
+      <c r="E37" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="G35" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="B36" s="16">
-        <v>4.8999999999999998E-4</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E36" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="G36" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H36" s="8"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="B37" s="14">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="C37" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D37" s="8"/>
-      <c r="E37" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="G37" s="10" t="s">
+      <c r="G37" t="s">
         <v>31</v>
       </c>
       <c r="H37" s="8"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="3"/>
@@ -9151,7 +9536,7 @@
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>0</v>
       </c>
@@ -9165,12 +9550,12 @@
       <c r="G39" s="8"/>
       <c r="H39" s="8"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B40" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
@@ -9179,11 +9564,11 @@
       <c r="G40" s="8"/>
       <c r="H40" s="8"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B41" s="10" t="s">
+      <c r="B41" t="s">
         <v>4</v>
       </c>
       <c r="C41" s="8"/>
@@ -9193,7 +9578,7 @@
       <c r="G41" s="8"/>
       <c r="H41" s="8"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="8" t="s">
         <v>5</v>
       </c>
@@ -9207,7 +9592,7 @@
       <c r="G42" s="8"/>
       <c r="H42" s="8"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="8" t="s">
         <v>6</v>
       </c>
@@ -9221,7 +9606,7 @@
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
         <v>8</v>
       </c>
@@ -9235,7 +9620,7 @@
       <c r="G44" s="8"/>
       <c r="H44" s="8"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>10</v>
       </c>
@@ -9247,7 +9632,7 @@
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="8" t="s">
         <v>11</v>
       </c>
@@ -9273,7 +9658,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>177</v>
       </c>
@@ -9283,7 +9668,7 @@
       <c r="C47" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D47" s="10" t="s">
+      <c r="D47" t="s">
         <v>4</v>
       </c>
       <c r="E47" t="s">
@@ -9297,7 +9682,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>47</v>
       </c>
@@ -9307,45 +9692,45 @@
       <c r="C48" t="s">
         <v>18</v>
       </c>
-      <c r="D48" s="10" t="s">
+      <c r="D48" t="s">
         <v>19</v>
       </c>
       <c r="E48" t="s">
         <v>21</v>
       </c>
       <c r="F48" s="8"/>
-      <c r="G48" s="10" t="s">
+      <c r="G48" t="s">
         <v>20</v>
       </c>
       <c r="H48" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="B49" s="25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A49" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="B49" s="22">
         <v>6.93</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D49" s="20" t="s">
+      <c r="D49" s="17" t="s">
         <v>4</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F49" s="20"/>
-      <c r="G49" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H49" s="20" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F49" s="17"/>
+      <c r="G49" t="s">
+        <v>20</v>
+      </c>
+      <c r="H49" s="17" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>55</v>
       </c>
@@ -9355,555 +9740,546 @@
       <c r="C50" t="s">
         <v>18</v>
       </c>
-      <c r="D50" s="10" t="s">
+      <c r="D50" t="s">
         <v>44</v>
       </c>
       <c r="E50" t="s">
         <v>24</v>
       </c>
-      <c r="G50" s="10" t="s">
+      <c r="G50" t="s">
         <v>20</v>
       </c>
       <c r="H50" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>178</v>
       </c>
-      <c r="B51" s="14">
+      <c r="B51" s="13">
         <v>3.0000000000000001E-5</v>
       </c>
       <c r="C51" t="s">
         <v>18</v>
       </c>
-      <c r="D51" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E51" s="10" t="s">
+      <c r="D51" t="s">
+        <v>4</v>
+      </c>
+      <c r="E51" t="s">
         <v>9</v>
       </c>
       <c r="F51" s="8"/>
-      <c r="G51" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H51" s="10" t="s">
+      <c r="G51" t="s">
+        <v>20</v>
+      </c>
+      <c r="H51" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>180</v>
       </c>
-      <c r="B52" s="14">
+      <c r="B52" s="13">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="C52" t="s">
         <v>18</v>
       </c>
-      <c r="D52" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E52" s="10" t="s">
+      <c r="D52" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" t="s">
         <v>9</v>
       </c>
       <c r="F52" s="8"/>
-      <c r="G52" s="10" t="s">
+      <c r="G52" t="s">
         <v>20</v>
       </c>
       <c r="H52" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>73</v>
       </c>
-      <c r="B53" s="14">
+      <c r="B53" s="13">
         <v>9.0000000000000006E-5</v>
       </c>
       <c r="C53" t="s">
         <v>18</v>
       </c>
-      <c r="D53" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E53" s="10" t="s">
+      <c r="D53" t="s">
+        <v>4</v>
+      </c>
+      <c r="E53" t="s">
         <v>9</v>
       </c>
       <c r="F53" s="8"/>
-      <c r="G53" s="10" t="s">
+      <c r="G53" t="s">
         <v>20</v>
       </c>
       <c r="H53" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>182</v>
       </c>
-      <c r="B54" s="14">
+      <c r="B54" s="13">
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="C54" t="s">
         <v>18</v>
       </c>
-      <c r="D54" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E54" s="10" t="s">
+      <c r="D54" t="s">
+        <v>4</v>
+      </c>
+      <c r="E54" t="s">
         <v>9</v>
       </c>
       <c r="F54" s="8"/>
-      <c r="G54" s="10" t="s">
+      <c r="G54" t="s">
         <v>20</v>
       </c>
       <c r="H54" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>49</v>
       </c>
-      <c r="B55" s="17">
+      <c r="B55" s="4">
         <f>0.2+0.00071996+0.64928</f>
         <v>0.84999996</v>
       </c>
       <c r="C55" t="s">
         <v>18</v>
       </c>
-      <c r="D55" s="10" t="s">
+      <c r="D55" t="s">
         <v>19</v>
       </c>
-      <c r="E55" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G55" s="10" t="s">
+      <c r="E55" t="s">
+        <v>9</v>
+      </c>
+      <c r="G55" t="s">
         <v>20</v>
       </c>
       <c r="H55" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>183</v>
       </c>
-      <c r="B56" s="14">
+      <c r="B56" s="13">
         <f>0.00020525+0.000034749</f>
         <v>2.3999900000000002E-4</v>
       </c>
       <c r="C56" t="s">
         <v>18</v>
       </c>
-      <c r="D56" s="10" t="s">
+      <c r="D56" t="s">
         <v>19</v>
       </c>
-      <c r="E56" s="10" t="s">
+      <c r="E56" t="s">
         <v>9</v>
       </c>
       <c r="F56" s="8"/>
-      <c r="G56" s="10" t="s">
+      <c r="G56" t="s">
         <v>20</v>
       </c>
       <c r="H56" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>184</v>
       </c>
-      <c r="B57" s="14">
+      <c r="B57" s="13">
         <v>3.7199999999999998E-11</v>
       </c>
       <c r="C57" t="s">
         <v>18</v>
       </c>
-      <c r="D57" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E57" s="10" t="s">
+      <c r="D57" t="s">
+        <v>4</v>
+      </c>
+      <c r="E57" t="s">
         <v>8</v>
       </c>
-      <c r="G57" s="10" t="s">
+      <c r="G57" t="s">
         <v>20</v>
       </c>
       <c r="H57" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>100</v>
       </c>
-      <c r="B58" s="14">
+      <c r="B58" s="13">
         <v>9.7999999999999997E-4</v>
       </c>
-      <c r="C58" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D58" s="10"/>
-      <c r="E58" s="20" t="s">
+      <c r="C58" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E58" s="17" t="s">
         <v>9</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="G58" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+      <c r="G58" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>32</v>
       </c>
-      <c r="B59" s="14">
+      <c r="B59" s="13">
         <v>8.1600000000000006E-3</v>
       </c>
-      <c r="C59" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D59" s="10"/>
+      <c r="C59" s="17" t="s">
+        <v>30</v>
+      </c>
       <c r="E59" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G59" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G59" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>191</v>
-      </c>
-      <c r="B60" s="14">
+        <v>190</v>
+      </c>
+      <c r="B60" s="13">
         <v>1.9999999999999999E-6</v>
       </c>
-      <c r="C60" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D60" s="10"/>
+      <c r="C60" s="17" t="s">
+        <v>30</v>
+      </c>
       <c r="E60" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F60" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="G60" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G60" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>37</v>
       </c>
-      <c r="B61" s="14">
+      <c r="B61" s="13">
         <v>1.4999999999999999E-4</v>
       </c>
-      <c r="C61" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D61" s="10"/>
+      <c r="C61" s="17" t="s">
+        <v>30</v>
+      </c>
       <c r="E61" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="G61" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+      <c r="G61" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>38</v>
       </c>
-      <c r="B62" s="14">
+      <c r="B62" s="13">
         <v>5.67375E-3</v>
       </c>
-      <c r="C62" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D62" s="10"/>
+      <c r="C62" s="17" t="s">
+        <v>30</v>
+      </c>
       <c r="E62" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F62" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="G62" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G62" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>192</v>
-      </c>
-      <c r="B63" s="14">
+        <v>191</v>
+      </c>
+      <c r="B63" s="13">
         <v>1.8000000000000001E-4</v>
       </c>
-      <c r="C63" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D63" s="10"/>
+      <c r="C63" s="17" t="s">
+        <v>30</v>
+      </c>
       <c r="E63" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="G63" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G63" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>193</v>
-      </c>
-      <c r="B64" s="16">
+        <v>192</v>
+      </c>
+      <c r="B64" s="15">
         <v>3.0000000000000001E-5</v>
       </c>
-      <c r="C64" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D64" s="10"/>
+      <c r="C64" s="17" t="s">
+        <v>30</v>
+      </c>
       <c r="E64" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="G64" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G64" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
+        <v>193</v>
+      </c>
+      <c r="B65" s="15">
+        <v>2.4000000000000001E-4</v>
+      </c>
+      <c r="C65" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E65" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F65" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G65" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
         <v>194</v>
       </c>
-      <c r="B65" s="16">
-        <v>2.4000000000000001E-4</v>
-      </c>
-      <c r="C65" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D65" s="10"/>
-      <c r="E65" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F65" s="20" t="s">
+      <c r="B66" s="15">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="C66" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E66" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F66" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="G65" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>195</v>
-      </c>
-      <c r="B66" s="16">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="C66" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D66" s="10"/>
-      <c r="E66" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F66" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="G66" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G66" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>193</v>
-      </c>
-      <c r="B67" s="16">
+        <v>192</v>
+      </c>
+      <c r="B67" s="15">
         <v>5.2999999999999998E-4</v>
       </c>
-      <c r="C67" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E67" s="20" t="s">
+      <c r="C67" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E67" s="17" t="s">
         <v>9</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="G67" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+      <c r="G67" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>38</v>
       </c>
       <c r="B68" s="4">
         <v>3.3362499999999998E-3</v>
       </c>
-      <c r="C68" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E68" s="20" t="s">
+      <c r="C68" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E68" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="F68" s="20" t="s">
+      <c r="F68" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="G68" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G68" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
+        <v>195</v>
+      </c>
+      <c r="B69" s="15">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="C69" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E69" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F69" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G69" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
         <v>196</v>
       </c>
-      <c r="B69" s="16">
-        <v>2.0000000000000002E-5</v>
-      </c>
-      <c r="C69" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E69" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F69" s="20" t="s">
+      <c r="B70" s="15">
+        <v>2.4000000000000001E-4</v>
+      </c>
+      <c r="C70" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E70" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F70" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="G69" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+      <c r="G70" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
         <v>197</v>
       </c>
-      <c r="B70" s="16">
-        <v>2.4000000000000001E-4</v>
-      </c>
-      <c r="C70" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E70" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F70" s="20" t="s">
+      <c r="B71" s="15">
+        <v>1.38E-5</v>
+      </c>
+      <c r="C71" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E71" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="G71" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>198</v>
+      </c>
+      <c r="B72" s="15">
+        <v>1E-4</v>
+      </c>
+      <c r="C72" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E72" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F72" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="G70" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>198</v>
-      </c>
-      <c r="B71" s="16">
-        <v>1.38E-5</v>
-      </c>
-      <c r="C71" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E71" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F71" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="G71" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+      <c r="G72" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
         <v>199</v>
       </c>
-      <c r="B72" s="16">
-        <v>1E-4</v>
-      </c>
-      <c r="C72" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E72" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F72" s="20" t="s">
+      <c r="B73" s="15">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="C73" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E73" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F73" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="G72" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+      <c r="G73" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A74" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="B73" s="16">
+      <c r="B74" s="15">
+        <v>4.8999999999999998E-4</v>
+      </c>
+      <c r="C74" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E74" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F74" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G74" t="s">
+        <v>31</v>
+      </c>
+      <c r="H74" s="8"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A75" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="B75" s="13">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="C73" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E73" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F73" s="20" t="s">
+      <c r="C75" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D75" s="8"/>
+      <c r="E75" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F75" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="G73" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="B74" s="16">
-        <v>4.8999999999999998E-4</v>
-      </c>
-      <c r="C74" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E74" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F74" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="G74" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H74" s="8"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="B75" s="14">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="C75" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D75" s="8"/>
-      <c r="E75" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F75" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="G75" s="10" t="s">
+      <c r="G75" t="s">
         <v>31</v>
       </c>
       <c r="H75" s="8"/>
@@ -9917,32 +10293,34 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{998EBEEB-B02A-47FC-B25F-8D09BAB943A0}">
   <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -9950,7 +10328,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -9958,15 +10336,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -9974,12 +10352,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -10005,14 +10383,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B9" s="4">
         <v>1</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="16" t="s">
         <v>16</v>
       </c>
       <c r="D9" t="s">
@@ -10025,17 +10403,17 @@
         <v>17</v>
       </c>
       <c r="H9" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>174</v>
       </c>
       <c r="B10" s="4">
         <v>2.5190000000000001</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="16" t="s">
         <v>16</v>
       </c>
       <c r="D10" t="s">
@@ -10051,31 +10429,31 @@
         <v>175</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>55</v>
       </c>
       <c r="B11" s="4">
         <v>0.14300000000000002</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" s="26" t="s">
         <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="20"/>
+      <c r="F11" s="17"/>
       <c r="G11" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="20" t="s">
+      <c r="H11" s="17" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -10083,7 +10461,7 @@
         <f>0.2255/1000</f>
         <v>2.2550000000000001E-4</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" t="s">
         <v>30</v>
       </c>
       <c r="D12" s="8"/>
@@ -10093,18 +10471,18 @@
       <c r="F12" t="s">
         <v>33</v>
       </c>
-      <c r="G12" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B13" s="4">
         <v>2.2000000000000002E-2</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" s="26" t="s">
         <v>18</v>
       </c>
       <c r="D13" t="s">
@@ -10117,17 +10495,17 @@
         <v>20</v>
       </c>
       <c r="H13" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>88</v>
       </c>
-      <c r="B14" s="16">
+      <c r="B14" s="15">
         <v>2.0789999999999999E-5</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" s="26" t="s">
         <v>18</v>
       </c>
       <c r="D14" s="8" t="s">
@@ -10143,14 +10521,14 @@
         <v>89</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="4">
         <v>0.12100000000000001</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="16" t="s">
         <v>30</v>
       </c>
       <c r="E15" t="s">
@@ -10163,14 +10541,14 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>38</v>
       </c>
       <c r="B16" s="4">
         <v>1.6500000000000001E-2</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="16" t="s">
         <v>30</v>
       </c>
       <c r="E16" t="s">
@@ -10183,14 +10561,14 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B17" s="4">
         <v>-1.474E-3</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" s="26" t="s">
         <v>18</v>
       </c>
       <c r="D17" t="s">
@@ -10206,14 +10584,14 @@
         <v>122</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>94</v>
       </c>
-      <c r="B18" s="16">
+      <c r="B18" s="15">
         <v>2.0789999999999999E-5</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="16" t="s">
         <v>30</v>
       </c>
       <c r="E18" t="s">
